--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -1222,7 +1222,7 @@
     <row r="23" ht="30" customHeight="1">
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Especificaciones del broker al 2026-08-19 16:02 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El COSTO DE MANTENCIÓN (swap) se estima por días calendario: es exacto en periodos de semanas completas y puede quedar sobre el cargo real en periodos cortos que incluyan un fin de semana. Este simulador no incorpora stop loss.</t>
+          <t>Especificaciones del broker al 2026-08-19 16:07 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El COSTO DE MANTENCIÓN (swap) se estima por días calendario: es exacto en periodos de semanas completas y puede quedar sobre el cargo real en periodos cortos que incluyan un fin de semana. Este simulador no incorpora stop loss.</t>
         </is>
       </c>
       <c r="D23" s="26" t="n"/>
@@ -1426,7 +1426,7 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>579411.41</v>
+        <v>579262.16</v>
       </c>
       <c r="F3" s="28" t="n">
         <v>0.010063</v>
@@ -1435,7 +1435,7 @@
         <v>0.04</v>
       </c>
       <c r="H3" s="29" t="n">
-        <v>158.127</v>
+        <v>158.168</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1474,7 +1474,7 @@
         <v>0.00026</v>
       </c>
       <c r="H4" s="29" t="n">
-        <v>1.16787</v>
+        <v>1.16786</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1513,7 +1513,7 @@
         <v>0.0005</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>1.36106</v>
+        <v>1.36099</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1552,7 +1552,7 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>4510.28</v>
+        <v>4510.01</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1591,7 +1591,7 @@
         <v>0.05</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>66.392</v>
+        <v>66.40900000000001</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1630,7 +1630,7 @@
         <v>0.15</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>84.964</v>
+        <v>84.949</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1666,10 +1666,10 @@
         <v>0.015016</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>80.22</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>68424.38</v>
+        <v>68596.38</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>29460.86</v>
+        <v>29461.38</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1747,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="29" t="n">
-        <v>7720.53</v>
+        <v>7718.53</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1786,7 +1786,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="29" t="n">
-        <v>53509.51</v>
+        <v>53495.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -2347,7 +2347,7 @@
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 16:02 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 16:07 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Simulador'!$B$1:$N$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Simulador'!$B$1:$N$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,11 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00###"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="dd-mm-yy"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -94,7 +92,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -119,6 +117,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
     <fill>
@@ -153,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -168,7 +171,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -185,13 +190,21 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -203,9 +216,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -215,12 +225,12 @@
     <xf numFmtId="165" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -232,9 +242,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -645,22 +652,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C1:P23"/>
+  <dimension ref="C1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="3" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
     <col width="3" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
@@ -694,7 +701,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Seleccione el instrumento y registre las operaciones del periodo. El volumen y los costos se calculan automáticamente.</t>
+          <t>Seleccione el instrumento y registre las operaciones del periodo. El volumen en pesos y el volumen en lotes son la misma magnitud: al modificar uno, el otro se ajusta.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -809,19 +816,19 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="C7" s="10">
-        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(($E$10:$E$15&gt;0)*($F$10:$F$15=0))&gt;0,"⚠ Hay una operación con capital comprometido y sin precio de entrada.",IF(SUMPRODUCT(($F$10:$F$15&gt;0)*(ABS($F$10:$F$15/$P$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($P$7,$P$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(($E$10:$E$15&gt;0)*($I$10:$I$15=0))&gt;0,"⚠ Hay una operación bajo el volumen mínimo de 0,01 lotes, que requiere $"&amp;FIXED(0.01*$P$7*$P$4*$P$5,0)&amp;".",IF($L$19&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($I$10:$I$15,"&gt;0")&amp;" operación(es) sobre "&amp;$P$1&amp;". El volumen indicado es el que se ingresa en MT5.")))))</f>
-        <v/>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
+        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(($E$11:$E$16&gt;0)*($F$11:$F$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($F$11:$F$16&gt;0)*(ABS($F$11:$F$16/$P$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($P$7,$P$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($E$11:$E$16=0))&gt;0,"⚠ Hay una operación bajo el volumen mínimo de 0,01 lotes, que requiere $"&amp;FIXED(0.01*$P$7*$P$4*$P$5,0)&amp;".",IF($L$20&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($E$11:$E$16,"&gt;0")&amp;" operación(es) sobre "&amp;$P$1&amp;". El volumen en lotes es el que se ingresa en MT5.")))))</f>
+        <v/>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>precio_ref</t>
@@ -832,22 +839,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>OPERACIONES DEL PERIODO   ·   cada fila es una operación independiente, con su fecha, dirección y capital</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+    <row r="8">
       <c r="O8" t="inlineStr">
         <is>
           <t>swap_modo</t>
@@ -858,62 +850,26 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="24" customHeight="1">
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>DIRECCIÓN</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>CAPITAL COMPROMETIDO</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>PRECIO DE ENTRADA</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>PRECIO DE SALIDA</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>DÍAS DE MANTENCIÓN</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>VOLUMEN (LOTES)</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>COSTO DE APERTURA</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>COSTO DE MANTENCIÓN</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>RESULTADO NETO</t>
-        </is>
-      </c>
-      <c r="M9" s="12" t="inlineStr">
-        <is>
-          <t>OBSERVACIÓN</t>
-        </is>
-      </c>
+          <t>SIMULACIÓN</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>COSTOS</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="14" t="n"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>swap_compra</t>
@@ -924,46 +880,61 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="C10" s="13" t="n">
-        <v>46249</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>COMPRA</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>919</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>924</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="16">
-        <f>IFERROR(MAX(0,ROUNDDOWN($E10/($F10*$P$4*$P$5),2)),0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="9">
-        <f>IF($I10=0,"",$I10*$P$6*$P$4)</f>
-        <v/>
-      </c>
-      <c r="K10" s="9">
-        <f>IF(OR($I10=0,$H10=0),"",-IF($D10="VENTA",$P$10,$P$9)*IF($P$8=1,$I10*POWER(10,-$P$2)*$P$4,$I10*$F10*$P$4/100/360)*$H10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="9">
-        <f>IF($I10=0,"",IF($D10="COMPRA",$G10-$F10,$F10-$G10)*$I10*$P$4-N($J10)-N($K10))</f>
-        <v/>
-      </c>
-      <c r="M10" s="17">
-        <f>IF(OR($I10=0,$G10=""),"",IF(AND($D10="COMPRA",$G10&lt;$F10),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($D10="VENTA",$G10&gt;$F10),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
-        <v/>
+    <row r="10" ht="34" customHeight="1">
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>VOLUMEN EN CLP</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>VOLUMEN EN LOTES</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>PRECIO DE ENTRADA</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>PRECIO DE SALIDA</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>DÍAS DE MANTENCIÓN</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>RESULTADO BRUTO</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>COSTO DE APERTURA (SPREAD)</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>COSTO DE MANTENCIÓN (SWAP)</t>
+        </is>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>RESULTADO NETO</t>
+        </is>
+      </c>
+      <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -976,312 +947,360 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="C11" s="13" t="n">
-        <v>46251</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>496125</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>918.75</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>923.75</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="9">
+        <f>IF(OR($E11=0,$G11=0),"",IF($C11="COMPRA",$G11-$F11,$F11-$G11)*$E11*$P$4)</f>
+        <v/>
+      </c>
+      <c r="J11" s="9">
+        <f>IF($E11=0,"",$E11*$P$6*$P$4)</f>
+        <v/>
+      </c>
+      <c r="K11" s="9">
+        <f>IF(OR($E11=0,$H11=0),"",-IF($C11="VENTA",$P$10,$P$9)*IF($P$8=1,$E11*POWER(10,-$P$2)*$P$4,$E11*$F11*$P$4/100/360)*$H11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="9">
+        <f>IF($E11=0,"",N($I11)-N($J11)-N($K11))</f>
+        <v/>
+      </c>
+      <c r="M11" s="20">
+        <f>IF(OR($E11=0,$G11=0),"",IF(AND($C11="COMPRA",$G11&lt;$F11),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C11="VENTA",$G11&gt;$F11),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>VENTA</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>400000</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>926</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>923</v>
-      </c>
-      <c r="H11" s="15" t="n">
+      <c r="D12" s="8" t="n">
+        <v>398072</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>925.75</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>922.75</v>
+      </c>
+      <c r="H12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="16">
-        <f>IFERROR(MAX(0,ROUNDDOWN($E11/($F11*$P$4*$P$5),2)),0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="9">
-        <f>IF($I11=0,"",$I11*$P$6*$P$4)</f>
-        <v/>
-      </c>
-      <c r="K11" s="9">
-        <f>IF(OR($I11=0,$H11=0),"",-IF($D11="VENTA",$P$10,$P$9)*IF($P$8=1,$I11*POWER(10,-$P$2)*$P$4,$I11*$F11*$P$4/100/360)*$H11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="9">
-        <f>IF($I11=0,"",IF($D11="COMPRA",$G11-$F11,$F11-$G11)*$I11*$P$4-N($J11)-N($K11))</f>
-        <v/>
-      </c>
-      <c r="M11" s="17">
-        <f>IF(OR($I11=0,$G11=""),"",IF(AND($D11="COMPRA",$G11&lt;$F11),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($D11="VENTA",$G11&gt;$F11),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="C12" s="13" t="n">
-        <v>46252</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="I12" s="9">
+        <f>IF(OR($E12=0,$G12=0),"",IF($C12="COMPRA",$G12-$F12,$F12-$G12)*$E12*$P$4)</f>
+        <v/>
+      </c>
+      <c r="J12" s="9">
+        <f>IF($E12=0,"",$E12*$P$6*$P$4)</f>
+        <v/>
+      </c>
+      <c r="K12" s="9">
+        <f>IF(OR($E12=0,$H12=0),"",-IF($C12="VENTA",$P$10,$P$9)*IF($P$8=1,$E12*POWER(10,-$P$2)*$P$4,$E12*$F12*$P$4/100/360)*$H12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="9">
+        <f>IF($E12=0,"",N($I12)-N($J12)-N($K12))</f>
+        <v/>
+      </c>
+      <c r="M12" s="20">
+        <f>IF(OR($E12=0,$G12=0),"",IF(AND($C12="COMPRA",$G12&lt;$F12),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C12="VENTA",$G12&gt;$F12),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>922</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>920.5</v>
-      </c>
-      <c r="H12" s="15" t="n">
+      <c r="D13" s="8" t="n">
+        <v>294960</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>921.75</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>920.25</v>
+      </c>
+      <c r="H13" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="16">
-        <f>IFERROR(MAX(0,ROUNDDOWN($E12/($F12*$P$4*$P$5),2)),0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="9">
-        <f>IF($I12=0,"",$I12*$P$6*$P$4)</f>
-        <v/>
-      </c>
-      <c r="K12" s="9">
-        <f>IF(OR($I12=0,$H12=0),"",-IF($D12="VENTA",$P$10,$P$9)*IF($P$8=1,$I12*POWER(10,-$P$2)*$P$4,$I12*$F12*$P$4/100/360)*$H12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="9">
-        <f>IF($I12=0,"",IF($D12="COMPRA",$G12-$F12,$F12-$G12)*$I12*$P$4-N($J12)-N($K12))</f>
-        <v/>
-      </c>
-      <c r="M12" s="17">
-        <f>IF(OR($I12=0,$G12=""),"",IF(AND($D12="COMPRA",$G12&lt;$F12),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($D12="VENTA",$G12&gt;$F12),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="16">
-        <f>IFERROR(MAX(0,ROUNDDOWN($E13/($F13*$P$4*$P$5),2)),0)</f>
+      <c r="I13" s="9">
+        <f>IF(OR($E13=0,$G13=0),"",IF($C13="COMPRA",$G13-$F13,$F13-$G13)*$E13*$P$4)</f>
         <v/>
       </c>
       <c r="J13" s="9">
-        <f>IF($I13=0,"",$I13*$P$6*$P$4)</f>
+        <f>IF($E13=0,"",$E13*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K13" s="9">
-        <f>IF(OR($I13=0,$H13=0),"",-IF($D13="VENTA",$P$10,$P$9)*IF($P$8=1,$I13*POWER(10,-$P$2)*$P$4,$I13*$F13*$P$4/100/360)*$H13)</f>
+        <f>IF(OR($E13=0,$H13=0),"",-IF($C13="VENTA",$P$10,$P$9)*IF($P$8=1,$E13*POWER(10,-$P$2)*$P$4,$E13*$F13*$P$4/100/360)*$H13)</f>
         <v/>
       </c>
       <c r="L13" s="9">
-        <f>IF($I13=0,"",IF($D13="COMPRA",$G13-$F13,$F13-$G13)*$I13*$P$4-N($J13)-N($K13))</f>
-        <v/>
-      </c>
-      <c r="M13" s="17">
-        <f>IF(OR($I13=0,$G13=""),"",IF(AND($D13="COMPRA",$G13&lt;$F13),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($D13="VENTA",$G13&gt;$F13),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF($E13=0,"",N($I13)-N($J13)-N($K13))</f>
+        <v/>
+      </c>
+      <c r="M13" s="20">
+        <f>IF(OR($E13=0,$G13=0),"",IF(AND($C13="COMPRA",$G13&lt;$F13),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C13="VENTA",$G13&gt;$F13),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="16">
-        <f>IFERROR(MAX(0,ROUNDDOWN($E14/($F14*$P$4*$P$5),2)),0)</f>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="9">
+        <f>IF(OR($E14=0,$G14=0),"",IF($C14="COMPRA",$G14-$F14,$F14-$G14)*$E14*$P$4)</f>
         <v/>
       </c>
       <c r="J14" s="9">
-        <f>IF($I14=0,"",$I14*$P$6*$P$4)</f>
+        <f>IF($E14=0,"",$E14*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K14" s="9">
-        <f>IF(OR($I14=0,$H14=0),"",-IF($D14="VENTA",$P$10,$P$9)*IF($P$8=1,$I14*POWER(10,-$P$2)*$P$4,$I14*$F14*$P$4/100/360)*$H14)</f>
+        <f>IF(OR($E14=0,$H14=0),"",-IF($C14="VENTA",$P$10,$P$9)*IF($P$8=1,$E14*POWER(10,-$P$2)*$P$4,$E14*$F14*$P$4/100/360)*$H14)</f>
         <v/>
       </c>
       <c r="L14" s="9">
-        <f>IF($I14=0,"",IF($D14="COMPRA",$G14-$F14,$F14-$G14)*$I14*$P$4-N($J14)-N($K14))</f>
-        <v/>
-      </c>
-      <c r="M14" s="17">
-        <f>IF(OR($I14=0,$G14=""),"",IF(AND($D14="COMPRA",$G14&lt;$F14),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($D14="VENTA",$G14&gt;$F14),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF($E14=0,"",N($I14)-N($J14)-N($K14))</f>
+        <v/>
+      </c>
+      <c r="M14" s="20">
+        <f>IF(OR($E14=0,$G14=0),"",IF(AND($C14="COMPRA",$G14&lt;$F14),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C14="VENTA",$G14&gt;$F14),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="16">
-        <f>IFERROR(MAX(0,ROUNDDOWN($E15/($F15*$P$4*$P$5),2)),0)</f>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="9">
+        <f>IF(OR($E15=0,$G15=0),"",IF($C15="COMPRA",$G15-$F15,$F15-$G15)*$E15*$P$4)</f>
         <v/>
       </c>
       <c r="J15" s="9">
-        <f>IF($I15=0,"",$I15*$P$6*$P$4)</f>
+        <f>IF($E15=0,"",$E15*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K15" s="9">
-        <f>IF(OR($I15=0,$H15=0),"",-IF($D15="VENTA",$P$10,$P$9)*IF($P$8=1,$I15*POWER(10,-$P$2)*$P$4,$I15*$F15*$P$4/100/360)*$H15)</f>
+        <f>IF(OR($E15=0,$H15=0),"",-IF($C15="VENTA",$P$10,$P$9)*IF($P$8=1,$E15*POWER(10,-$P$2)*$P$4,$E15*$F15*$P$4/100/360)*$H15)</f>
         <v/>
       </c>
       <c r="L15" s="9">
-        <f>IF($I15=0,"",IF($D15="COMPRA",$G15-$F15,$F15-$G15)*$I15*$P$4-N($J15)-N($K15))</f>
-        <v/>
-      </c>
-      <c r="M15" s="17">
-        <f>IF(OR($I15=0,$G15=""),"",IF(AND($D15="COMPRA",$G15&lt;$F15),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($D15="VENTA",$G15&gt;$F15),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF($E15=0,"",N($I15)-N($J15)-N($K15))</f>
+        <v/>
+      </c>
+      <c r="M15" s="20">
+        <f>IF(OR($E15=0,$G15=0),"",IF(AND($C15="COMPRA",$G15&lt;$F15),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C15="VENTA",$G15&gt;$F15),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="9">
+        <f>IF(OR($E16=0,$G16=0),"",IF($C16="COMPRA",$G16-$F16,$F16-$G16)*$E16*$P$4)</f>
+        <v/>
+      </c>
+      <c r="J16" s="9">
+        <f>IF($E16=0,"",$E16*$P$6*$P$4)</f>
+        <v/>
+      </c>
+      <c r="K16" s="9">
+        <f>IF(OR($E16=0,$H16=0),"",-IF($C16="VENTA",$P$10,$P$9)*IF($P$8=1,$E16*POWER(10,-$P$2)*$P$4,$E16*$F16*$P$4/100/360)*$H16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="9">
+        <f>IF($E16=0,"",N($I16)-N($J16)-N($K16))</f>
+        <v/>
+      </c>
+      <c r="M16" s="20">
+        <f>IF(OR($E16=0,$G16=0),"",IF(AND($C16="COMPRA",$G16&lt;$F16),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C16="VENTA",$G16&gt;$F16),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>TOTALES</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="19">
-        <f>SUM(E10:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="21">
-        <f>SUM(I10:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="19">
-        <f>SUM(J10:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="19">
-        <f>SUM(K10:K15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="19">
-        <f>SUM(L10:L15)</f>
-        <v/>
-      </c>
-      <c r="M16" s="20" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="I18" s="22" t="inlineStr">
+      <c r="D17" s="22">
+        <f>SUM(D11:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="23">
+        <f>SUM(E11:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="22">
+        <f>SUM(I11:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="24">
+        <f>SUM(J11:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="24">
+        <f>SUM(K11:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="24">
+        <f>SUM(L11:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="21" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>Exposición nocional total</t>
         </is>
       </c>
-      <c r="L18" s="9">
-        <f>SUMPRODUCT($I$10:$I$15,$F$10:$F$15)*$P$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="I19" s="22" t="inlineStr">
+      <c r="L19" s="9">
+        <f>SUMPRODUCT($E$11:$E$16,$F$11:$F$16)*$P$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>Margen requerido (posiciones simultáneas)</t>
         </is>
       </c>
-      <c r="L19" s="9">
-        <f>$L$18*$P$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="I20" s="22" t="inlineStr">
+      <c r="L20" s="9">
+        <f>$L$19*$P$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="I21" s="25" t="inlineStr">
         <is>
           <t>Resultado neto del periodo</t>
         </is>
       </c>
-      <c r="L20" s="9">
-        <f>$L$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="I21" s="23" t="inlineStr">
+      <c r="L21" s="9">
+        <f>$L$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="I22" s="26" t="inlineStr">
         <is>
           <t>Patrimonio final</t>
         </is>
       </c>
-      <c r="L21" s="24">
-        <f>$F$5+$L$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="C23" s="25" t="inlineStr">
-        <is>
-          <t>Especificaciones del broker al 2026-08-19 16:07 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El COSTO DE MANTENCIÓN (swap) se estima por días calendario: es exacto en periodos de semanas completas y puede quedar sobre el cargo real en periodos cortos que incluyan un fin de semana. Este simulador no incorpora stop loss.</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="26" t="n"/>
-      <c r="G23" s="26" t="n"/>
-      <c r="H23" s="26" t="n"/>
-      <c r="I23" s="26" t="n"/>
-      <c r="J23" s="26" t="n"/>
-      <c r="K23" s="26" t="n"/>
-      <c r="L23" s="26" t="n"/>
-      <c r="M23" s="26" t="n"/>
+      <c r="L22" s="27">
+        <f>$F$5+$L$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>Especificaciones del broker al 2026-08-19 21:06 hora Chile. Celdas crema: campos editables; el resto son fórmulas. VOLUMEN EN CLP y VOLUMEN EN LOTES son gemelas y se sincronizan con la macro del archivo: el importe se homologa al equivalente exacto del volumen, cuyo paso mínimo es 0,01 lotes. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="28" t="n"/>
+      <c r="J24" s="28" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="28" t="n"/>
+      <c r="M24" s="28" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="17">
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="C8:M8"/>
     <mergeCell ref="I19:K19"/>
+    <mergeCell ref="C9:I9"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="I22:K22"/>
     <mergeCell ref="C7:M7"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="C24:M24"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C23:M23"/>
-    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="J9:L9"/>
     <mergeCell ref="I21:K21"/>
     <mergeCell ref="C2:L2"/>
     <mergeCell ref="C1:L1"/>
     <mergeCell ref="I6:K6"/>
   </mergeCells>
-  <conditionalFormatting sqref="L10:L16">
+  <conditionalFormatting sqref="I11:L17">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND($L10&lt;&gt;"",$L10&lt;0)</formula>
+      <formula>AND(I11&lt;&gt;"",I11&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M10:M15">
+  <conditionalFormatting sqref="M11:M16">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>$M10&lt;&gt;""</formula>
+      <formula>$M11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L21">
+  <conditionalFormatting sqref="L22">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>$L$21&lt;$F$5</formula>
+      <formula>$L$22&lt;$F$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Instrumento no válido" error="Seleccione un instrumento de la lista." type="list">
       <formula1>Datos!$A$2:$A$26</formula1>
     </dataValidation>
-    <dataValidation sqref="D10 D11 D12 D13 D14 D15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dirección no válida" error="Seleccione COMPRA o VENTA." type="list">
+    <dataValidation sqref="C11 C12 C13 C14 C15 C16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dirección no válida" error="Seleccione COMPRA o VENTA." type="list">
       <formula1>"COMPRA,VENTA"</formula1>
     </dataValidation>
-    <dataValidation sqref="H10 H11 H12 H13 H14 H15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos de mantención de la posición (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
+    <dataValidation sqref="H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos de mantención de la posición (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>3650</formula2>
+    </dataValidation>
+    <dataValidation sqref="E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Volumen no válido" error="El volumen en lotes no puede ser negativo. El paso mínimo es 0,01." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1313,57 +1332,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>INSTRUMENTO</t>
         </is>
       </c>
-      <c r="B1" s="27" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>TICKER MT5</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>DECIMALES</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>TAMAÑO DE CONTRATO (1 lote)</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>VALOR EN CLP DE 1,0 DE PRECIO (POR LOTE)</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>MARGEN</t>
         </is>
       </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="H1" s="27" t="inlineStr">
+      <c r="H1" s="29" t="inlineStr">
         <is>
           <t>PRECIO DE REFERENCIA</t>
         </is>
       </c>
-      <c r="I1" s="27" t="inlineStr">
+      <c r="I1" s="29" t="inlineStr">
         <is>
           <t>MODO SWAP</t>
         </is>
       </c>
-      <c r="J1" s="27" t="inlineStr">
+      <c r="J1" s="29" t="inlineStr">
         <is>
           <t>SWAP COMPRA</t>
         </is>
       </c>
-      <c r="K1" s="27" t="inlineStr">
+      <c r="K1" s="29" t="inlineStr">
         <is>
           <t>SWAP VENTA</t>
         </is>
@@ -1389,14 +1408,14 @@
       <c r="E2" t="n">
         <v>100000</v>
       </c>
-      <c r="F2" s="28" t="n">
+      <c r="F2" s="30" t="n">
         <v>0.01</v>
       </c>
-      <c r="G2" s="29" t="n">
+      <c r="G2" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="29" t="n">
-        <v>922</v>
+      <c r="H2" s="31" t="n">
+        <v>921.75</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -1426,16 +1445,16 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>579262.16</v>
-      </c>
-      <c r="F3" s="28" t="n">
+        <v>577910.5600000001</v>
+      </c>
+      <c r="F3" s="30" t="n">
         <v>0.010063</v>
       </c>
-      <c r="G3" s="29" t="n">
+      <c r="G3" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="H3" s="29" t="n">
-        <v>158.168</v>
+      <c r="H3" s="31" t="n">
+        <v>158.497</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1465,16 +1484,16 @@
         <v>100000</v>
       </c>
       <c r="E4" t="n">
-        <v>92200000</v>
-      </c>
-      <c r="F4" s="28" t="n">
+        <v>92175000</v>
+      </c>
+      <c r="F4" s="30" t="n">
         <v>0.01</v>
       </c>
-      <c r="G4" s="29" t="n">
+      <c r="G4" s="31" t="n">
         <v>0.00026</v>
       </c>
-      <c r="H4" s="29" t="n">
-        <v>1.16786</v>
+      <c r="H4" s="31" t="n">
+        <v>1.16725</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1504,16 +1523,16 @@
         <v>100000</v>
       </c>
       <c r="E5" t="n">
-        <v>92200000</v>
-      </c>
-      <c r="F5" s="28" t="n">
+        <v>92175000</v>
+      </c>
+      <c r="F5" s="30" t="n">
         <v>0.01</v>
       </c>
-      <c r="G5" s="29" t="n">
+      <c r="G5" s="31" t="n">
         <v>0.0005</v>
       </c>
-      <c r="H5" s="29" t="n">
-        <v>1.36099</v>
+      <c r="H5" s="31" t="n">
+        <v>1.35983</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1543,16 +1562,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>92100</v>
-      </c>
-      <c r="F6" s="28" t="n">
+        <v>92075</v>
+      </c>
+      <c r="F6" s="30" t="n">
         <v>0.045049</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H6" s="29" t="n">
-        <v>4510.01</v>
+      <c r="H6" s="31" t="n">
+        <v>4492.74</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1582,16 +1601,16 @@
         <v>5000</v>
       </c>
       <c r="E7" t="n">
-        <v>4605000</v>
-      </c>
-      <c r="F7" s="28" t="n">
+        <v>4603750</v>
+      </c>
+      <c r="F7" s="30" t="n">
         <v>0.045049</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="31" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" s="29" t="n">
-        <v>66.40900000000001</v>
+      <c r="H7" s="31" t="n">
+        <v>66.45999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1621,16 +1640,16 @@
         <v>1000</v>
       </c>
       <c r="E8" t="n">
-        <v>921000</v>
-      </c>
-      <c r="F8" s="28" t="n">
+        <v>920750</v>
+      </c>
+      <c r="F8" s="30" t="n">
         <v>0.015016</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="H8" s="29" t="n">
-        <v>84.949</v>
+      <c r="H8" s="31" t="n">
+        <v>85.485</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1660,16 +1679,16 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>921</v>
-      </c>
-      <c r="F9" s="28" t="n">
+        <v>920.75</v>
+      </c>
+      <c r="F9" s="30" t="n">
         <v>0.015016</v>
       </c>
-      <c r="G9" s="29" t="n">
-        <v>80.98999999999999</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>68596.38</v>
+      <c r="G9" s="31" t="n">
+        <v>81.16</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>69356.39999999999</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1699,16 +1718,16 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>921</v>
-      </c>
-      <c r="F10" s="28" t="n">
+        <v>920.75</v>
+      </c>
+      <c r="F10" s="30" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="29" t="n">
-        <v>29461.38</v>
+      <c r="H10" s="31" t="n">
+        <v>29599.3</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1738,16 +1757,16 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>921</v>
-      </c>
-      <c r="F11" s="28" t="n">
+        <v>920.75</v>
+      </c>
+      <c r="F11" s="30" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="29" t="n">
-        <v>7718.53</v>
+      <c r="H11" s="31" t="n">
+        <v>7732.12</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1777,16 +1796,16 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>921</v>
-      </c>
-      <c r="F12" s="28" t="n">
+        <v>920.75</v>
+      </c>
+      <c r="F12" s="30" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="29" t="n">
-        <v>53495.51</v>
+      <c r="H12" s="31" t="n">
+        <v>53503.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -1816,15 +1835,15 @@
         <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F13" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F13" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G13" s="29" t="n">
+      <c r="G13" s="31" t="n">
         <v>0.32</v>
       </c>
-      <c r="H13" s="29" t="n">
+      <c r="H13" s="31" t="n">
         <v>316.63</v>
       </c>
       <c r="I13" t="n">
@@ -1855,15 +1874,15 @@
         <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F14" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F14" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H14" s="29" t="n">
+      <c r="H14" s="31" t="n">
         <v>483.99</v>
       </c>
       <c r="I14" t="n">
@@ -1894,15 +1913,15 @@
         <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F15" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F15" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G15" s="29" t="n">
+      <c r="G15" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="H15" s="29" t="n">
+      <c r="H15" s="31" t="n">
         <v>218.24</v>
       </c>
       <c r="I15" t="n">
@@ -1933,15 +1952,15 @@
         <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F16" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F16" s="30" t="n">
         <v>0.007508</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="31" t="n">
         <v>0.31</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H16" s="31" t="n">
         <v>266.22</v>
       </c>
       <c r="I16" t="n">
@@ -1972,15 +1991,15 @@
         <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F17" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F17" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G17" s="29" t="n">
+      <c r="G17" s="31" t="n">
         <v>0.26</v>
       </c>
-      <c r="H17" s="29" t="n">
+      <c r="H17" s="31" t="n">
         <v>467.08</v>
       </c>
       <c r="I17" t="n">
@@ -2011,15 +2030,15 @@
         <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F18" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F18" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G18" s="29" t="n">
+      <c r="G18" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="29" t="n">
+      <c r="H18" s="31" t="n">
         <v>1917.47</v>
       </c>
       <c r="I18" t="n">
@@ -2050,15 +2069,15 @@
         <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F19" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F19" s="30" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G19" s="29" t="n">
+      <c r="G19" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="H19" s="29" t="n">
+      <c r="H19" s="31" t="n">
         <v>357.55</v>
       </c>
       <c r="I19" t="n">
@@ -2089,15 +2108,15 @@
         <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F20" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F20" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="H20" s="29" t="n">
+      <c r="H20" s="31" t="n">
         <v>63.19</v>
       </c>
       <c r="I20" t="n">
@@ -2128,15 +2147,15 @@
         <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F21" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F21" s="30" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="31" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="H21" s="29" t="n">
+      <c r="H21" s="31" t="n">
         <v>1021.38</v>
       </c>
       <c r="I21" t="n">
@@ -2167,15 +2186,15 @@
         <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F22" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F22" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="31" t="n">
         <v>0.11</v>
       </c>
-      <c r="H22" s="29" t="n">
+      <c r="H22" s="31" t="n">
         <v>214.59</v>
       </c>
       <c r="I22" t="n">
@@ -2206,15 +2225,15 @@
         <v>50</v>
       </c>
       <c r="E23" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F23" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F23" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="31" t="n">
         <v>0.89</v>
       </c>
-      <c r="H23" s="29" t="n">
+      <c r="H23" s="31" t="n">
         <v>221.83</v>
       </c>
       <c r="I23" t="n">
@@ -2245,15 +2264,15 @@
         <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F24" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F24" s="30" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="H24" s="29" t="n">
+      <c r="H24" s="31" t="n">
         <v>815.77</v>
       </c>
       <c r="I24" t="n">
@@ -2284,15 +2303,15 @@
         <v>50</v>
       </c>
       <c r="E25" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F25" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F25" s="30" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G25" s="29" t="n">
+      <c r="G25" s="31" t="n">
         <v>0.21</v>
       </c>
-      <c r="H25" s="29" t="n">
+      <c r="H25" s="31" t="n">
         <v>357.22</v>
       </c>
       <c r="I25" t="n">
@@ -2323,15 +2342,15 @@
         <v>50</v>
       </c>
       <c r="E26" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F26" s="28" t="n">
+        <v>46037.5</v>
+      </c>
+      <c r="F26" s="30" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G26" s="29" t="n">
+      <c r="G26" s="31" t="n">
         <v>0.77</v>
       </c>
-      <c r="H26" s="29" t="n">
+      <c r="H26" s="31" t="n">
         <v>582.4299999999999</v>
       </c>
       <c r="I26" t="n">
@@ -2345,9 +2364,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 16:07 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:06 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00###"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.00;-0.00;&quot;&quot;"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -204,9 +205,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -701,7 +701,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Seleccione el instrumento y registre las operaciones del periodo. El volumen en pesos y el volumen en lotes son la misma magnitud: al modificar uno, el otro se ajusta.</t>
+          <t>Seleccione el instrumento y registre las operaciones del periodo. El volumen en pesos y el volumen en lotes son la misma magnitud: se escribe el importe y el volumen en lotes se ajusta.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -953,10 +953,11 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>496125</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.54</v>
+        <v>496126</v>
+      </c>
+      <c r="E11" s="17">
+        <f>IFERROR(MAX(0,ROUNDDOWN($D11/($F11*$P$4*$P$5),2)),0)</f>
+        <v/>
       </c>
       <c r="F11" s="18" t="n">
         <v>918.75</v>
@@ -995,10 +996,11 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>398072</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.43</v>
+        <v>398073</v>
+      </c>
+      <c r="E12" s="17">
+        <f>IFERROR(MAX(0,ROUNDDOWN($D12/($F12*$P$4*$P$5),2)),0)</f>
+        <v/>
       </c>
       <c r="F12" s="18" t="n">
         <v>925.75</v>
@@ -1037,10 +1039,11 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>294960</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0.32</v>
+        <v>294961</v>
+      </c>
+      <c r="E13" s="17">
+        <f>IFERROR(MAX(0,ROUNDDOWN($D13/($F13*$P$4*$P$5),2)),0)</f>
+        <v/>
       </c>
       <c r="F13" s="18" t="n">
         <v>921.75</v>
@@ -1075,7 +1078,10 @@
     <row r="14" ht="24" customHeight="1">
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="17" t="n"/>
+      <c r="E14" s="17">
+        <f>IFERROR(MAX(0,ROUNDDOWN($D14/($F14*$P$4*$P$5),2)),0)</f>
+        <v/>
+      </c>
       <c r="F14" s="18" t="n"/>
       <c r="G14" s="18" t="n"/>
       <c r="H14" s="19" t="n"/>
@@ -1103,7 +1109,10 @@
     <row r="15" ht="24" customHeight="1">
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="8" t="n"/>
-      <c r="E15" s="17" t="n"/>
+      <c r="E15" s="17">
+        <f>IFERROR(MAX(0,ROUNDDOWN($D15/($F15*$P$4*$P$5),2)),0)</f>
+        <v/>
+      </c>
       <c r="F15" s="18" t="n"/>
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="19" t="n"/>
@@ -1131,7 +1140,10 @@
     <row r="16" ht="24" customHeight="1">
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="17" t="n"/>
+      <c r="E16" s="17">
+        <f>IFERROR(MAX(0,ROUNDDOWN($D16/($F16*$P$4*$P$5),2)),0)</f>
+        <v/>
+      </c>
       <c r="F16" s="18" t="n"/>
       <c r="G16" s="18" t="n"/>
       <c r="H16" s="19" t="n"/>
@@ -1238,7 +1250,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>Especificaciones del broker al 2026-08-19 21:06 hora Chile. Celdas crema: campos editables; el resto son fórmulas. VOLUMEN EN CLP y VOLUMEN EN LOTES son gemelas y se sincronizan con la macro del archivo: el importe se homologa al equivalente exacto del volumen, cuyo paso mínimo es 0,01 lotes. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
+          <t>Especificaciones del broker al 2026-08-19 21:19 hora Chile. Celdas crema: campos editables; el resto son fórmulas. VOLUMEN EN CLP y VOLUMEN EN LOTES son la misma magnitud: se escribe el importe y el volumen se ajusta, truncado al paso de 0,01 lotes que exige MT5. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
         </is>
       </c>
       <c r="D24" s="28" t="n"/>
@@ -1288,7 +1300,7 @@
       <formula>$L$22&lt;$F$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Instrumento no válido" error="Seleccione un instrumento de la lista." type="list">
       <formula1>Datos!$A$2:$A$26</formula1>
     </dataValidation>
@@ -1298,9 +1310,6 @@
     <dataValidation sqref="H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos de mantención de la posición (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>3650</formula2>
-    </dataValidation>
-    <dataValidation sqref="E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Volumen no válido" error="El volumen en lotes no puede ser negativo. El paso mínimo es 0,01." type="decimal" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1445,7 +1454,7 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>577910.5600000001</v>
+        <v>578084.53</v>
       </c>
       <c r="F3" s="30" t="n">
         <v>0.010063</v>
@@ -1454,7 +1463,7 @@
         <v>0.04</v>
       </c>
       <c r="H3" s="31" t="n">
-        <v>158.497</v>
+        <v>158.449</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1493,7 +1502,7 @@
         <v>0.00026</v>
       </c>
       <c r="H4" s="31" t="n">
-        <v>1.16725</v>
+        <v>1.16769</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1532,7 +1541,7 @@
         <v>0.0005</v>
       </c>
       <c r="H5" s="31" t="n">
-        <v>1.35983</v>
+        <v>1.36052</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1571,7 +1580,7 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>4492.74</v>
+        <v>4497.63</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1610,7 +1619,7 @@
         <v>0.05</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>66.45999999999999</v>
+        <v>66.742</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1649,7 +1658,7 @@
         <v>0.15</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>85.485</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1685,10 +1694,10 @@
         <v>0.015016</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>81.16</v>
+        <v>80.06</v>
       </c>
       <c r="H9" s="31" t="n">
-        <v>69356.39999999999</v>
+        <v>69419.82000000001</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1727,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="31" t="n">
-        <v>29599.3</v>
+        <v>29584.69</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1766,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>7732.12</v>
+        <v>7731.99</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1805,7 +1814,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>53503.51</v>
+        <v>53514.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -2366,7 +2375,7 @@
     <row r="28">
       <c r="A28" s="32" t="inlineStr">
         <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:06 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:19 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -19,10 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00###"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.00;-0.00;&quot;&quot;"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -205,8 +204,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -222,10 +222,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -701,7 +701,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Seleccione el instrumento y registre las operaciones del periodo. El volumen en pesos y el volumen en lotes son la misma magnitud: se escribe el importe y el volumen en lotes se ajusta.</t>
+          <t>Seleccione el instrumento y registre las operaciones del periodo. El volumen en lotes y el volumen en pesos son la misma magnitud: se escribe el volumen en lotes y el importe en pesos se ajusta.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -816,7 +816,7 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="C7" s="10">
-        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(($E$11:$E$16&gt;0)*($F$11:$F$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($F$11:$F$16&gt;0)*(ABS($F$11:$F$16/$P$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($P$7,$P$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($E$11:$E$16=0))&gt;0,"⚠ Hay una operación bajo el volumen mínimo de 0,01 lotes, que requiere $"&amp;FIXED(0.01*$P$7*$P$4*$P$5,0)&amp;".",IF($L$20&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($E$11:$E$16,"&gt;0")&amp;" operación(es) sobre "&amp;$P$1&amp;". El volumen en lotes es el que se ingresa en MT5.")))))</f>
+        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($F$11:$F$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($F$11:$F$16&gt;0)*(ABS($F$11:$F$16/$P$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($P$7,$P$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(--(MOD(ROUND($D$11:$D$16*100,6),1)&lt;&gt;0))&gt;0,"⚠ Hay un volumen que no es múltiplo de 0,01 lotes, el paso mínimo de MT5.",IF($L$20&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($D$11:$D$16,"&gt;0")&amp;" operación(es) sobre "&amp;$P$1&amp;". El volumen en lotes es el que se ingresa en MT5.")))))</f>
         <v/>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
+          <t>VOLUMEN EN LOTES</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
           <t>VOLUMEN EN CLP</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>VOLUMEN EN LOTES</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -952,11 +952,11 @@
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>496126</v>
-      </c>
-      <c r="E11" s="17">
-        <f>IFERROR(MAX(0,ROUNDDOWN($D11/($F11*$P$4*$P$5),2)),0)</f>
+      <c r="D11" s="17" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E11" s="9">
+        <f>IF($D11=0,"",$D11*$F11*$P$4*$P$5)</f>
         <v/>
       </c>
       <c r="F11" s="18" t="n">
@@ -969,23 +969,23 @@
         <v>2</v>
       </c>
       <c r="I11" s="9">
-        <f>IF(OR($E11=0,$G11=0),"",IF($C11="COMPRA",$G11-$F11,$F11-$G11)*$E11*$P$4)</f>
+        <f>IF(OR($D11=0,$G11=0),"",IF($C11="COMPRA",$G11-$F11,$F11-$G11)*$D11*$P$4)</f>
         <v/>
       </c>
       <c r="J11" s="9">
-        <f>IF($E11=0,"",$E11*$P$6*$P$4)</f>
+        <f>IF($D11=0,"",$D11*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K11" s="9">
-        <f>IF(OR($E11=0,$H11=0),"",-IF($C11="VENTA",$P$10,$P$9)*IF($P$8=1,$E11*POWER(10,-$P$2)*$P$4,$E11*$F11*$P$4/100/360)*$H11)</f>
+        <f>IF(OR($D11=0,$H11=0),"",-IF($C11="VENTA",$P$10,$P$9)*IF($P$8=1,$D11*POWER(10,-$P$2)*$P$4,$D11*$F11*$P$4/100/360)*$H11)</f>
         <v/>
       </c>
       <c r="L11" s="9">
-        <f>IF($E11=0,"",N($I11)-N($J11)-N($K11))</f>
+        <f>IF($D11=0,"",N($I11)-N($J11)-N($K11))</f>
         <v/>
       </c>
       <c r="M11" s="20">
-        <f>IF(OR($E11=0,$G11=0),"",IF(AND($C11="COMPRA",$G11&lt;$F11),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C11="VENTA",$G11&gt;$F11),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D11=0,$G11=0),"",IF(AND($C11="COMPRA",$G11&lt;$F11),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C11="VENTA",$G11&gt;$F11),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
@@ -995,11 +995,11 @@
           <t>VENTA</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>398073</v>
-      </c>
-      <c r="E12" s="17">
-        <f>IFERROR(MAX(0,ROUNDDOWN($D12/($F12*$P$4*$P$5),2)),0)</f>
+      <c r="D12" s="17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E12" s="9">
+        <f>IF($D12=0,"",$D12*$F12*$P$4*$P$5)</f>
         <v/>
       </c>
       <c r="F12" s="18" t="n">
@@ -1012,23 +1012,23 @@
         <v>1</v>
       </c>
       <c r="I12" s="9">
-        <f>IF(OR($E12=0,$G12=0),"",IF($C12="COMPRA",$G12-$F12,$F12-$G12)*$E12*$P$4)</f>
+        <f>IF(OR($D12=0,$G12=0),"",IF($C12="COMPRA",$G12-$F12,$F12-$G12)*$D12*$P$4)</f>
         <v/>
       </c>
       <c r="J12" s="9">
-        <f>IF($E12=0,"",$E12*$P$6*$P$4)</f>
+        <f>IF($D12=0,"",$D12*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K12" s="9">
-        <f>IF(OR($E12=0,$H12=0),"",-IF($C12="VENTA",$P$10,$P$9)*IF($P$8=1,$E12*POWER(10,-$P$2)*$P$4,$E12*$F12*$P$4/100/360)*$H12)</f>
+        <f>IF(OR($D12=0,$H12=0),"",-IF($C12="VENTA",$P$10,$P$9)*IF($P$8=1,$D12*POWER(10,-$P$2)*$P$4,$D12*$F12*$P$4/100/360)*$H12)</f>
         <v/>
       </c>
       <c r="L12" s="9">
-        <f>IF($E12=0,"",N($I12)-N($J12)-N($K12))</f>
+        <f>IF($D12=0,"",N($I12)-N($J12)-N($K12))</f>
         <v/>
       </c>
       <c r="M12" s="20">
-        <f>IF(OR($E12=0,$G12=0),"",IF(AND($C12="COMPRA",$G12&lt;$F12),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C12="VENTA",$G12&gt;$F12),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D12=0,$G12=0),"",IF(AND($C12="COMPRA",$G12&lt;$F12),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C12="VENTA",$G12&gt;$F12),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
@@ -1038,11 +1038,11 @@
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>294961</v>
-      </c>
-      <c r="E13" s="17">
-        <f>IFERROR(MAX(0,ROUNDDOWN($D13/($F13*$P$4*$P$5),2)),0)</f>
+      <c r="D13" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E13" s="9">
+        <f>IF($D13=0,"",$D13*$F13*$P$4*$P$5)</f>
         <v/>
       </c>
       <c r="F13" s="18" t="n">
@@ -1055,116 +1055,116 @@
         <v>0</v>
       </c>
       <c r="I13" s="9">
-        <f>IF(OR($E13=0,$G13=0),"",IF($C13="COMPRA",$G13-$F13,$F13-$G13)*$E13*$P$4)</f>
+        <f>IF(OR($D13=0,$G13=0),"",IF($C13="COMPRA",$G13-$F13,$F13-$G13)*$D13*$P$4)</f>
         <v/>
       </c>
       <c r="J13" s="9">
-        <f>IF($E13=0,"",$E13*$P$6*$P$4)</f>
+        <f>IF($D13=0,"",$D13*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K13" s="9">
-        <f>IF(OR($E13=0,$H13=0),"",-IF($C13="VENTA",$P$10,$P$9)*IF($P$8=1,$E13*POWER(10,-$P$2)*$P$4,$E13*$F13*$P$4/100/360)*$H13)</f>
+        <f>IF(OR($D13=0,$H13=0),"",-IF($C13="VENTA",$P$10,$P$9)*IF($P$8=1,$D13*POWER(10,-$P$2)*$P$4,$D13*$F13*$P$4/100/360)*$H13)</f>
         <v/>
       </c>
       <c r="L13" s="9">
-        <f>IF($E13=0,"",N($I13)-N($J13)-N($K13))</f>
+        <f>IF($D13=0,"",N($I13)-N($J13)-N($K13))</f>
         <v/>
       </c>
       <c r="M13" s="20">
-        <f>IF(OR($E13=0,$G13=0),"",IF(AND($C13="COMPRA",$G13&lt;$F13),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C13="VENTA",$G13&gt;$F13),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D13=0,$G13=0),"",IF(AND($C13="COMPRA",$G13&lt;$F13),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C13="VENTA",$G13&gt;$F13),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="17">
-        <f>IFERROR(MAX(0,ROUNDDOWN($D14/($F14*$P$4*$P$5),2)),0)</f>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="9">
+        <f>IF($D14=0,"",$D14*$F14*$P$4*$P$5)</f>
         <v/>
       </c>
       <c r="F14" s="18" t="n"/>
       <c r="G14" s="18" t="n"/>
       <c r="H14" s="19" t="n"/>
       <c r="I14" s="9">
-        <f>IF(OR($E14=0,$G14=0),"",IF($C14="COMPRA",$G14-$F14,$F14-$G14)*$E14*$P$4)</f>
+        <f>IF(OR($D14=0,$G14=0),"",IF($C14="COMPRA",$G14-$F14,$F14-$G14)*$D14*$P$4)</f>
         <v/>
       </c>
       <c r="J14" s="9">
-        <f>IF($E14=0,"",$E14*$P$6*$P$4)</f>
+        <f>IF($D14=0,"",$D14*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K14" s="9">
-        <f>IF(OR($E14=0,$H14=0),"",-IF($C14="VENTA",$P$10,$P$9)*IF($P$8=1,$E14*POWER(10,-$P$2)*$P$4,$E14*$F14*$P$4/100/360)*$H14)</f>
+        <f>IF(OR($D14=0,$H14=0),"",-IF($C14="VENTA",$P$10,$P$9)*IF($P$8=1,$D14*POWER(10,-$P$2)*$P$4,$D14*$F14*$P$4/100/360)*$H14)</f>
         <v/>
       </c>
       <c r="L14" s="9">
-        <f>IF($E14=0,"",N($I14)-N($J14)-N($K14))</f>
+        <f>IF($D14=0,"",N($I14)-N($J14)-N($K14))</f>
         <v/>
       </c>
       <c r="M14" s="20">
-        <f>IF(OR($E14=0,$G14=0),"",IF(AND($C14="COMPRA",$G14&lt;$F14),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C14="VENTA",$G14&gt;$F14),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D14=0,$G14=0),"",IF(AND($C14="COMPRA",$G14&lt;$F14),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C14="VENTA",$G14&gt;$F14),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="17">
-        <f>IFERROR(MAX(0,ROUNDDOWN($D15/($F15*$P$4*$P$5),2)),0)</f>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="9">
+        <f>IF($D15=0,"",$D15*$F15*$P$4*$P$5)</f>
         <v/>
       </c>
       <c r="F15" s="18" t="n"/>
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="19" t="n"/>
       <c r="I15" s="9">
-        <f>IF(OR($E15=0,$G15=0),"",IF($C15="COMPRA",$G15-$F15,$F15-$G15)*$E15*$P$4)</f>
+        <f>IF(OR($D15=0,$G15=0),"",IF($C15="COMPRA",$G15-$F15,$F15-$G15)*$D15*$P$4)</f>
         <v/>
       </c>
       <c r="J15" s="9">
-        <f>IF($E15=0,"",$E15*$P$6*$P$4)</f>
+        <f>IF($D15=0,"",$D15*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K15" s="9">
-        <f>IF(OR($E15=0,$H15=0),"",-IF($C15="VENTA",$P$10,$P$9)*IF($P$8=1,$E15*POWER(10,-$P$2)*$P$4,$E15*$F15*$P$4/100/360)*$H15)</f>
+        <f>IF(OR($D15=0,$H15=0),"",-IF($C15="VENTA",$P$10,$P$9)*IF($P$8=1,$D15*POWER(10,-$P$2)*$P$4,$D15*$F15*$P$4/100/360)*$H15)</f>
         <v/>
       </c>
       <c r="L15" s="9">
-        <f>IF($E15=0,"",N($I15)-N($J15)-N($K15))</f>
+        <f>IF($D15=0,"",N($I15)-N($J15)-N($K15))</f>
         <v/>
       </c>
       <c r="M15" s="20">
-        <f>IF(OR($E15=0,$G15=0),"",IF(AND($C15="COMPRA",$G15&lt;$F15),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C15="VENTA",$G15&gt;$F15),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D15=0,$G15=0),"",IF(AND($C15="COMPRA",$G15&lt;$F15),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C15="VENTA",$G15&gt;$F15),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="17">
-        <f>IFERROR(MAX(0,ROUNDDOWN($D16/($F16*$P$4*$P$5),2)),0)</f>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="9">
+        <f>IF($D16=0,"",$D16*$F16*$P$4*$P$5)</f>
         <v/>
       </c>
       <c r="F16" s="18" t="n"/>
       <c r="G16" s="18" t="n"/>
       <c r="H16" s="19" t="n"/>
       <c r="I16" s="9">
-        <f>IF(OR($E16=0,$G16=0),"",IF($C16="COMPRA",$G16-$F16,$F16-$G16)*$E16*$P$4)</f>
+        <f>IF(OR($D16=0,$G16=0),"",IF($C16="COMPRA",$G16-$F16,$F16-$G16)*$D16*$P$4)</f>
         <v/>
       </c>
       <c r="J16" s="9">
-        <f>IF($E16=0,"",$E16*$P$6*$P$4)</f>
+        <f>IF($D16=0,"",$D16*$P$6*$P$4)</f>
         <v/>
       </c>
       <c r="K16" s="9">
-        <f>IF(OR($E16=0,$H16=0),"",-IF($C16="VENTA",$P$10,$P$9)*IF($P$8=1,$E16*POWER(10,-$P$2)*$P$4,$E16*$F16*$P$4/100/360)*$H16)</f>
+        <f>IF(OR($D16=0,$H16=0),"",-IF($C16="VENTA",$P$10,$P$9)*IF($P$8=1,$D16*POWER(10,-$P$2)*$P$4,$D16*$F16*$P$4/100/360)*$H16)</f>
         <v/>
       </c>
       <c r="L16" s="9">
-        <f>IF($E16=0,"",N($I16)-N($J16)-N($K16))</f>
+        <f>IF($D16=0,"",N($I16)-N($J16)-N($K16))</f>
         <v/>
       </c>
       <c r="M16" s="20">
-        <f>IF(OR($E16=0,$G16=0),"",IF(AND($C16="COMPRA",$G16&lt;$F16),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C16="VENTA",$G16&gt;$F16),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D16=0,$G16=0),"",IF(AND($C16="COMPRA",$G16&lt;$F16),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C16="VENTA",$G16&gt;$F16),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       <c r="F17" s="21" t="n"/>
       <c r="G17" s="21" t="n"/>
       <c r="H17" s="21" t="n"/>
-      <c r="I17" s="22">
+      <c r="I17" s="23">
         <f>SUM(I11:I16)</f>
         <v/>
       </c>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="L19" s="9">
-        <f>SUMPRODUCT($E$11:$E$16,$F$11:$F$16)*$P$4</f>
+        <f>SUMPRODUCT($D$11:$D$16,$F$11:$F$16)*$P$4</f>
         <v/>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>Especificaciones del broker al 2026-08-19 21:19 hora Chile. Celdas crema: campos editables; el resto son fórmulas. VOLUMEN EN CLP y VOLUMEN EN LOTES son la misma magnitud: se escribe el importe y el volumen se ajusta, truncado al paso de 0,01 lotes que exige MT5. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
+          <t>Especificaciones del broker al 2026-08-19 21:26 hora Chile. Celdas crema: campos editables; el resto son fórmulas. VOLUMEN EN LOTES y VOLUMEN EN CLP son la misma magnitud: se escribe el volumen en lotes, en múltiplos de 0,01, y el importe en pesos se ajusta. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
         </is>
       </c>
       <c r="D24" s="28" t="n"/>
@@ -1300,12 +1300,15 @@
       <formula>$L$22&lt;$F$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Instrumento no válido" error="Seleccione un instrumento de la lista." type="list">
       <formula1>Datos!$A$2:$A$26</formula1>
     </dataValidation>
     <dataValidation sqref="C11 C12 C13 C14 C15 C16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dirección no válida" error="Seleccione COMPRA o VENTA." type="list">
       <formula1>"COMPRA,VENTA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D11 D12 D13 D14 D15 D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Volumen no válido" error="El volumen mínimo que acepta MT5 es 0,01 lotes, y debe ser múltiplo de 0,01." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.01</formula1>
     </dataValidation>
     <dataValidation sqref="H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos de mantención de la posición (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
       <formula1>0</formula1>
@@ -1454,7 +1457,7 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>578084.53</v>
+        <v>578102.66</v>
       </c>
       <c r="F3" s="30" t="n">
         <v>0.010063</v>
@@ -1463,7 +1466,7 @@
         <v>0.04</v>
       </c>
       <c r="H3" s="31" t="n">
-        <v>158.449</v>
+        <v>158.444</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1502,7 +1505,7 @@
         <v>0.00026</v>
       </c>
       <c r="H4" s="31" t="n">
-        <v>1.16769</v>
+        <v>1.16785</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1541,7 +1544,7 @@
         <v>0.0005</v>
       </c>
       <c r="H5" s="31" t="n">
-        <v>1.36052</v>
+        <v>1.36057</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1580,7 +1583,7 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>4497.63</v>
+        <v>4498.24</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1619,7 +1622,7 @@
         <v>0.05</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>66.742</v>
+        <v>66.761</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1658,7 +1661,7 @@
         <v>0.15</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1694,10 +1697,10 @@
         <v>0.015016</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>80.06</v>
+        <v>79.27</v>
       </c>
       <c r="H9" s="31" t="n">
-        <v>69419.82000000001</v>
+        <v>69364.77</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1736,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="31" t="n">
-        <v>29584.69</v>
+        <v>29571.09</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1775,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>7731.99</v>
+        <v>7729.75</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1814,7 +1817,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>53514.51</v>
+        <v>53506.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -2375,7 +2378,7 @@
     <row r="28">
       <c r="A28" s="32" t="inlineStr">
         <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:19 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:26 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -816,7 +816,7 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="C7" s="10">
-        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($F$11:$F$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($F$11:$F$16&gt;0)*(ABS($F$11:$F$16/$P$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($P$7,$P$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(--(MOD(ROUND($D$11:$D$16*100,6),1)&lt;&gt;0))&gt;0,"⚠ Hay un volumen que no es múltiplo de 0,01 lotes, el paso mínimo de MT5.",IF($L$20&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($D$11:$D$16,"&gt;0")&amp;" operación(es) sobre "&amp;$P$1&amp;". El volumen en lotes es el que se ingresa en MT5.")))))</f>
+        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(--ISTEXT($D$11:$D$16))+SUMPRODUCT(--ISTEXT($F$11:$G$16))+SUMPRODUCT(--ISTEXT($H$11:$H$16))&gt;0,"⚠ Hay un valor escrito como texto. El separador decimal de este Excel es la coma: escriba 0,54 y no 0.54.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($F$11:$F$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($F$11:$F$16&gt;0)*(ABS($F$11:$F$16/$P$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($P$7,$P$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(--(MOD(ROUND($D$11:$D$16*100,6),1)&lt;&gt;0))&gt;0,"⚠ Hay un volumen que no es múltiplo de 0,01 lotes, el paso mínimo de MT5.",IF($L$20&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($D$11:$D$16,"&gt;0")&amp;" operación(es) sobre "&amp;$P$1&amp;". El volumen en lotes es el que se ingresa en MT5."))))))</f>
         <v/>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -1250,7 +1250,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>Especificaciones del broker al 2026-08-19 21:26 hora Chile. Celdas crema: campos editables; el resto son fórmulas. VOLUMEN EN LOTES y VOLUMEN EN CLP son la misma magnitud: se escribe el volumen en lotes, en múltiplos de 0,01, y el importe en pesos se ajusta. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
+          <t>Especificaciones del broker al 2026-08-19 21:32 hora Chile. Celdas crema: campos editables; el resto son fórmulas. VOLUMEN EN LOTES y VOLUMEN EN CLP son la misma magnitud: se escribe el volumen en lotes, en múltiplos de 0,01, y el importe en pesos se ajusta. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
         </is>
       </c>
       <c r="D24" s="28" t="n"/>
@@ -1300,19 +1300,25 @@
       <formula>$L$22&lt;$F$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="6">
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Instrumento no válido" error="Seleccione un instrumento de la lista." type="list">
       <formula1>Datos!$A$2:$A$26</formula1>
     </dataValidation>
     <dataValidation sqref="C11 C12 C13 C14 C15 C16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dirección no válida" error="Seleccione COMPRA o VENTA." type="list">
       <formula1>"COMPRA,VENTA"</formula1>
     </dataValidation>
-    <dataValidation sqref="D11 D12 D13 D14 D15 D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Volumen no válido" error="El volumen mínimo que acepta MT5 es 0,01 lotes, y debe ser múltiplo de 0,01." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="D11 D12 D13 D14 D15 D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Volumen no válido" error="El volumen mínimo que acepta MT5 es 0,01 lotes, en múltiplos de 0,01. Use la coma como separador decimal: 0,54 y no 0.54." type="decimal" operator="greaterThanOrEqual">
       <formula1>0.01</formula1>
+    </dataValidation>
+    <dataValidation sqref="F11 F12 F13 F14 F15 F16 G11 G12 G13 G14 G15 G16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Precio no válido" error="Escriba un precio numérico, con la coma como separador decimal: 918,75 y no 918.75." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos de mantención de la posición (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>3650</formula2>
+    </dataValidation>
+    <dataValidation sqref="F5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Capital no válido" error="Escriba el capital de la cuenta en pesos, sin separador decimal." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1457,7 +1463,7 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>578102.66</v>
+        <v>578345.6800000001</v>
       </c>
       <c r="F3" s="30" t="n">
         <v>0.010063</v>
@@ -1466,7 +1472,7 @@
         <v>0.04</v>
       </c>
       <c r="H3" s="31" t="n">
-        <v>158.444</v>
+        <v>158.377</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1505,7 +1511,7 @@
         <v>0.00026</v>
       </c>
       <c r="H4" s="31" t="n">
-        <v>1.16785</v>
+        <v>1.16811</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1544,7 +1550,7 @@
         <v>0.0005</v>
       </c>
       <c r="H5" s="31" t="n">
-        <v>1.36057</v>
+        <v>1.36076</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1583,7 +1589,7 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>4498.24</v>
+        <v>4499.08</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1622,7 +1628,7 @@
         <v>0.05</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>66.761</v>
+        <v>66.92100000000001</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1661,7 +1667,7 @@
         <v>0.15</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>85.39</v>
+        <v>85.245</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1697,10 +1703,10 @@
         <v>0.015016</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>79.27</v>
+        <v>81.05</v>
       </c>
       <c r="H9" s="31" t="n">
-        <v>69364.77</v>
+        <v>69367.2</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1739,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="31" t="n">
-        <v>29571.09</v>
+        <v>29567.47</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1778,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>7729.75</v>
+        <v>7729.25</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1817,7 +1823,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>53506.51</v>
+        <v>53515.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -2378,7 +2384,7 @@
     <row r="28">
       <c r="A28" s="32" t="inlineStr">
         <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:26 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:32 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -701,7 +701,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Seleccione el instrumento y registre las operaciones del periodo. El volumen en lotes y el volumen en pesos son la misma magnitud: se escribe el volumen en lotes y el importe en pesos se ajusta.</t>
+          <t>Seleccione el instrumento y registre las operaciones del periodo. Se escribe el volumen en lotes, la unidad del terminal, y la planilla calcula el margen que bloquea y los costos que descuenta.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>VOLUMEN EN CLP</t>
+          <t>MARGEN REQUERIDO</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>DÍAS DE MANTENCIÓN</t>
+          <t>DÍAS ABIERTA</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
@@ -1250,7 +1250,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>Especificaciones del broker al 2026-08-19 21:32 hora Chile. Celdas crema: campos editables; el resto son fórmulas. VOLUMEN EN LOTES y VOLUMEN EN CLP son la misma magnitud: se escribe el volumen en lotes, en múltiplos de 0,01, y el importe en pesos se ajusta. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
+          <t>Especificaciones del broker al 2026-08-19 21:38 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos de 0,01, el paso que acepta MT5, y el MARGEN REQUERIDO se ajusta con él. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
         </is>
       </c>
       <c r="D24" s="28" t="n"/>
@@ -1313,7 +1313,7 @@
     <dataValidation sqref="F11 F12 F13 F14 F15 F16 G11 G12 G13 G14 G15 G16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Precio no válido" error="Escriba un precio numérico, con la coma como separador decimal: 918,75 y no 918.75." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos de mantención de la posición (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
+    <dataValidation sqref="H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos que la posición queda abierta (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>3650</formula2>
     </dataValidation>
@@ -1463,7 +1463,7 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>578345.6800000001</v>
+        <v>578222.33</v>
       </c>
       <c r="F3" s="30" t="n">
         <v>0.010063</v>
@@ -1472,7 +1472,7 @@
         <v>0.04</v>
       </c>
       <c r="H3" s="31" t="n">
-        <v>158.377</v>
+        <v>158.411</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1511,7 +1511,7 @@
         <v>0.00026</v>
       </c>
       <c r="H4" s="31" t="n">
-        <v>1.16811</v>
+        <v>1.16822</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1550,7 +1550,7 @@
         <v>0.0005</v>
       </c>
       <c r="H5" s="31" t="n">
-        <v>1.36076</v>
+        <v>1.36094</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1589,7 +1589,7 @@
         <v>0.6</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>4499.08</v>
+        <v>4497.8</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1628,7 +1628,7 @@
         <v>0.05</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>66.92100000000001</v>
+        <v>66.833</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1667,7 +1667,7 @@
         <v>0.15</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>85.245</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1703,10 +1703,10 @@
         <v>0.015016</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>81.05</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="H9" s="31" t="n">
-        <v>69367.2</v>
+        <v>69543.8</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1745,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="31" t="n">
-        <v>29567.47</v>
+        <v>29571.58</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>7729.25</v>
+        <v>7728.74</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1823,7 +1823,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>53515.51</v>
+        <v>53507.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -2384,7 +2384,7 @@
     <row r="28">
       <c r="A28" s="32" t="inlineStr">
         <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:32 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:38 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Simulador'!$B$1:$N$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Simulador'!$B$1:$O$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,9 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00###"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot; veces&quot;"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -156,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -208,6 +210,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -228,11 +233,17 @@
     <xf numFmtId="165" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -337,7 +348,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
@@ -652,25 +663,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C1:P24"/>
+  <dimension ref="C1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="3" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
-    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -688,20 +700,21 @@
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
-      <c r="O1" t="inlineStr">
+      <c r="M1" s="1" t="n"/>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="P1">
+      <c r="R1">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,2,FALSE),0)</f>
         <v/>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Seleccione el instrumento y registre las operaciones del periodo. Se escribe el volumen en lotes, la unidad del terminal, y la planilla calcula el margen que bloquea y los costos que descuenta.</t>
+          <t>Se escribe el volumen en lotes, la unidad del terminal. La planilla calcula el margen que bloquea, el apalancamiento y los costos.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -713,23 +726,24 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" s="2" t="n"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>digits</t>
         </is>
       </c>
-      <c r="P2">
+      <c r="R2">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,3,FALSE),0)</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>contrato</t>
         </is>
       </c>
-      <c r="P3">
+      <c r="R3">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,4,FALSE),0)</f>
         <v/>
       </c>
@@ -746,21 +760,21 @@
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Precio de referencia</t>
         </is>
       </c>
-      <c r="L4" s="7">
-        <f>$P$7</f>
-        <v/>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="M4" s="7">
+        <f>$R$7</f>
+        <v/>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>clp_unidad</t>
         </is>
       </c>
-      <c r="P4">
+      <c r="R4">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,5,FALSE),0)</f>
         <v/>
       </c>
@@ -775,48 +789,48 @@
         <v>2000000</v>
       </c>
       <c r="G5" s="5" t="n"/>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Capital mínimo por operación (0,01 lotes)</t>
         </is>
       </c>
-      <c r="L5" s="9">
-        <f>0.01*$P$7*$P$4*$P$5</f>
-        <v/>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="M5" s="9">
+        <f>0.01*$R$7*$R$4*$R$5</f>
+        <v/>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>tasa</t>
         </is>
       </c>
-      <c r="P5">
+      <c r="R5">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,6,FALSE),0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Spread vigente al generar</t>
         </is>
       </c>
-      <c r="L6" s="7">
-        <f>$P$6</f>
-        <v/>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M6" s="7">
+        <f>$R$6</f>
+        <v/>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>spread</t>
         </is>
       </c>
-      <c r="P6">
+      <c r="R6">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,7,FALSE),0)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="C7" s="10">
-        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(--ISTEXT($D$11:$D$16))+SUMPRODUCT(--ISTEXT($F$11:$G$16))+SUMPRODUCT(--ISTEXT($H$11:$H$16))&gt;0,"⚠ Hay un valor escrito como texto. El separador decimal de este Excel es la coma: escriba 0,54 y no 0.54.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($F$11:$F$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($F$11:$F$16&gt;0)*(ABS($F$11:$F$16/$P$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($P$7,$P$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(--(MOD(ROUND($D$11:$D$16*100,6),1)&lt;&gt;0))&gt;0,"⚠ Hay un volumen que no es múltiplo de 0,01 lotes, el paso mínimo de MT5.",IF($L$20&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($D$11:$D$16,"&gt;0")&amp;" operación(es) sobre "&amp;$P$1&amp;". El volumen en lotes es el que se ingresa en MT5."))))))</f>
+        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(--ISTEXT($D$11:$D$16))+SUMPRODUCT(--ISTEXT($G$11:$H$16))+SUMPRODUCT(--ISTEXT($I$11:$I$16))&gt;0,"⚠ Hay un valor escrito como texto. El separador decimal de este Excel es la coma: escriba 0,54 y no 0.54.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($G$11:$G$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($G$11:$G$16&gt;0)*(ABS($G$11:$G$16/$R$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($R$7,$R$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(--(MOD(ROUND($D$11:$D$16*100,6),1)&lt;&gt;0))&gt;0,"⚠ Hay un volumen que no es múltiplo de 0,01 lotes, el paso mínimo de MT5.",IF($M$21&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($D$11:$D$16,"&gt;0")&amp;" operación(es) sobre "&amp;$R$1&amp;". El volumen en lotes es el que se ingresa en MT5."))))))</f>
         <v/>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -829,23 +843,24 @@
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
-      <c r="O7" t="inlineStr">
+      <c r="N7" s="11" t="n"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>precio_ref</t>
         </is>
       </c>
-      <c r="P7">
+      <c r="R7">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>swap_modo</t>
         </is>
       </c>
-      <c r="P8">
+      <c r="R8">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,9,FALSE),0)</f>
         <v/>
       </c>
@@ -862,20 +877,21 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>COSTOS</t>
         </is>
       </c>
-      <c r="K9" s="13" t="n"/>
       <c r="L9" s="13" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>swap_compra</t>
         </is>
       </c>
-      <c r="P9">
+      <c r="R9">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,10,FALSE),0)</f>
         <v/>
       </c>
@@ -898,50 +914,55 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
+          <t>APALANCAMIENTO (VECES)</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
           <t>PRECIO DE ENTRADA</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>PRECIO DE SALIDA</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>DÍAS ABIERTA</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>RESULTADO BRUTO</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>COSTO DE APERTURA (SPREAD)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="L10" s="16" t="inlineStr">
         <is>
           <t>COSTO DE MANTENCIÓN (SWAP)</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="M10" s="16" t="inlineStr">
         <is>
           <t>RESULTADO NETO</t>
         </is>
       </c>
-      <c r="M10" s="15" t="inlineStr">
+      <c r="N10" s="15" t="inlineStr">
         <is>
           <t>OBSERVACIÓN</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>swap_venta</t>
         </is>
       </c>
-      <c r="P10">
+      <c r="R10">
         <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,11,FALSE),0)</f>
         <v/>
       </c>
@@ -956,36 +977,40 @@
         <v>0.54</v>
       </c>
       <c r="E11" s="9">
-        <f>IF($D11=0,"",$D11*$F11*$P$4*$P$5)</f>
-        <v/>
-      </c>
-      <c r="F11" s="18" t="n">
+        <f>IF($D11=0,"",$D11*$G11*$R$4*$R$5)</f>
+        <v/>
+      </c>
+      <c r="F11" s="18">
+        <f>IF(OR($D11=0,$F$5=0),"",$D11*$G11*$R$4/$F$5)</f>
+        <v/>
+      </c>
+      <c r="G11" s="19" t="n">
         <v>918.75</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <v>923.75</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="I11" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="9">
-        <f>IF(OR($D11=0,$G11=0),"",IF($C11="COMPRA",$G11-$F11,$F11-$G11)*$D11*$P$4)</f>
-        <v/>
-      </c>
       <c r="J11" s="9">
-        <f>IF($D11=0,"",$D11*$P$6*$P$4)</f>
+        <f>IF(OR($D11=0,$H11=0),"",IF($C11="COMPRA",$H11-$G11,$G11-$H11)*$D11*$R$4)</f>
         <v/>
       </c>
       <c r="K11" s="9">
-        <f>IF(OR($D11=0,$H11=0),"",-IF($C11="VENTA",$P$10,$P$9)*IF($P$8=1,$D11*POWER(10,-$P$2)*$P$4,$D11*$F11*$P$4/100/360)*$H11)</f>
+        <f>IF($D11=0,"",$D11*$R$6*$R$4)</f>
         <v/>
       </c>
       <c r="L11" s="9">
-        <f>IF($D11=0,"",N($I11)-N($J11)-N($K11))</f>
-        <v/>
-      </c>
-      <c r="M11" s="20">
-        <f>IF(OR($D11=0,$G11=0),"",IF(AND($C11="COMPRA",$G11&lt;$F11),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C11="VENTA",$G11&gt;$F11),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D11=0,$I11=0),"",-IF($C11="VENTA",$R$10,$R$9)*IF($R$8=1,$D11*POWER(10,-$R$2)*$R$4,$D11*$G11*$R$4/100/360)*$I11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="9">
+        <f>IF($D11=0,"",N($J11)-N($K11)-N($L11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="21">
+        <f>IF(OR($D11=0,$H11=0),"",IF(AND($C11="COMPRA",$H11&lt;$G11),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C11="VENTA",$H11&gt;$G11),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
@@ -999,36 +1024,40 @@
         <v>0.43</v>
       </c>
       <c r="E12" s="9">
-        <f>IF($D12=0,"",$D12*$F12*$P$4*$P$5)</f>
-        <v/>
-      </c>
-      <c r="F12" s="18" t="n">
+        <f>IF($D12=0,"",$D12*$G12*$R$4*$R$5)</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>IF(OR($D12=0,$F$5=0),"",$D12*$G12*$R$4/$F$5)</f>
+        <v/>
+      </c>
+      <c r="G12" s="19" t="n">
         <v>925.75</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>922.75</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="I12" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="9">
-        <f>IF(OR($D12=0,$G12=0),"",IF($C12="COMPRA",$G12-$F12,$F12-$G12)*$D12*$P$4)</f>
-        <v/>
-      </c>
       <c r="J12" s="9">
-        <f>IF($D12=0,"",$D12*$P$6*$P$4)</f>
+        <f>IF(OR($D12=0,$H12=0),"",IF($C12="COMPRA",$H12-$G12,$G12-$H12)*$D12*$R$4)</f>
         <v/>
       </c>
       <c r="K12" s="9">
-        <f>IF(OR($D12=0,$H12=0),"",-IF($C12="VENTA",$P$10,$P$9)*IF($P$8=1,$D12*POWER(10,-$P$2)*$P$4,$D12*$F12*$P$4/100/360)*$H12)</f>
+        <f>IF($D12=0,"",$D12*$R$6*$R$4)</f>
         <v/>
       </c>
       <c r="L12" s="9">
-        <f>IF($D12=0,"",N($I12)-N($J12)-N($K12))</f>
-        <v/>
-      </c>
-      <c r="M12" s="20">
-        <f>IF(OR($D12=0,$G12=0),"",IF(AND($C12="COMPRA",$G12&lt;$F12),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C12="VENTA",$G12&gt;$F12),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D12=0,$I12=0),"",-IF($C12="VENTA",$R$10,$R$9)*IF($R$8=1,$D12*POWER(10,-$R$2)*$R$4,$D12*$G12*$R$4/100/360)*$I12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="9">
+        <f>IF($D12=0,"",N($J12)-N($K12)-N($L12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="21">
+        <f>IF(OR($D12=0,$H12=0),"",IF(AND($C12="COMPRA",$H12&lt;$G12),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C12="VENTA",$H12&gt;$G12),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
@@ -1042,36 +1071,40 @@
         <v>0.32</v>
       </c>
       <c r="E13" s="9">
-        <f>IF($D13=0,"",$D13*$F13*$P$4*$P$5)</f>
-        <v/>
-      </c>
-      <c r="F13" s="18" t="n">
+        <f>IF($D13=0,"",$D13*$G13*$R$4*$R$5)</f>
+        <v/>
+      </c>
+      <c r="F13" s="18">
+        <f>IF(OR($D13=0,$F$5=0),"",$D13*$G13*$R$4/$F$5)</f>
+        <v/>
+      </c>
+      <c r="G13" s="19" t="n">
         <v>921.75</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <v>920.25</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="I13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="9">
-        <f>IF(OR($D13=0,$G13=0),"",IF($C13="COMPRA",$G13-$F13,$F13-$G13)*$D13*$P$4)</f>
-        <v/>
-      </c>
       <c r="J13" s="9">
-        <f>IF($D13=0,"",$D13*$P$6*$P$4)</f>
+        <f>IF(OR($D13=0,$H13=0),"",IF($C13="COMPRA",$H13-$G13,$G13-$H13)*$D13*$R$4)</f>
         <v/>
       </c>
       <c r="K13" s="9">
-        <f>IF(OR($D13=0,$H13=0),"",-IF($C13="VENTA",$P$10,$P$9)*IF($P$8=1,$D13*POWER(10,-$P$2)*$P$4,$D13*$F13*$P$4/100/360)*$H13)</f>
+        <f>IF($D13=0,"",$D13*$R$6*$R$4)</f>
         <v/>
       </c>
       <c r="L13" s="9">
-        <f>IF($D13=0,"",N($I13)-N($J13)-N($K13))</f>
-        <v/>
-      </c>
-      <c r="M13" s="20">
-        <f>IF(OR($D13=0,$G13=0),"",IF(AND($C13="COMPRA",$G13&lt;$F13),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C13="VENTA",$G13&gt;$F13),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D13=0,$I13=0),"",-IF($C13="VENTA",$R$10,$R$9)*IF($R$8=1,$D13*POWER(10,-$R$2)*$R$4,$D13*$G13*$R$4/100/360)*$I13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="9">
+        <f>IF($D13=0,"",N($J13)-N($K13)-N($L13))</f>
+        <v/>
+      </c>
+      <c r="N13" s="21">
+        <f>IF(OR($D13=0,$H13=0),"",IF(AND($C13="COMPRA",$H13&lt;$G13),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C13="VENTA",$H13&gt;$G13),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
@@ -1079,30 +1112,34 @@
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="17" t="n"/>
       <c r="E14" s="9">
-        <f>IF($D14=0,"",$D14*$F14*$P$4*$P$5)</f>
-        <v/>
-      </c>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
+        <f>IF($D14=0,"",$D14*$G14*$R$4*$R$5)</f>
+        <v/>
+      </c>
+      <c r="F14" s="18">
+        <f>IF(OR($D14=0,$F$5=0),"",$D14*$G14*$R$4/$F$5)</f>
+        <v/>
+      </c>
+      <c r="G14" s="19" t="n"/>
       <c r="H14" s="19" t="n"/>
-      <c r="I14" s="9">
-        <f>IF(OR($D14=0,$G14=0),"",IF($C14="COMPRA",$G14-$F14,$F14-$G14)*$D14*$P$4)</f>
-        <v/>
-      </c>
+      <c r="I14" s="20" t="n"/>
       <c r="J14" s="9">
-        <f>IF($D14=0,"",$D14*$P$6*$P$4)</f>
+        <f>IF(OR($D14=0,$H14=0),"",IF($C14="COMPRA",$H14-$G14,$G14-$H14)*$D14*$R$4)</f>
         <v/>
       </c>
       <c r="K14" s="9">
-        <f>IF(OR($D14=0,$H14=0),"",-IF($C14="VENTA",$P$10,$P$9)*IF($P$8=1,$D14*POWER(10,-$P$2)*$P$4,$D14*$F14*$P$4/100/360)*$H14)</f>
+        <f>IF($D14=0,"",$D14*$R$6*$R$4)</f>
         <v/>
       </c>
       <c r="L14" s="9">
-        <f>IF($D14=0,"",N($I14)-N($J14)-N($K14))</f>
-        <v/>
-      </c>
-      <c r="M14" s="20">
-        <f>IF(OR($D14=0,$G14=0),"",IF(AND($C14="COMPRA",$G14&lt;$F14),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C14="VENTA",$G14&gt;$F14),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D14=0,$I14=0),"",-IF($C14="VENTA",$R$10,$R$9)*IF($R$8=1,$D14*POWER(10,-$R$2)*$R$4,$D14*$G14*$R$4/100/360)*$I14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="9">
+        <f>IF($D14=0,"",N($J14)-N($K14)-N($L14))</f>
+        <v/>
+      </c>
+      <c r="N14" s="21">
+        <f>IF(OR($D14=0,$H14=0),"",IF(AND($C14="COMPRA",$H14&lt;$G14),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C14="VENTA",$H14&gt;$G14),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
@@ -1110,30 +1147,34 @@
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="17" t="n"/>
       <c r="E15" s="9">
-        <f>IF($D15=0,"",$D15*$F15*$P$4*$P$5)</f>
-        <v/>
-      </c>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
+        <f>IF($D15=0,"",$D15*$G15*$R$4*$R$5)</f>
+        <v/>
+      </c>
+      <c r="F15" s="18">
+        <f>IF(OR($D15=0,$F$5=0),"",$D15*$G15*$R$4/$F$5)</f>
+        <v/>
+      </c>
+      <c r="G15" s="19" t="n"/>
       <c r="H15" s="19" t="n"/>
-      <c r="I15" s="9">
-        <f>IF(OR($D15=0,$G15=0),"",IF($C15="COMPRA",$G15-$F15,$F15-$G15)*$D15*$P$4)</f>
-        <v/>
-      </c>
+      <c r="I15" s="20" t="n"/>
       <c r="J15" s="9">
-        <f>IF($D15=0,"",$D15*$P$6*$P$4)</f>
+        <f>IF(OR($D15=0,$H15=0),"",IF($C15="COMPRA",$H15-$G15,$G15-$H15)*$D15*$R$4)</f>
         <v/>
       </c>
       <c r="K15" s="9">
-        <f>IF(OR($D15=0,$H15=0),"",-IF($C15="VENTA",$P$10,$P$9)*IF($P$8=1,$D15*POWER(10,-$P$2)*$P$4,$D15*$F15*$P$4/100/360)*$H15)</f>
+        <f>IF($D15=0,"",$D15*$R$6*$R$4)</f>
         <v/>
       </c>
       <c r="L15" s="9">
-        <f>IF($D15=0,"",N($I15)-N($J15)-N($K15))</f>
-        <v/>
-      </c>
-      <c r="M15" s="20">
-        <f>IF(OR($D15=0,$G15=0),"",IF(AND($C15="COMPRA",$G15&lt;$F15),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C15="VENTA",$G15&gt;$F15),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D15=0,$I15=0),"",-IF($C15="VENTA",$R$10,$R$9)*IF($R$8=1,$D15*POWER(10,-$R$2)*$R$4,$D15*$G15*$R$4/100/360)*$I15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="9">
+        <f>IF($D15=0,"",N($J15)-N($K15)-N($L15))</f>
+        <v/>
+      </c>
+      <c r="N15" s="21">
+        <f>IF(OR($D15=0,$H15=0),"",IF(AND($C15="COMPRA",$H15&lt;$G15),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C15="VENTA",$H15&gt;$G15),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
@@ -1141,163 +1182,184 @@
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="17" t="n"/>
       <c r="E16" s="9">
-        <f>IF($D16=0,"",$D16*$F16*$P$4*$P$5)</f>
-        <v/>
-      </c>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
+        <f>IF($D16=0,"",$D16*$G16*$R$4*$R$5)</f>
+        <v/>
+      </c>
+      <c r="F16" s="18">
+        <f>IF(OR($D16=0,$F$5=0),"",$D16*$G16*$R$4/$F$5)</f>
+        <v/>
+      </c>
+      <c r="G16" s="19" t="n"/>
       <c r="H16" s="19" t="n"/>
-      <c r="I16" s="9">
-        <f>IF(OR($D16=0,$G16=0),"",IF($C16="COMPRA",$G16-$F16,$F16-$G16)*$D16*$P$4)</f>
-        <v/>
-      </c>
+      <c r="I16" s="20" t="n"/>
       <c r="J16" s="9">
-        <f>IF($D16=0,"",$D16*$P$6*$P$4)</f>
+        <f>IF(OR($D16=0,$H16=0),"",IF($C16="COMPRA",$H16-$G16,$G16-$H16)*$D16*$R$4)</f>
         <v/>
       </c>
       <c r="K16" s="9">
-        <f>IF(OR($D16=0,$H16=0),"",-IF($C16="VENTA",$P$10,$P$9)*IF($P$8=1,$D16*POWER(10,-$P$2)*$P$4,$D16*$F16*$P$4/100/360)*$H16)</f>
+        <f>IF($D16=0,"",$D16*$R$6*$R$4)</f>
         <v/>
       </c>
       <c r="L16" s="9">
-        <f>IF($D16=0,"",N($I16)-N($J16)-N($K16))</f>
-        <v/>
-      </c>
-      <c r="M16" s="20">
-        <f>IF(OR($D16=0,$G16=0),"",IF(AND($C16="COMPRA",$G16&lt;$F16),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C16="VENTA",$G16&gt;$F16),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <f>IF(OR($D16=0,$I16=0),"",-IF($C16="VENTA",$R$10,$R$9)*IF($R$8=1,$D16*POWER(10,-$R$2)*$R$4,$D16*$G16*$R$4/100/360)*$I16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="9">
+        <f>IF($D16=0,"",N($J16)-N($K16)-N($L16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="21">
+        <f>IF(OR($D16=0,$H16=0),"",IF(AND($C16="COMPRA",$H16&lt;$G16),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C16="VENTA",$H16&gt;$G16),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>TOTALES</t>
         </is>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <f>SUM(D11:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="24">
         <f>SUM(E11:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="23">
-        <f>SUM(I11:I16)</f>
-        <v/>
-      </c>
+      <c r="F17" s="25">
+        <f>SUM(F11:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
       <c r="J17" s="24">
         <f>SUM(J11:J16)</f>
         <v/>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="26">
         <f>SUM(K11:K16)</f>
         <v/>
       </c>
-      <c r="L17" s="24">
+      <c r="L17" s="26">
         <f>SUM(L11:L16)</f>
         <v/>
       </c>
-      <c r="M17" s="21" t="n"/>
+      <c r="M17" s="26">
+        <f>SUM(M11:M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="22" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>Exposición nocional total</t>
-        </is>
-      </c>
-      <c r="L19" s="9">
-        <f>SUMPRODUCT($D$11:$D$16,$F$11:$F$16)*$P$4</f>
+      <c r="J19" s="27" t="inlineStr">
+        <is>
+          <t>Monto total controlado</t>
+        </is>
+      </c>
+      <c r="M19" s="9">
+        <f>SUMPRODUCT($D$11:$D$16,$G$11:$G$16)*$R$4</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="I20" s="25" t="inlineStr">
+      <c r="J20" s="27" t="inlineStr">
+        <is>
+          <t>Apalancamiento total</t>
+        </is>
+      </c>
+      <c r="M20" s="28">
+        <f>$F$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="J21" s="27" t="inlineStr">
         <is>
           <t>Margen requerido (posiciones simultáneas)</t>
         </is>
       </c>
-      <c r="L20" s="9">
-        <f>$L$19*$P$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="I21" s="25" t="inlineStr">
+      <c r="M21" s="9">
+        <f>$M$19*$R$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="J22" s="27" t="inlineStr">
         <is>
           <t>Resultado neto del periodo</t>
         </is>
       </c>
-      <c r="L21" s="9">
-        <f>$L$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="I22" s="26" t="inlineStr">
+      <c r="M22" s="9">
+        <f>$M$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="J23" s="29" t="inlineStr">
         <is>
           <t>Patrimonio final</t>
         </is>
       </c>
-      <c r="L22" s="27">
-        <f>$F$5+$L$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>Especificaciones del broker al 2026-08-19 21:38 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos de 0,01, el paso que acepta MT5, y el MARGEN REQUERIDO se ajusta con él. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="n"/>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="28" t="n"/>
-      <c r="I24" s="28" t="n"/>
-      <c r="J24" s="28" t="n"/>
-      <c r="K24" s="28" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="28" t="n"/>
+      <c r="M23" s="30">
+        <f>$F$5+$M$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Especificaciones del broker al 2026-08-19 21:49 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos de 0,01, el paso que acepta MT5. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="31" t="n"/>
+      <c r="H25" s="31" t="n"/>
+      <c r="I25" s="31" t="n"/>
+      <c r="J25" s="31" t="n"/>
+      <c r="K25" s="31" t="n"/>
+      <c r="L25" s="31" t="n"/>
+      <c r="M25" s="31" t="n"/>
+      <c r="N25" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J6:L6"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="C7:M7"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="C25:N25"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J22:L22"/>
     <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C1:M1"/>
+    <mergeCell ref="J23:L23"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="C24:M24"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="C2:M2"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="C9:J9"/>
   </mergeCells>
-  <conditionalFormatting sqref="I11:L17">
+  <conditionalFormatting sqref="J11:M17">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(I11&lt;&gt;"",I11&lt;0)</formula>
+      <formula>AND(J11&lt;&gt;"",J11&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11:M16">
+  <conditionalFormatting sqref="N11:N16">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>$M11&lt;&gt;""</formula>
+      <formula>$N11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L22">
+  <conditionalFormatting sqref="M23">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>$L$22&lt;$F$5</formula>
+      <formula>$M$23&lt;$F$5</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -1310,10 +1372,10 @@
     <dataValidation sqref="D11 D12 D13 D14 D15 D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Volumen no válido" error="El volumen mínimo que acepta MT5 es 0,01 lotes, en múltiplos de 0,01. Use la coma como separador decimal: 0,54 y no 0.54." type="decimal" operator="greaterThanOrEqual">
       <formula1>0.01</formula1>
     </dataValidation>
-    <dataValidation sqref="F11 F12 F13 F14 F15 F16 G11 G12 G13 G14 G15 G16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Precio no válido" error="Escriba un precio numérico, con la coma como separador decimal: 918,75 y no 918.75." type="decimal" operator="greaterThan">
+    <dataValidation sqref="G11 G12 G13 G14 G15 G16 H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Precio no válido" error="Escriba un precio numérico, con la coma como separador decimal: 918,75 y no 918.75." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos que la posición queda abierta (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
+    <dataValidation sqref="I11 I12 I13 I14 I15 I16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Días no válidos" error="Indique los días completos que la posición queda abierta (0 si se abre y cierra en la misma jornada)." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>3650</formula2>
     </dataValidation>
@@ -1350,57 +1412,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>INSTRUMENTO</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>TICKER MT5</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>DECIMALES</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>TAMAÑO DE CONTRATO (1 lote)</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>VALOR EN CLP DE 1,0 DE PRECIO (POR LOTE)</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>MARGEN</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>PRECIO DE REFERENCIA</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>MODO SWAP</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>SWAP COMPRA</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>SWAP VENTA</t>
         </is>
@@ -1426,13 +1488,13 @@
       <c r="E2" t="n">
         <v>100000</v>
       </c>
-      <c r="F2" s="30" t="n">
+      <c r="F2" s="33" t="n">
         <v>0.01</v>
       </c>
-      <c r="G2" s="31" t="n">
+      <c r="G2" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="31" t="n">
+      <c r="H2" s="34" t="n">
         <v>921.75</v>
       </c>
       <c r="I2" t="n">
@@ -1463,16 +1525,16 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>578222.33</v>
-      </c>
-      <c r="F3" s="30" t="n">
+        <v>577620.84</v>
+      </c>
+      <c r="F3" s="33" t="n">
         <v>0.010063</v>
       </c>
-      <c r="G3" s="31" t="n">
+      <c r="G3" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="H3" s="31" t="n">
-        <v>158.411</v>
+      <c r="H3" s="34" t="n">
+        <v>158.577</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1504,14 +1566,14 @@
       <c r="E4" t="n">
         <v>92175000</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="33" t="n">
         <v>0.01</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="34" t="n">
         <v>0.00026</v>
       </c>
-      <c r="H4" s="31" t="n">
-        <v>1.16822</v>
+      <c r="H4" s="34" t="n">
+        <v>1.16766</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1543,14 +1605,14 @@
       <c r="E5" t="n">
         <v>92175000</v>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="33" t="n">
         <v>0.01</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="34" t="n">
         <v>0.0005</v>
       </c>
-      <c r="H5" s="31" t="n">
-        <v>1.36094</v>
+      <c r="H5" s="34" t="n">
+        <v>1.36066</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1582,14 +1644,14 @@
       <c r="E6" t="n">
         <v>92075</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="33" t="n">
         <v>0.045049</v>
       </c>
-      <c r="G6" s="31" t="n">
+      <c r="G6" s="34" t="n">
         <v>0.6</v>
       </c>
-      <c r="H6" s="31" t="n">
-        <v>4497.8</v>
+      <c r="H6" s="34" t="n">
+        <v>4491.07</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1621,14 +1683,14 @@
       <c r="E7" t="n">
         <v>4603750</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="33" t="n">
         <v>0.045049</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="34" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" s="31" t="n">
-        <v>66.833</v>
+      <c r="H7" s="34" t="n">
+        <v>66.78700000000001</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1660,14 +1722,14 @@
       <c r="E8" t="n">
         <v>920750</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="33" t="n">
         <v>0.015016</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="34" t="n">
         <v>0.15</v>
       </c>
-      <c r="H8" s="31" t="n">
-        <v>85.45999999999999</v>
+      <c r="H8" s="34" t="n">
+        <v>85.405</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1699,14 +1761,14 @@
       <c r="E9" t="n">
         <v>920.75</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="33" t="n">
         <v>0.015016</v>
       </c>
-      <c r="G9" s="31" t="n">
-        <v>79.76000000000001</v>
-      </c>
-      <c r="H9" s="31" t="n">
-        <v>69543.8</v>
+      <c r="G9" s="34" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="H9" s="34" t="n">
+        <v>69801</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1738,14 +1800,14 @@
       <c r="E10" t="n">
         <v>920.75</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="33" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G10" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="31" t="n">
-        <v>29571.58</v>
+      <c r="H10" s="34" t="n">
+        <v>29592.96</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1777,14 +1839,14 @@
       <c r="E11" t="n">
         <v>920.75</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="33" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G11" s="31" t="n">
+      <c r="G11" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="31" t="n">
-        <v>7728.74</v>
+      <c r="H11" s="34" t="n">
+        <v>7730.24</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1816,14 +1878,14 @@
       <c r="E12" t="n">
         <v>920.75</v>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="33" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="31" t="n">
-        <v>53507.51</v>
+      <c r="H12" s="34" t="n">
+        <v>53499.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -1855,13 +1917,13 @@
       <c r="E13" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G13" s="31" t="n">
+      <c r="G13" s="34" t="n">
         <v>0.32</v>
       </c>
-      <c r="H13" s="31" t="n">
+      <c r="H13" s="34" t="n">
         <v>316.63</v>
       </c>
       <c r="I13" t="n">
@@ -1894,13 +1956,13 @@
       <c r="E14" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G14" s="31" t="n">
+      <c r="G14" s="34" t="n">
         <v>0.6</v>
       </c>
-      <c r="H14" s="31" t="n">
+      <c r="H14" s="34" t="n">
         <v>483.99</v>
       </c>
       <c r="I14" t="n">
@@ -1933,13 +1995,13 @@
       <c r="E15" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G15" s="31" t="n">
+      <c r="G15" s="34" t="n">
         <v>0.9</v>
       </c>
-      <c r="H15" s="31" t="n">
+      <c r="H15" s="34" t="n">
         <v>218.24</v>
       </c>
       <c r="I15" t="n">
@@ -1972,13 +2034,13 @@
       <c r="E16" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="33" t="n">
         <v>0.007508</v>
       </c>
-      <c r="G16" s="31" t="n">
+      <c r="G16" s="34" t="n">
         <v>0.31</v>
       </c>
-      <c r="H16" s="31" t="n">
+      <c r="H16" s="34" t="n">
         <v>266.22</v>
       </c>
       <c r="I16" t="n">
@@ -2011,13 +2073,13 @@
       <c r="E17" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G17" s="31" t="n">
+      <c r="G17" s="34" t="n">
         <v>0.26</v>
       </c>
-      <c r="H17" s="31" t="n">
+      <c r="H17" s="34" t="n">
         <v>467.08</v>
       </c>
       <c r="I17" t="n">
@@ -2050,13 +2112,13 @@
       <c r="E18" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G18" s="31" t="n">
+      <c r="G18" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="31" t="n">
+      <c r="H18" s="34" t="n">
         <v>1917.47</v>
       </c>
       <c r="I18" t="n">
@@ -2089,13 +2151,13 @@
       <c r="E19" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="33" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G19" s="31" t="n">
+      <c r="G19" s="34" t="n">
         <v>0.25</v>
       </c>
-      <c r="H19" s="31" t="n">
+      <c r="H19" s="34" t="n">
         <v>357.55</v>
       </c>
       <c r="I19" t="n">
@@ -2128,13 +2190,13 @@
       <c r="E20" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G20" s="31" t="n">
+      <c r="G20" s="34" t="n">
         <v>0.08</v>
       </c>
-      <c r="H20" s="31" t="n">
+      <c r="H20" s="34" t="n">
         <v>63.19</v>
       </c>
       <c r="I20" t="n">
@@ -2167,13 +2229,13 @@
       <c r="E21" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="33" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G21" s="31" t="n">
+      <c r="G21" s="34" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="H21" s="31" t="n">
+      <c r="H21" s="34" t="n">
         <v>1021.38</v>
       </c>
       <c r="I21" t="n">
@@ -2206,13 +2268,13 @@
       <c r="E22" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F22" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G22" s="31" t="n">
+      <c r="G22" s="34" t="n">
         <v>0.11</v>
       </c>
-      <c r="H22" s="31" t="n">
+      <c r="H22" s="34" t="n">
         <v>214.59</v>
       </c>
       <c r="I22" t="n">
@@ -2245,13 +2307,13 @@
       <c r="E23" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G23" s="31" t="n">
+      <c r="G23" s="34" t="n">
         <v>0.89</v>
       </c>
-      <c r="H23" s="31" t="n">
+      <c r="H23" s="34" t="n">
         <v>221.83</v>
       </c>
       <c r="I23" t="n">
@@ -2284,13 +2346,13 @@
       <c r="E24" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F24" s="33" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G24" s="31" t="n">
+      <c r="G24" s="34" t="n">
         <v>0.45</v>
       </c>
-      <c r="H24" s="31" t="n">
+      <c r="H24" s="34" t="n">
         <v>815.77</v>
       </c>
       <c r="I24" t="n">
@@ -2323,13 +2385,13 @@
       <c r="E25" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F25" s="30" t="n">
+      <c r="F25" s="33" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G25" s="31" t="n">
+      <c r="G25" s="34" t="n">
         <v>0.21</v>
       </c>
-      <c r="H25" s="31" t="n">
+      <c r="H25" s="34" t="n">
         <v>357.22</v>
       </c>
       <c r="I25" t="n">
@@ -2362,13 +2424,13 @@
       <c r="E26" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F26" s="33" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G26" s="31" t="n">
+      <c r="G26" s="34" t="n">
         <v>0.77</v>
       </c>
-      <c r="H26" s="31" t="n">
+      <c r="H26" s="34" t="n">
         <v>582.4299999999999</v>
       </c>
       <c r="I26" t="n">
@@ -2382,9 +2444,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:38 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:49 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Simulador'!$B$1:$O$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Simulador'!$B$1:$O$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,11 +19,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.00###"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0&quot; veces&quot;"/>
+    <numFmt numFmtId="168" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -158,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -243,6 +245,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -663,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C1:R25"/>
+  <dimension ref="C1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1013,6 +1021,14 @@
         <f>IF(OR($D11=0,$H11=0),"",IF(AND($C11="COMPRA",$H11&lt;$G11),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C11="VENTA",$H11&gt;$G11),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>llamada_margen</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="C12" s="4" t="inlineStr">
@@ -1059,6 +1075,14 @@
       <c r="N12" s="21">
         <f>IF(OR($D12=0,$H12=0),"",IF(AND($C12="COMPRA",$H12&lt;$G12),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C12="VENTA",$H12&gt;$G12),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>cierre_forzado</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -1288,64 +1312,88 @@
     <row r="22" ht="22" customHeight="1">
       <c r="J22" s="27" t="inlineStr">
         <is>
+          <t>Nivel de margen al abrir</t>
+        </is>
+      </c>
+      <c r="M22" s="29">
+        <f>IF($M$21=0,"",100*$F$5/$M$21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="J23" s="27" t="inlineStr">
+        <is>
+          <t>Movimiento adverso hasta la llamada a margen</t>
+        </is>
+      </c>
+      <c r="M23" s="30">
+        <f>IF($M$19=0,"",100*($F$5-$R$11/100*$M$21)/$M$19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="J24" s="27" t="inlineStr">
+        <is>
           <t>Resultado neto del periodo</t>
         </is>
       </c>
-      <c r="M22" s="9">
+      <c r="M24" s="9">
         <f>$M$17</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="J23" s="29" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="J25" s="31" t="inlineStr">
         <is>
           <t>Patrimonio final</t>
         </is>
       </c>
-      <c r="M23" s="30">
+      <c r="M25" s="32">
         <f>$F$5+$M$17</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>Especificaciones del broker al 2026-08-19 21:49 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos de 0,01, el paso que acepta MT5. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. Este simulador no incorpora stop loss.</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-      <c r="J25" s="31" t="n"/>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="n"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>Especificaciones del broker al 2026-08-19 21:59 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos de 0,01, el paso que acepta MT5. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker llama a margen cuando el nivel baja de 90% y cierra posiciones en 50%. Este simulador no incorpora stop loss.</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="33" t="n"/>
+      <c r="F27" s="33" t="n"/>
+      <c r="G27" s="33" t="n"/>
+      <c r="H27" s="33" t="n"/>
+      <c r="I27" s="33" t="n"/>
+      <c r="J27" s="33" t="n"/>
+      <c r="K27" s="33" t="n"/>
+      <c r="L27" s="33" t="n"/>
+      <c r="M27" s="33" t="n"/>
+      <c r="N27" s="33" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="18">
+  <mergeCells count="20">
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="J5:L5"/>
     <mergeCell ref="J6:L6"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="C25:N25"/>
-    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J25:L25"/>
     <mergeCell ref="J22:L22"/>
+    <mergeCell ref="C27:N27"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="C1:M1"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C2:M2"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J20:L20"/>
     <mergeCell ref="J21:L21"/>
     <mergeCell ref="C7:N7"/>
     <mergeCell ref="C9:J9"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="C2:M2"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="C4:E4"/>
   </mergeCells>
   <conditionalFormatting sqref="J11:M17">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -1357,9 +1405,19 @@
       <formula>$N11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M25">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>$M$25&lt;$F$5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M22">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>$M$22&lt;$R$11</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>$M$23&lt;$F$5</formula>
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>$M$23&lt;=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -1412,57 +1470,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>INSTRUMENTO</t>
         </is>
       </c>
-      <c r="B1" s="32" t="inlineStr">
+      <c r="B1" s="34" t="inlineStr">
         <is>
           <t>TICKER MT5</t>
         </is>
       </c>
-      <c r="C1" s="32" t="inlineStr">
+      <c r="C1" s="34" t="inlineStr">
         <is>
           <t>DECIMALES</t>
         </is>
       </c>
-      <c r="D1" s="32" t="inlineStr">
+      <c r="D1" s="34" t="inlineStr">
         <is>
           <t>TAMAÑO DE CONTRATO (1 lote)</t>
         </is>
       </c>
-      <c r="E1" s="32" t="inlineStr">
+      <c r="E1" s="34" t="inlineStr">
         <is>
           <t>VALOR EN CLP DE 1,0 DE PRECIO (POR LOTE)</t>
         </is>
       </c>
-      <c r="F1" s="32" t="inlineStr">
+      <c r="F1" s="34" t="inlineStr">
         <is>
           <t>MARGEN</t>
         </is>
       </c>
-      <c r="G1" s="32" t="inlineStr">
+      <c r="G1" s="34" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="H1" s="32" t="inlineStr">
+      <c r="H1" s="34" t="inlineStr">
         <is>
           <t>PRECIO DE REFERENCIA</t>
         </is>
       </c>
-      <c r="I1" s="32" t="inlineStr">
+      <c r="I1" s="34" t="inlineStr">
         <is>
           <t>MODO SWAP</t>
         </is>
       </c>
-      <c r="J1" s="32" t="inlineStr">
+      <c r="J1" s="34" t="inlineStr">
         <is>
           <t>SWAP COMPRA</t>
         </is>
       </c>
-      <c r="K1" s="32" t="inlineStr">
+      <c r="K1" s="34" t="inlineStr">
         <is>
           <t>SWAP VENTA</t>
         </is>
@@ -1488,13 +1546,13 @@
       <c r="E2" t="n">
         <v>100000</v>
       </c>
-      <c r="F2" s="33" t="n">
+      <c r="F2" s="35" t="n">
         <v>0.01</v>
       </c>
-      <c r="G2" s="34" t="n">
+      <c r="G2" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="34" t="n">
+      <c r="H2" s="36" t="n">
         <v>921.75</v>
       </c>
       <c r="I2" t="n">
@@ -1525,16 +1583,16 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>577620.84</v>
-      </c>
-      <c r="F3" s="33" t="n">
+        <v>577667.9</v>
+      </c>
+      <c r="F3" s="35" t="n">
         <v>0.010063</v>
       </c>
-      <c r="G3" s="34" t="n">
+      <c r="G3" s="36" t="n">
         <v>0.04</v>
       </c>
-      <c r="H3" s="34" t="n">
-        <v>158.577</v>
+      <c r="H3" s="36" t="n">
+        <v>158.564</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1566,14 +1624,14 @@
       <c r="E4" t="n">
         <v>92175000</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="F4" s="35" t="n">
         <v>0.01</v>
       </c>
-      <c r="G4" s="34" t="n">
+      <c r="G4" s="36" t="n">
         <v>0.00026</v>
       </c>
-      <c r="H4" s="34" t="n">
-        <v>1.16766</v>
+      <c r="H4" s="36" t="n">
+        <v>1.16767</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1605,14 +1663,14 @@
       <c r="E5" t="n">
         <v>92175000</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="35" t="n">
         <v>0.01</v>
       </c>
-      <c r="G5" s="34" t="n">
+      <c r="G5" s="36" t="n">
         <v>0.0005</v>
       </c>
-      <c r="H5" s="34" t="n">
-        <v>1.36066</v>
+      <c r="H5" s="36" t="n">
+        <v>1.36084</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1644,14 +1702,14 @@
       <c r="E6" t="n">
         <v>92075</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="35" t="n">
         <v>0.045049</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="36" t="n">
         <v>0.6</v>
       </c>
-      <c r="H6" s="34" t="n">
-        <v>4491.07</v>
+      <c r="H6" s="36" t="n">
+        <v>4489.18</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1683,14 +1741,14 @@
       <c r="E7" t="n">
         <v>4603750</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="35" t="n">
         <v>0.045049</v>
       </c>
-      <c r="G7" s="34" t="n">
+      <c r="G7" s="36" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" s="34" t="n">
-        <v>66.78700000000001</v>
+      <c r="H7" s="36" t="n">
+        <v>66.746</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1722,14 +1780,14 @@
       <c r="E8" t="n">
         <v>920750</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="35" t="n">
         <v>0.015016</v>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G8" s="36" t="n">
         <v>0.15</v>
       </c>
-      <c r="H8" s="34" t="n">
-        <v>85.405</v>
+      <c r="H8" s="36" t="n">
+        <v>85.515</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1761,14 +1819,14 @@
       <c r="E9" t="n">
         <v>920.75</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="35" t="n">
         <v>0.015016</v>
       </c>
-      <c r="G9" s="34" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="H9" s="34" t="n">
-        <v>69801</v>
+      <c r="G9" s="36" t="n">
+        <v>80.59</v>
+      </c>
+      <c r="H9" s="36" t="n">
+        <v>69732.77</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1800,14 +1858,14 @@
       <c r="E10" t="n">
         <v>920.75</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="35" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G10" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="34" t="n">
-        <v>29592.96</v>
+      <c r="H10" s="36" t="n">
+        <v>29571.93</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1839,14 +1897,14 @@
       <c r="E11" t="n">
         <v>920.75</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="35" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G11" s="34" t="n">
+      <c r="G11" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="34" t="n">
-        <v>7730.24</v>
+      <c r="H11" s="36" t="n">
+        <v>7728.36</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1878,14 +1936,14 @@
       <c r="E12" t="n">
         <v>920.75</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="35" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="34" t="n">
-        <v>53499.51</v>
+      <c r="H12" s="36" t="n">
+        <v>53495.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -1917,13 +1975,13 @@
       <c r="E13" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="36" t="n">
         <v>0.32</v>
       </c>
-      <c r="H13" s="34" t="n">
+      <c r="H13" s="36" t="n">
         <v>316.63</v>
       </c>
       <c r="I13" t="n">
@@ -1956,13 +2014,13 @@
       <c r="E14" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="G14" s="36" t="n">
         <v>0.6</v>
       </c>
-      <c r="H14" s="34" t="n">
+      <c r="H14" s="36" t="n">
         <v>483.99</v>
       </c>
       <c r="I14" t="n">
@@ -1995,13 +2053,13 @@
       <c r="E15" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F15" s="33" t="n">
+      <c r="F15" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G15" s="34" t="n">
+      <c r="G15" s="36" t="n">
         <v>0.9</v>
       </c>
-      <c r="H15" s="34" t="n">
+      <c r="H15" s="36" t="n">
         <v>218.24</v>
       </c>
       <c r="I15" t="n">
@@ -2034,13 +2092,13 @@
       <c r="E16" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F16" s="35" t="n">
         <v>0.007508</v>
       </c>
-      <c r="G16" s="34" t="n">
+      <c r="G16" s="36" t="n">
         <v>0.31</v>
       </c>
-      <c r="H16" s="34" t="n">
+      <c r="H16" s="36" t="n">
         <v>266.22</v>
       </c>
       <c r="I16" t="n">
@@ -2073,13 +2131,13 @@
       <c r="E17" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F17" s="33" t="n">
+      <c r="F17" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G17" s="34" t="n">
+      <c r="G17" s="36" t="n">
         <v>0.26</v>
       </c>
-      <c r="H17" s="34" t="n">
+      <c r="H17" s="36" t="n">
         <v>467.08</v>
       </c>
       <c r="I17" t="n">
@@ -2112,13 +2170,13 @@
       <c r="E18" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F18" s="33" t="n">
+      <c r="F18" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G18" s="34" t="n">
+      <c r="G18" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="34" t="n">
+      <c r="H18" s="36" t="n">
         <v>1917.47</v>
       </c>
       <c r="I18" t="n">
@@ -2151,13 +2209,13 @@
       <c r="E19" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F19" s="33" t="n">
+      <c r="F19" s="35" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G19" s="34" t="n">
+      <c r="G19" s="36" t="n">
         <v>0.25</v>
       </c>
-      <c r="H19" s="34" t="n">
+      <c r="H19" s="36" t="n">
         <v>357.55</v>
       </c>
       <c r="I19" t="n">
@@ -2190,13 +2248,13 @@
       <c r="E20" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F20" s="33" t="n">
+      <c r="F20" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G20" s="34" t="n">
+      <c r="G20" s="36" t="n">
         <v>0.08</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="H20" s="36" t="n">
         <v>63.19</v>
       </c>
       <c r="I20" t="n">
@@ -2229,13 +2287,13 @@
       <c r="E21" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F21" s="33" t="n">
+      <c r="F21" s="35" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="36" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="H21" s="34" t="n">
+      <c r="H21" s="36" t="n">
         <v>1021.38</v>
       </c>
       <c r="I21" t="n">
@@ -2268,13 +2326,13 @@
       <c r="E22" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F22" s="33" t="n">
+      <c r="F22" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G22" s="34" t="n">
+      <c r="G22" s="36" t="n">
         <v>0.11</v>
       </c>
-      <c r="H22" s="34" t="n">
+      <c r="H22" s="36" t="n">
         <v>214.59</v>
       </c>
       <c r="I22" t="n">
@@ -2307,13 +2365,13 @@
       <c r="E23" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F23" s="33" t="n">
+      <c r="F23" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G23" s="34" t="n">
+      <c r="G23" s="36" t="n">
         <v>0.89</v>
       </c>
-      <c r="H23" s="34" t="n">
+      <c r="H23" s="36" t="n">
         <v>221.83</v>
       </c>
       <c r="I23" t="n">
@@ -2346,13 +2404,13 @@
       <c r="E24" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F24" s="33" t="n">
+      <c r="F24" s="35" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G24" s="34" t="n">
+      <c r="G24" s="36" t="n">
         <v>0.45</v>
       </c>
-      <c r="H24" s="34" t="n">
+      <c r="H24" s="36" t="n">
         <v>815.77</v>
       </c>
       <c r="I24" t="n">
@@ -2385,13 +2443,13 @@
       <c r="E25" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F25" s="33" t="n">
+      <c r="F25" s="35" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G25" s="34" t="n">
+      <c r="G25" s="36" t="n">
         <v>0.21</v>
       </c>
-      <c r="H25" s="34" t="n">
+      <c r="H25" s="36" t="n">
         <v>357.22</v>
       </c>
       <c r="I25" t="n">
@@ -2424,13 +2482,13 @@
       <c r="E26" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="35" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G26" s="34" t="n">
+      <c r="G26" s="36" t="n">
         <v>0.77</v>
       </c>
-      <c r="H26" s="34" t="n">
+      <c r="H26" s="36" t="n">
         <v>582.4299999999999</v>
       </c>
       <c r="I26" t="n">
@@ -2444,9 +2502,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
-        <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:49 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+      <c r="A28" s="37" t="inlineStr">
+        <is>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:59 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -19,13 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.00###"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0&quot; veces&quot;"/>
     <numFmt numFmtId="168" formatCode="0&quot;%&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -160,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,9 +247,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1323,11 +1319,11 @@
     <row r="23" ht="22" customHeight="1">
       <c r="J23" s="27" t="inlineStr">
         <is>
-          <t>Movimiento adverso hasta la llamada a margen</t>
-        </is>
-      </c>
-      <c r="M23" s="30">
-        <f>IF($M$19=0,"",100*($F$5-$R$11/100*$M$21)/$M$19)</f>
+          <t>Recorrido adverso hasta la llamada a margen</t>
+        </is>
+      </c>
+      <c r="M23" s="7">
+        <f>IF(OR($M$21=0,SUMPRODUCT((($C$11:$C$16="COMPRA")*2-1)*$D$11:$D$16)=0),"",MAX(0,ROUND(($F$5-$R$11/100*$M$21)/ABS(SUMPRODUCT((($C$11:$C$16="COMPRA")*2-1)*$D$11:$D$16)*$R$4),$R$2)))</f>
         <v/>
       </c>
     </row>
@@ -1343,33 +1339,33 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="J25" s="31" t="inlineStr">
+      <c r="J25" s="30" t="inlineStr">
         <is>
           <t>Patrimonio final</t>
         </is>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="31">
         <f>$F$5+$M$17</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>Especificaciones del broker al 2026-08-19 21:59 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos de 0,01, el paso que acepta MT5. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker llama a margen cuando el nivel baja de 90% y cierra posiciones en 50%. Este simulador no incorpora stop loss.</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="33" t="n"/>
-      <c r="F27" s="33" t="n"/>
-      <c r="G27" s="33" t="n"/>
-      <c r="H27" s="33" t="n"/>
-      <c r="I27" s="33" t="n"/>
-      <c r="J27" s="33" t="n"/>
-      <c r="K27" s="33" t="n"/>
-      <c r="L27" s="33" t="n"/>
-      <c r="M27" s="33" t="n"/>
-      <c r="N27" s="33" t="n"/>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>Especificaciones del broker al 2026-08-19 22:06 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos de 0,01, el paso que acepta MT5. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker llama a margen cuando el nivel baja de 90% y cierra posiciones en 50%. Este simulador no incorpora stop loss.</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="32" t="n"/>
+      <c r="J27" s="32" t="n"/>
+      <c r="K27" s="32" t="n"/>
+      <c r="L27" s="32" t="n"/>
+      <c r="M27" s="32" t="n"/>
+      <c r="N27" s="32" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
@@ -1470,57 +1466,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>INSTRUMENTO</t>
         </is>
       </c>
-      <c r="B1" s="34" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>TICKER MT5</t>
         </is>
       </c>
-      <c r="C1" s="34" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>DECIMALES</t>
         </is>
       </c>
-      <c r="D1" s="34" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>TAMAÑO DE CONTRATO (1 lote)</t>
         </is>
       </c>
-      <c r="E1" s="34" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>VALOR EN CLP DE 1,0 DE PRECIO (POR LOTE)</t>
         </is>
       </c>
-      <c r="F1" s="34" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>MARGEN</t>
         </is>
       </c>
-      <c r="G1" s="34" t="inlineStr">
+      <c r="G1" s="33" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="H1" s="34" t="inlineStr">
+      <c r="H1" s="33" t="inlineStr">
         <is>
           <t>PRECIO DE REFERENCIA</t>
         </is>
       </c>
-      <c r="I1" s="34" t="inlineStr">
+      <c r="I1" s="33" t="inlineStr">
         <is>
           <t>MODO SWAP</t>
         </is>
       </c>
-      <c r="J1" s="34" t="inlineStr">
+      <c r="J1" s="33" t="inlineStr">
         <is>
           <t>SWAP COMPRA</t>
         </is>
       </c>
-      <c r="K1" s="34" t="inlineStr">
+      <c r="K1" s="33" t="inlineStr">
         <is>
           <t>SWAP VENTA</t>
         </is>
@@ -1546,13 +1542,13 @@
       <c r="E2" t="n">
         <v>100000</v>
       </c>
-      <c r="F2" s="35" t="n">
+      <c r="F2" s="34" t="n">
         <v>0.01</v>
       </c>
-      <c r="G2" s="36" t="n">
+      <c r="G2" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="36" t="n">
+      <c r="H2" s="35" t="n">
         <v>921.75</v>
       </c>
       <c r="I2" t="n">
@@ -1583,16 +1579,16 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>577667.9</v>
-      </c>
-      <c r="F3" s="35" t="n">
+        <v>578066.4</v>
+      </c>
+      <c r="F3" s="34" t="n">
         <v>0.010063</v>
       </c>
-      <c r="G3" s="36" t="n">
+      <c r="G3" s="35" t="n">
         <v>0.04</v>
       </c>
-      <c r="H3" s="36" t="n">
-        <v>158.564</v>
+      <c r="H3" s="35" t="n">
+        <v>158.454</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1624,14 +1620,14 @@
       <c r="E4" t="n">
         <v>92175000</v>
       </c>
-      <c r="F4" s="35" t="n">
+      <c r="F4" s="34" t="n">
         <v>0.01</v>
       </c>
-      <c r="G4" s="36" t="n">
+      <c r="G4" s="35" t="n">
         <v>0.00026</v>
       </c>
-      <c r="H4" s="36" t="n">
-        <v>1.16767</v>
+      <c r="H4" s="35" t="n">
+        <v>1.16829</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1663,14 +1659,14 @@
       <c r="E5" t="n">
         <v>92175000</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="34" t="n">
         <v>0.01</v>
       </c>
-      <c r="G5" s="36" t="n">
+      <c r="G5" s="35" t="n">
         <v>0.0005</v>
       </c>
-      <c r="H5" s="36" t="n">
-        <v>1.36084</v>
+      <c r="H5" s="35" t="n">
+        <v>1.36157</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1702,14 +1698,14 @@
       <c r="E6" t="n">
         <v>92075</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="34" t="n">
         <v>0.045049</v>
       </c>
-      <c r="G6" s="36" t="n">
+      <c r="G6" s="35" t="n">
         <v>0.6</v>
       </c>
-      <c r="H6" s="36" t="n">
-        <v>4489.18</v>
+      <c r="H6" s="35" t="n">
+        <v>4498.2</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1741,14 +1737,14 @@
       <c r="E7" t="n">
         <v>4603750</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="34" t="n">
         <v>0.045049</v>
       </c>
-      <c r="G7" s="36" t="n">
+      <c r="G7" s="35" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" s="36" t="n">
-        <v>66.746</v>
+      <c r="H7" s="35" t="n">
+        <v>67.175</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1780,14 +1776,14 @@
       <c r="E8" t="n">
         <v>920750</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="34" t="n">
         <v>0.015016</v>
       </c>
-      <c r="G8" s="36" t="n">
+      <c r="G8" s="35" t="n">
         <v>0.15</v>
       </c>
-      <c r="H8" s="36" t="n">
-        <v>85.515</v>
+      <c r="H8" s="35" t="n">
+        <v>85.505</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1819,14 +1815,14 @@
       <c r="E9" t="n">
         <v>920.75</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="34" t="n">
         <v>0.015016</v>
       </c>
-      <c r="G9" s="36" t="n">
-        <v>80.59</v>
-      </c>
-      <c r="H9" s="36" t="n">
-        <v>69732.77</v>
+      <c r="G9" s="35" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>69728.5</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1858,14 +1854,14 @@
       <c r="E10" t="n">
         <v>920.75</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="34" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G10" s="36" t="n">
+      <c r="G10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="36" t="n">
-        <v>29571.93</v>
+      <c r="H10" s="35" t="n">
+        <v>29606.18</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1897,14 +1893,14 @@
       <c r="E11" t="n">
         <v>920.75</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="34" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G11" s="36" t="n">
+      <c r="G11" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="36" t="n">
-        <v>7728.36</v>
+      <c r="H11" s="35" t="n">
+        <v>7732.36</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -1936,14 +1932,14 @@
       <c r="E12" t="n">
         <v>920.75</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="34" t="n">
         <v>0.050054</v>
       </c>
-      <c r="G12" s="36" t="n">
+      <c r="G12" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="36" t="n">
-        <v>53495.51</v>
+      <c r="H12" s="35" t="n">
+        <v>53515.51</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -1975,13 +1971,13 @@
       <c r="E13" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G13" s="36" t="n">
+      <c r="G13" s="35" t="n">
         <v>0.32</v>
       </c>
-      <c r="H13" s="36" t="n">
+      <c r="H13" s="35" t="n">
         <v>316.63</v>
       </c>
       <c r="I13" t="n">
@@ -2014,13 +2010,13 @@
       <c r="E14" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G14" s="36" t="n">
+      <c r="G14" s="35" t="n">
         <v>0.6</v>
       </c>
-      <c r="H14" s="36" t="n">
+      <c r="H14" s="35" t="n">
         <v>483.99</v>
       </c>
       <c r="I14" t="n">
@@ -2053,13 +2049,13 @@
       <c r="E15" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G15" s="36" t="n">
+      <c r="G15" s="35" t="n">
         <v>0.9</v>
       </c>
-      <c r="H15" s="36" t="n">
+      <c r="H15" s="35" t="n">
         <v>218.24</v>
       </c>
       <c r="I15" t="n">
@@ -2092,13 +2088,13 @@
       <c r="E16" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="34" t="n">
         <v>0.007508</v>
       </c>
-      <c r="G16" s="36" t="n">
+      <c r="G16" s="35" t="n">
         <v>0.31</v>
       </c>
-      <c r="H16" s="36" t="n">
+      <c r="H16" s="35" t="n">
         <v>266.22</v>
       </c>
       <c r="I16" t="n">
@@ -2131,13 +2127,13 @@
       <c r="E17" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G17" s="36" t="n">
+      <c r="G17" s="35" t="n">
         <v>0.26</v>
       </c>
-      <c r="H17" s="36" t="n">
+      <c r="H17" s="35" t="n">
         <v>467.08</v>
       </c>
       <c r="I17" t="n">
@@ -2170,13 +2166,13 @@
       <c r="E18" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G18" s="36" t="n">
+      <c r="G18" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="36" t="n">
+      <c r="H18" s="35" t="n">
         <v>1917.47</v>
       </c>
       <c r="I18" t="n">
@@ -2209,13 +2205,13 @@
       <c r="E19" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="34" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G19" s="36" t="n">
+      <c r="G19" s="35" t="n">
         <v>0.25</v>
       </c>
-      <c r="H19" s="36" t="n">
+      <c r="H19" s="35" t="n">
         <v>357.55</v>
       </c>
       <c r="I19" t="n">
@@ -2248,13 +2244,13 @@
       <c r="E20" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G20" s="36" t="n">
+      <c r="G20" s="35" t="n">
         <v>0.08</v>
       </c>
-      <c r="H20" s="36" t="n">
+      <c r="H20" s="35" t="n">
         <v>63.19</v>
       </c>
       <c r="I20" t="n">
@@ -2287,13 +2283,13 @@
       <c r="E21" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="F21" s="34" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G21" s="36" t="n">
+      <c r="G21" s="35" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="H21" s="36" t="n">
+      <c r="H21" s="35" t="n">
         <v>1021.38</v>
       </c>
       <c r="I21" t="n">
@@ -2326,13 +2322,13 @@
       <c r="E22" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F22" s="35" t="n">
+      <c r="F22" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G22" s="36" t="n">
+      <c r="G22" s="35" t="n">
         <v>0.11</v>
       </c>
-      <c r="H22" s="36" t="n">
+      <c r="H22" s="35" t="n">
         <v>214.59</v>
       </c>
       <c r="I22" t="n">
@@ -2365,13 +2361,13 @@
       <c r="E23" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F23" s="35" t="n">
+      <c r="F23" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G23" s="36" t="n">
+      <c r="G23" s="35" t="n">
         <v>0.89</v>
       </c>
-      <c r="H23" s="36" t="n">
+      <c r="H23" s="35" t="n">
         <v>221.83</v>
       </c>
       <c r="I23" t="n">
@@ -2404,13 +2400,13 @@
       <c r="E24" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F24" s="35" t="n">
+      <c r="F24" s="34" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G24" s="36" t="n">
+      <c r="G24" s="35" t="n">
         <v>0.45</v>
       </c>
-      <c r="H24" s="36" t="n">
+      <c r="H24" s="35" t="n">
         <v>815.77</v>
       </c>
       <c r="I24" t="n">
@@ -2443,13 +2439,13 @@
       <c r="E25" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F25" s="35" t="n">
+      <c r="F25" s="34" t="n">
         <v>0.002503</v>
       </c>
-      <c r="G25" s="36" t="n">
+      <c r="G25" s="35" t="n">
         <v>0.21</v>
       </c>
-      <c r="H25" s="36" t="n">
+      <c r="H25" s="35" t="n">
         <v>357.22</v>
       </c>
       <c r="I25" t="n">
@@ -2482,13 +2478,13 @@
       <c r="E26" t="n">
         <v>46037.5</v>
       </c>
-      <c r="F26" s="35" t="n">
+      <c r="F26" s="34" t="n">
         <v>0.005005</v>
       </c>
-      <c r="G26" s="36" t="n">
+      <c r="G26" s="35" t="n">
         <v>0.77</v>
       </c>
-      <c r="H26" s="36" t="n">
+      <c r="H26" s="35" t="n">
         <v>582.4299999999999</v>
       </c>
       <c r="I26" t="n">
@@ -2502,9 +2498,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
-        <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 21:59 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 22:06 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Simulador" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulador" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Simulador'!$B$1:$O$28</definedName>
@@ -349,7 +349,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>13</col>
@@ -364,13 +364,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="R1">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,2,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="R2">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,3,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,3,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="R3">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,4,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,4,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="R4">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,5,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -793,13 +793,12 @@
         <v>2000000</v>
       </c>
       <c r="G5" s="5" t="n"/>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Capital mínimo por operación (0,01 lotes)</t>
-        </is>
+      <c r="J5" s="6">
+        <f>"Capital mínimo ("&amp;FIXED($R$13,2)&amp;" lotes)"</f>
+        <v/>
       </c>
       <c r="M5" s="9">
-        <f>0.01*$R$7*$R$4*$R$5</f>
+        <f>$R$13*$R$7*$R$4*$R$5</f>
         <v/>
       </c>
       <c r="Q5" t="inlineStr">
@@ -808,7 +807,7 @@
         </is>
       </c>
       <c r="R5">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,6,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -828,13 +827,13 @@
         </is>
       </c>
       <c r="R6">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,7,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,7,FALSE),0)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="C7" s="10">
-        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(--ISTEXT($D$11:$D$16))+SUMPRODUCT(--ISTEXT($G$11:$H$16))+SUMPRODUCT(--ISTEXT($I$11:$I$16))&gt;0,"⚠ Hay un valor escrito como texto. El separador decimal de este Excel es la coma: escriba 0,54 y no 0.54.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($G$11:$G$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($G$11:$G$16&gt;0)*(ABS($G$11:$G$16/$R$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($R$7,$R$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(SUMPRODUCT(--(MOD(ROUND($D$11:$D$16*100,6),1)&lt;&gt;0))&gt;0,"⚠ Hay un volumen que no es múltiplo de 0,01 lotes, el paso mínimo de MT5.",IF($M$21&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($D$11:$D$16,"&gt;0")&amp;" operación(es) sobre "&amp;$R$1&amp;". El volumen en lotes es el que se ingresa en MT5."))))))</f>
+        <f>IF($F$4="","⚠ Seleccione un instrumento de la lista.",IF(SUMPRODUCT(--ISTEXT($D$11:$D$16))+SUMPRODUCT(--ISTEXT($G$11:$H$16))+SUMPRODUCT(--ISTEXT($I$11:$I$16))&gt;0,"⚠ Hay un valor escrito como texto. El separador decimal de este Excel es la coma: escriba 0,54 y no 0.54.",IF(SUMPRODUCT(($D$11:$D$16&gt;0)*($G$11:$G$16=0))&gt;0,"⚠ Hay una operación con volumen y sin precio de entrada.",IF(SUMPRODUCT(($G$11:$G$16&gt;0)*(ABS($G$11:$G$16/$R$7-1)&gt;0.1))&gt;0,"⚠ Un precio de entrada difiere en más de 10% del precio de referencia ($"&amp;FIXED($R$7,$R$2)&amp;"). Verifique que corresponda al instrumento seleccionado.",IF(IFERROR(SUMPRODUCT(($D$11:$D$16&gt;0)*(($D$11:$D$16&lt;$R$13)+(MOD(ROUND($D$11:$D$16/$R$14,6),1)&lt;&gt;0)))&gt;0,FALSE),"⚠ Hay un volumen inválido para este instrumento: el mínimo es "&amp;FIXED($R$13,2)&amp;" lotes y debe ir en múltiplos de "&amp;FIXED($R$14,2)&amp;".",IF($M$21&gt;$F$5,"⚠ El margen requerido excede el capital de la cuenta.","✓ "&amp;COUNTIF($D$11:$D$16,"&gt;0")&amp;" operación(es) sobre "&amp;$R$1&amp;". El volumen en lotes es el que se ingresa en MT5."))))))</f>
         <v/>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -854,7 +853,7 @@
         </is>
       </c>
       <c r="R7">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,8,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -865,7 +864,7 @@
         </is>
       </c>
       <c r="R8">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,9,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,9,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -896,7 +895,7 @@
         </is>
       </c>
       <c r="R9">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,10,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -967,7 +966,7 @@
         </is>
       </c>
       <c r="R10">
-        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$K,11,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,11,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -989,10 +988,10 @@
         <v/>
       </c>
       <c r="G11" s="19" t="n">
-        <v>918.75</v>
+        <v>912.4299999999999</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>923.75</v>
+        <v>917.4299999999999</v>
       </c>
       <c r="I11" s="20" t="n">
         <v>2</v>
@@ -1023,7 +1022,7 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
@@ -1044,10 +1043,10 @@
         <v/>
       </c>
       <c r="G12" s="19" t="n">
-        <v>925.75</v>
+        <v>919.4299999999999</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>922.75</v>
+        <v>916.4299999999999</v>
       </c>
       <c r="I12" s="20" t="n">
         <v>1</v>
@@ -1099,10 +1098,10 @@
         <v/>
       </c>
       <c r="G13" s="19" t="n">
-        <v>921.75</v>
+        <v>915.4299999999999</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>920.25</v>
+        <v>913.9299999999999</v>
       </c>
       <c r="I13" s="20" t="n">
         <v>0</v>
@@ -1125,6 +1124,15 @@
       </c>
       <c r="N13" s="21">
         <f>IF(OR($D13=0,$H13=0),"",IF(AND($C13="COMPRA",$H13&lt;$G13),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C13="VENTA",$H13&gt;$G13),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
+        <v/>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>vol_min</t>
+        </is>
+      </c>
+      <c r="R13">
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,12,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -1162,6 +1170,15 @@
         <f>IF(OR($D14=0,$H14=0),"",IF(AND($C14="COMPRA",$H14&lt;$G14),"precio de salida inferior a la entrada: resultado negativo en una compra",IF(AND($C14="VENTA",$H14&gt;$G14),"precio de salida superior a la entrada: resultado negativo en una venta","")))</f>
         <v/>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>vol_paso</t>
+        </is>
+      </c>
+      <c r="R14">
+        <f>IFERROR(VLOOKUP($F$4,Datos!$A:$N,13,FALSE),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="C15" s="4" t="n"/>
@@ -1319,11 +1336,11 @@
     <row r="23" ht="22" customHeight="1">
       <c r="J23" s="27" t="inlineStr">
         <is>
-          <t>Recorrido adverso hasta la llamada a margen</t>
+          <t>Recorrido adverso hasta el cierre forzado</t>
         </is>
       </c>
       <c r="M23" s="7">
-        <f>IF(OR($M$21=0,SUMPRODUCT((($C$11:$C$16="COMPRA")*2-1)*$D$11:$D$16)=0),"",MAX(0,ROUND(($F$5-$R$11/100*$M$21)/ABS(SUMPRODUCT((($C$11:$C$16="COMPRA")*2-1)*$D$11:$D$16)*$R$4),$R$2)))</f>
+        <f>IF(OR($M$21=0,SUMPRODUCT((($C$11:$C$16="COMPRA")*2-1)*$D$11:$D$16)=0),"",MAX(0,ROUND(($F$5-$R$12/100*$M$21)/ABS(SUMPRODUCT((($C$11:$C$16="COMPRA")*2-1)*$D$11:$D$16)*$R$4),$R$2)))</f>
         <v/>
       </c>
     </row>
@@ -1349,10 +1366,10 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="42" customHeight="1">
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>Especificaciones del broker al 2026-08-19 22:06 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos de 0,01, el paso que acepta MT5. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker llama a margen cuando el nivel baja de 90% y cierra posiciones en 50%. Este simulador no incorpora stop loss.</t>
+          <t>Especificaciones del broker al 2026-08-24 10:28 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos del paso que acepta MT5 en ese instrumento, indicado arriba a la derecha. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker avisa cuando el nivel de margen baja de 200% y cierra posiciones por su cuenta en 50%, que es el umbral contra el que se mide el recorrido. Este simulador no incorpora stop loss.</t>
         </is>
       </c>
       <c r="D27" s="32" t="n"/>
@@ -1418,13 +1435,13 @@
   </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Instrumento no válido" error="Seleccione un instrumento de la lista." type="list">
-      <formula1>Datos!$A$2:$A$26</formula1>
+      <formula1>Datos!$A$2:$A$149</formula1>
     </dataValidation>
     <dataValidation sqref="C11 C12 C13 C14 C15 C16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dirección no válida" error="Seleccione COMPRA o VENTA." type="list">
       <formula1>"COMPRA,VENTA"</formula1>
     </dataValidation>
-    <dataValidation sqref="D11 D12 D13 D14 D15 D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Volumen no válido" error="El volumen mínimo que acepta MT5 es 0,01 lotes, en múltiplos de 0,01. Use la coma como separador decimal: 0,54 y no 0.54." type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.01</formula1>
+    <dataValidation sqref="D11 D12 D13 D14 D15 D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Volumen no válido" error="El volumen no alcanza el mínimo que MT5 acepta en este instrumento, que se indica arriba a la derecha. Use la coma como separador decimal: 0,54 y no 0.54." type="decimal" operator="greaterThanOrEqual">
+      <formula1>$R$13</formula1>
     </dataValidation>
     <dataValidation sqref="G11 G12 G13 G14 G15 G16 H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Precio no válido" error="Escriba un precio numérico, con la coma como separador decimal: 918,75 y no 918.75." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
@@ -1449,10 +1466,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -1463,6 +1480,9 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1521,55 +1541,81 @@
           <t>SWAP VENTA</t>
         </is>
       </c>
+      <c r="L1" s="33" t="inlineStr">
+        <is>
+          <t>VOLUMEN MÍNIMO</t>
+        </is>
+      </c>
+      <c r="M1" s="33" t="inlineStr">
+        <is>
+          <t>PASO DE VOLUMEN</t>
+        </is>
+      </c>
+      <c r="N1" s="33" t="inlineStr">
+        <is>
+          <t>GRUPO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dólar / Peso Chileno</t>
+          <t>Australian Dollar vs Canadian Dollar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USDCLP</t>
+          <t>AUDCAD</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>100000</v>
       </c>
       <c r="E2" t="n">
-        <v>100000</v>
+        <v>66220820.46</v>
       </c>
       <c r="F2" s="34" t="n">
-        <v>0.01</v>
+        <v>0.009998999999999999</v>
       </c>
       <c r="G2" s="35" t="n">
-        <v>1</v>
+        <v>0.0004</v>
       </c>
       <c r="H2" s="35" t="n">
-        <v>921.75</v>
+        <v>0.99038</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>-7</v>
+        <v>-2.31</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1</v>
+        <v>-9.138999999999999</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dólar / Yen Japonés</t>
+          <t>Australian Dollar vs Japanese Yen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1579,36 +1625,47 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>578066.4</v>
+        <v>575344.1</v>
       </c>
       <c r="F3" s="34" t="n">
-        <v>0.010063</v>
+        <v>0.009998</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="35" t="n">
-        <v>158.454</v>
+        <v>114.003</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.513</v>
+        <v>-2.014</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.631</v>
+        <v>-14.365</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Euro / Dólar</t>
+          <t>Australian Dollar vs New Zealand Dollar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1618,36 +1675,47 @@
         <v>100000</v>
       </c>
       <c r="E4" t="n">
-        <v>92175000</v>
+        <v>54639270.41</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>0.01</v>
+        <v>0.009996</v>
       </c>
       <c r="G4" s="35" t="n">
-        <v>0.00026</v>
+        <v>0.0006000000000000001</v>
       </c>
       <c r="H4" s="35" t="n">
-        <v>1.16829</v>
+        <v>1.20075</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.455</v>
+        <v>-3.164</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.09</v>
+        <v>-10.686</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Libra / Dólar</t>
+          <t>Australian Dollar vs Swiss Franc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1657,850 +1725,7242 @@
         <v>100000</v>
       </c>
       <c r="E5" t="n">
-        <v>92175000</v>
+        <v>114193226.47</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>0.01</v>
+        <v>0.009991</v>
       </c>
       <c r="G5" s="35" t="n">
-        <v>0.0005</v>
+        <v>0.0009000000000000001</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>1.36157</v>
+        <v>0.57477</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.612</v>
+        <v>-0.253</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.264</v>
+        <v>-11.128</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Oro</t>
+          <t>Australian Dollar vs US Dollar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="E6" t="n">
-        <v>92075</v>
+        <v>91543000</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.045049</v>
+        <v>0.01</v>
       </c>
       <c r="G6" s="35" t="n">
-        <v>0.6</v>
+        <v>0.00032</v>
       </c>
       <c r="H6" s="35" t="n">
-        <v>4498.2</v>
+        <v>0.71637</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>-16</v>
+        <v>-2.206</v>
       </c>
       <c r="K6" t="n">
-        <v>-6</v>
+        <v>-1.285</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Plata</t>
+          <t>British Pounds  vs. New Zealand Dollar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XAGUSD</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5000</v>
+        <v>100000</v>
       </c>
       <c r="E7" t="n">
-        <v>4603750</v>
+        <v>54639270.41</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.045049</v>
+        <v>0.019982</v>
       </c>
       <c r="G7" s="35" t="n">
-        <v>0.05</v>
+        <v>0.003</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>67.175</v>
+        <v>2.28802</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>-4</v>
+        <v>-5.185</v>
       </c>
       <c r="K7" t="n">
-        <v>-1</v>
+        <v>-22.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Petróleo WTI</t>
+          <t>British Pounds vs Australian Dollar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WTI.spot</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="E8" t="n">
-        <v>920750</v>
+        <v>65578658.91</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.015016</v>
+        <v>0.009997000000000001</v>
       </c>
       <c r="G8" s="35" t="n">
-        <v>0.15</v>
+        <v>0.0009000000000000001</v>
       </c>
       <c r="H8" s="35" t="n">
-        <v>85.505</v>
+        <v>1.90519</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>-20</v>
+        <v>-9.022</v>
       </c>
       <c r="K8" t="n">
-        <v>-15</v>
+        <v>-7.371</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>British Pounds vs Canadian Dollar</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BTCUSD</t>
+          <t>GBPCAD</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E9" t="n">
-        <v>920.75</v>
+        <v>66220820.46</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.015016</v>
+        <v>0.009998</v>
       </c>
       <c r="G9" s="35" t="n">
-        <v>79.2</v>
+        <v>0.0009000000000000001</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>69728.5</v>
+        <v>1.88645</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.288</v>
+        <v>-3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.082</v>
+        <v>-19.11</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nasdaq 100</t>
+          <t>British Pounds vs Japanese Yen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>US100.spot</t>
+          <t>GBPJPY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E10" t="n">
-        <v>920.75</v>
+        <v>575344.1</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.050054</v>
+        <v>0.009998999999999999</v>
       </c>
       <c r="G10" s="35" t="n">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="H10" s="35" t="n">
-        <v>29606.18</v>
+        <v>217.117</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.8415</v>
+        <v>-3.222</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9899</v>
+        <v>-28.652</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>British Pounds vs Swiss Franc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>US500.spot</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E11" t="n">
-        <v>920.75</v>
+        <v>114193226.47</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.050054</v>
+        <v>0.009995</v>
       </c>
       <c r="G11" s="35" t="n">
-        <v>1</v>
+        <v>0.0008</v>
       </c>
       <c r="H11" s="35" t="n">
-        <v>7732.36</v>
+        <v>1.09432</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8415</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9899</v>
+        <v>-24.531</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dow Jones Industrial</t>
+          <t>Canadian Dollar vs Japanese Yen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>US30.spot</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E12" t="n">
-        <v>920.75</v>
+        <v>575344.1</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>0.050054</v>
+        <v>0.009998</v>
       </c>
       <c r="G12" s="35" t="n">
-        <v>7</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="35" t="n">
-        <v>53515.51</v>
+        <v>115.125</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6161</v>
+        <v>-1.201</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9353</v>
+        <v>-8.281000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Canadian Dollar vs Swiss Franc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#AAPL</t>
+          <t>CADCHF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E13" t="n">
-        <v>46037.5</v>
+        <v>114193226.47</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>0.005005</v>
+        <v>0.009991</v>
       </c>
       <c r="G13" s="35" t="n">
-        <v>0.32</v>
+        <v>0.00075</v>
       </c>
       <c r="H13" s="35" t="n">
-        <v>316.63</v>
+        <v>0.5804</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.1</v>
+        <v>0.507</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.1</v>
+        <v>-7.852</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Microsoft Corp.</t>
+          <t>Dólar / Peso Chileno</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>#MSFT</t>
+          <t>USDCLP</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E14" t="n">
-        <v>46037.5</v>
+        <v>100000</v>
       </c>
       <c r="F14" s="34" t="n">
-        <v>0.005005</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="35" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H14" s="35" t="n">
-        <v>483.99</v>
+        <v>915.4299999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.1</v>
+        <v>-7</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.1</v>
+        <v>-0.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NVIDIA Corp.</t>
+          <t>Dólar / Yen Japonés</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>#NVDA</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E15" t="n">
-        <v>46037.5</v>
+        <v>571607.87</v>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.005005</v>
+        <v>0.010063</v>
       </c>
       <c r="G15" s="35" t="n">
-        <v>0.9</v>
+        <v>0.04</v>
       </c>
       <c r="H15" s="35" t="n">
-        <v>218.24</v>
+        <v>159.15</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.1</v>
+        <v>-2.513</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.1</v>
+        <v>-23.933</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amazon.com Inc.</t>
+          <t>Euro / Dólar</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#AMZN</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E16" t="n">
-        <v>46037.5</v>
+        <v>91543000</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>0.007508</v>
+        <v>0.01</v>
       </c>
       <c r="G16" s="35" t="n">
-        <v>0.31</v>
+        <v>0.00026</v>
       </c>
       <c r="H16" s="35" t="n">
-        <v>266.22</v>
+        <v>1.16718</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.1</v>
+        <v>-15.808</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.1</v>
+        <v>-1.09</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Euro vs Australian Dollar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>#AMD</t>
+          <t>EURAUD</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E17" t="n">
-        <v>46037.5</v>
+        <v>65578658.91</v>
       </c>
       <c r="F17" s="34" t="n">
-        <v>0.005005</v>
+        <v>0.009997000000000001</v>
       </c>
       <c r="G17" s="35" t="n">
-        <v>0.26</v>
+        <v>0.0006000000000000001</v>
       </c>
       <c r="H17" s="35" t="n">
-        <v>467.08</v>
+        <v>1.62979</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.1</v>
+        <v>-17.017</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.1</v>
+        <v>-0.218</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc.</t>
+          <t>Euro vs British Pounds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#MELI</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E18" t="n">
-        <v>46037.5</v>
+        <v>124903100.06</v>
       </c>
       <c r="F18" s="34" t="n">
-        <v>0.005005</v>
+        <v>0.009996</v>
       </c>
       <c r="G18" s="35" t="n">
-        <v>7</v>
+        <v>0.0005</v>
       </c>
       <c r="H18" s="35" t="n">
-        <v>1917.47</v>
+        <v>0.85575</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.1</v>
+        <v>-10.296</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.1</v>
+        <v>-0.645</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Euro vs Canadian Dollar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>#JPM</t>
+          <t>EURCAD</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E19" t="n">
-        <v>46037.5</v>
+        <v>66220820.46</v>
       </c>
       <c r="F19" s="34" t="n">
-        <v>0.002503</v>
+        <v>0.009997000000000001</v>
       </c>
       <c r="G19" s="35" t="n">
-        <v>0.25</v>
+        <v>0.0009000000000000001</v>
       </c>
       <c r="H19" s="35" t="n">
-        <v>357.55</v>
+        <v>1.61392</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.1</v>
+        <v>-6.136</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.1</v>
+        <v>-2.899</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Euro vs Japanese Yen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>#BAC</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E20" t="n">
-        <v>46037.5</v>
+        <v>575344.1</v>
       </c>
       <c r="F20" s="34" t="n">
-        <v>0.005005</v>
+        <v>0.009998999999999999</v>
       </c>
       <c r="G20" s="35" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H20" s="35" t="n">
-        <v>63.19</v>
+        <v>185.734</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.1</v>
+        <v>-5.375</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.1</v>
+        <v>-11.57</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Euro vs New Zealand Dollar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>#GS</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E21" t="n">
-        <v>46037.5</v>
+        <v>54639270.41</v>
       </c>
       <c r="F21" s="34" t="n">
-        <v>0.002503</v>
+        <v>0.009995</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.0009000000000000001</v>
       </c>
       <c r="H21" s="35" t="n">
-        <v>1021.38</v>
+        <v>1.95655</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.1</v>
+        <v>-7.802</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.1</v>
+        <v>-2.418</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Euro vs Swiss Franc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>#MS</t>
+          <t>EURCHF</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E22" t="n">
-        <v>46037.5</v>
+        <v>114193226.47</v>
       </c>
       <c r="F22" s="34" t="n">
-        <v>0.005005</v>
+        <v>0.009995</v>
       </c>
       <c r="G22" s="35" t="n">
-        <v>0.11</v>
+        <v>0.0005</v>
       </c>
       <c r="H22" s="35" t="n">
-        <v>214.59</v>
+        <v>0.9361</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>-5.1</v>
+        <v>-5.094</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.1</v>
+        <v>-12.272</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Boeing Co.</t>
+          <t>Euro vs Turkish Lira</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>#BA</t>
+          <t>EURTRY</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E23" t="n">
-        <v>46037.5</v>
+        <v>1907120.41</v>
       </c>
       <c r="F23" s="34" t="n">
-        <v>0.005005</v>
+        <v>0.009967999999999999</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>0.89</v>
+        <v>0.1</v>
       </c>
       <c r="H23" s="35" t="n">
-        <v>221.83</v>
+        <v>56.20374</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.1</v>
+        <v>-896.1950000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.1</v>
+        <v>-179.903</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Libra / Dólar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#CAT</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E24" t="n">
-        <v>46037.5</v>
+        <v>91543000</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>0.002503</v>
+        <v>0.01</v>
       </c>
       <c r="G24" s="35" t="n">
-        <v>0.45</v>
+        <v>0.0005</v>
       </c>
       <c r="H24" s="35" t="n">
-        <v>815.77</v>
+        <v>1.36442</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.1</v>
+        <v>-3.612</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.1</v>
+        <v>-3.264</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>New Zealand Dollar vs Canadian Dollar</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>#GE</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>100000</v>
       </c>
       <c r="E25" t="n">
-        <v>46037.5</v>
+        <v>66220820.46</v>
       </c>
       <c r="F25" s="34" t="n">
-        <v>0.002503</v>
+        <v>0.009998999999999999</v>
       </c>
       <c r="G25" s="35" t="n">
-        <v>0.21</v>
+        <v>0.00075</v>
       </c>
       <c r="H25" s="35" t="n">
-        <v>357.22</v>
+        <v>0.82523</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.1</v>
+        <v>-2.249</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.1</v>
+        <v>-3.029</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>New Zealand Dollar vs Japanise Yen</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NZDJPY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>575344.1</v>
+      </c>
+      <c r="F26" s="34" t="n">
+        <v>0.009998999999999999</v>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>94.977</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>New Zealand Dollar vs Swiss Franc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NZDCHF</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>114193226.47</v>
+      </c>
+      <c r="F27" s="34" t="n">
+        <v>0.009993</v>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>0.47881</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-6.812</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>New Zealand Dollar vs US Dollar</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>91543000</v>
+      </c>
+      <c r="F28" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G28" s="35" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1.449</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.965</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Swiss Franc vs Japanese Yen</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CHFJPY</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>575344.1</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G29" s="35" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>198.48</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-5.657</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.869</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>US Dollar vs Canadian Dollar</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>38418086.21</v>
+      </c>
+      <c r="F30" s="34" t="n">
+        <v>0.017232</v>
+      </c>
+      <c r="G30" s="35" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="H30" s="35" t="n">
+        <v>1.38281</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-2.884</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-9.815</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>US Dollar vs Mexican Pesos</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>USDMXN</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5098553.58</v>
+      </c>
+      <c r="F31" s="34" t="n">
+        <v>0.01059</v>
+      </c>
+      <c r="G31" s="35" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H31" s="35" t="n">
+        <v>16.9547</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-355.797</v>
+      </c>
+      <c r="K31" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>US Dollar vs Swiss Franc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>50796548.57</v>
+      </c>
+      <c r="F32" s="34" t="n">
+        <v>0.022466</v>
+      </c>
+      <c r="G32" s="35" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H32" s="35" t="n">
+        <v>0.80215</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.221</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-16.003</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>US Dollar vs Turkish Lira</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>USDTRY</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1862119.78</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>0.163322</v>
+      </c>
+      <c r="G33" s="35" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H33" s="35" t="n">
+        <v>48.16064</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-4683.575</v>
+      </c>
+      <c r="K33" t="n">
+        <v>134.429</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NGAS</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9150300</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>0.010004</v>
+      </c>
+      <c r="G34" s="35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H34" s="35" t="n">
+        <v>2.868</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>CFD Commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Oro</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="n">
+        <v>91503</v>
+      </c>
+      <c r="F35" s="34" t="n">
+        <v>0.04502</v>
+      </c>
+      <c r="G35" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H35" s="35" t="n">
+        <v>4673.36</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>CFD Commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Petróleo WTI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>WTI.spot</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" t="n">
+        <v>91503</v>
+      </c>
+      <c r="F36" s="34" t="n">
+        <v>0.015007</v>
+      </c>
+      <c r="G36" s="35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>85.587</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>CFD Commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Plata</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4575150</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <v>0.04502</v>
+      </c>
+      <c r="G37" s="35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H37" s="35" t="n">
+        <v>69.136</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>CFD Commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>UK Oil</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BRENT.spot</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" t="n">
+        <v>91503</v>
+      </c>
+      <c r="F38" s="34" t="n">
+        <v>0.015007</v>
+      </c>
+      <c r="G38" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H38" s="35" t="n">
+        <v>92.676</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>CFD Commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CAC 40 Francia Spot</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FRA40.spot</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1067.77</v>
+      </c>
+      <c r="F39" s="34" t="n">
+        <v>0.050033</v>
+      </c>
+      <c r="G39" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>8459.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-3.5838</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-2.258</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>CFD Indices</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CFD based on spot on index FTSE 100</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>UK100.spot</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1248.03</v>
+      </c>
+      <c r="F40" s="34" t="n">
+        <v>0.05004</v>
+      </c>
+      <c r="G40" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>10857.3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-5.728</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-5.568</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>CFD Indices</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DAX 40 Alemania Spot</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GER40.spot</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1067.77</v>
+      </c>
+      <c r="F41" s="34" t="n">
+        <v>0.050033</v>
+      </c>
+      <c r="G41" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>26074.25</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-3.5001</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-2.2795</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>CFD Indices</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dow Jones Industrial</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>US30.spot</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F42" s="34" t="n">
+        <v>0.050022</v>
+      </c>
+      <c r="G42" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" s="35" t="n">
+        <v>53439.51</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-3.6161</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-1.9353</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>CFD Indices</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Nasdaq 100</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>US100.spot</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F43" s="34" t="n">
+        <v>0.050022</v>
+      </c>
+      <c r="G43" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="35" t="n">
+        <v>28932.38</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-3.8415</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-1.9899</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>CFD Indices</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>US500.spot</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9150.299999999999</v>
+      </c>
+      <c r="F44" s="34" t="n">
+        <v>0.050022</v>
+      </c>
+      <c r="G44" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="35" t="n">
+        <v>7654.23</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-3.8415</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-1.9899</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>CFD Indices</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Bitcoin</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F45" s="34" t="n">
+        <v>0.015007</v>
+      </c>
+      <c r="G45" s="35" t="n">
+        <v>83.79000000000001</v>
+      </c>
+      <c r="H45" s="35" t="n">
+        <v>79260.84</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-0.288</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Criptomonedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cardano vs US Dollar</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ADAUSD</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>915030</v>
+      </c>
+      <c r="F46" s="34" t="n">
+        <v>0.006003</v>
+      </c>
+      <c r="G46" s="35" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="H46" s="35" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Criptomonedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dogecoin vs US Dollar</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DOGUSD</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9150300</v>
+      </c>
+      <c r="F47" s="34" t="n">
+        <v>0.006003</v>
+      </c>
+      <c r="G47" s="35" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="H47" s="35" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Criptomonedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ethereum vs US Dollar</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ETHUSD</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F48" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G48" s="35" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="H48" s="35" t="n">
+        <v>2515.29</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-0.288</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-0.103</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Criptomonedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Litecoin vs US Dollar</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LTCUSD</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9150.299999999999</v>
+      </c>
+      <c r="F49" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G49" s="35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H49" s="35" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Criptomonedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Solana vs US Dollar</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SOLUSD</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="n">
+        <v>91503</v>
+      </c>
+      <c r="F50" s="34" t="n">
+        <v>0.006003</v>
+      </c>
+      <c r="G50" s="35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H50" s="35" t="n">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Criptomonedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ETF Direxoin Daily Financial Bull 3x Shares</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FAS.US</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F51" s="34" t="n">
+        <v>0.250109</v>
+      </c>
+      <c r="G51" s="35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H51" s="35" t="n">
+        <v>185.64</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ETF Financial Select Sector SPDR CFD</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>XLF.US</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F52" s="34" t="n">
+        <v>0.250109</v>
+      </c>
+      <c r="G52" s="35" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H52" s="35" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ETF Global X Artificial Intelligence &amp; Technology</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AIQ.US</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F53" s="34" t="n">
+        <v>0.100044</v>
+      </c>
+      <c r="G53" s="35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H53" s="35" t="n">
+        <v>62.17</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ETF PowerShares QQQ Trust Series 1 CFD</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>QQQ.US</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F54" s="34" t="n">
+        <v>0.100044</v>
+      </c>
+      <c r="G54" s="35" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H54" s="35" t="n">
+        <v>704</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ETF SPDR Gold Shares CFD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GLD.US</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F55" s="34" t="n">
+        <v>0.100044</v>
+      </c>
+      <c r="G55" s="35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H55" s="35" t="n">
+        <v>428.74</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ETF SPDR S&amp;P 500 Trust CFD</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SPY.US</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F56" s="34" t="n">
+        <v>0.100044</v>
+      </c>
+      <c r="G56" s="35" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H56" s="35" t="n">
+        <v>763.04</v>
+      </c>
+      <c r="I56" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ETF Vanguard Total Bond Market ETF</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BND.US</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F57" s="34" t="n">
+        <v>0.250109</v>
+      </c>
+      <c r="G57" s="35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H57" s="35" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ETF Vanguard Total International Bond ETF</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BNDX.US</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F58" s="34" t="n">
+        <v>0.250109</v>
+      </c>
+      <c r="G58" s="35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H58" s="35" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ETF iShares China Large-Cap CFD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FXI.US</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F59" s="34" t="n">
+        <v>0.100044</v>
+      </c>
+      <c r="G59" s="35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H59" s="35" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ETF iShares MSCI Brazil Capped CFD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EWZ.US</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F60" s="34" t="n">
+        <v>0.100044</v>
+      </c>
+      <c r="G60" s="35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H60" s="35" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ETF iShares MSCI Emerging Markets CFD</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EEM.US</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F61" s="34" t="n">
+        <v>0.100044</v>
+      </c>
+      <c r="G61" s="35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H61" s="35" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ETF iShares PHLX Semiconductor CFD</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SOXX.US</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F62" s="34" t="n">
+        <v>0.100044</v>
+      </c>
+      <c r="G62" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H62" s="35" t="n">
+        <v>500.46</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ETF iShares Russell 2000 Index Fund</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>IWM.US</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F63" s="34" t="n">
+        <v>0.250109</v>
+      </c>
+      <c r="G63" s="35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H63" s="35" t="n">
+        <v>298.89</v>
+      </c>
+      <c r="I63" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>CFD ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AT&amp;T Inc.</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>#T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F64" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G64" s="35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H64" s="35" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Abbott Laboratories</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>#ABT</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F65" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G65" s="35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H65" s="35" t="n">
+        <v>117.17</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Adobe Systems Incorporated</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>#ADBE</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F66" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G66" s="35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H66" s="35" t="n">
+        <v>277.19</v>
+      </c>
+      <c r="I66" t="n">
+        <v>5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>#AMD</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F67" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G67" s="35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H67" s="35" t="n">
+        <v>455.71</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Airbnb Inc.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>#ABNB</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F68" s="34" t="n">
+        <v>0.020009</v>
+      </c>
+      <c r="G68" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H68" s="35" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="I68" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Alibaba Group Holding Limited</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>#BABA</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F69" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G69" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H69" s="35" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Alphabet Inc. Class C (Google)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>#GOOG</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F70" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G70" s="35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H70" s="35" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc.</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>#AMZN</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F71" s="34" t="n">
+        <v>0.007503</v>
+      </c>
+      <c r="G71" s="35" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H71" s="35" t="n">
+        <v>261.31</v>
+      </c>
+      <c r="I71" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>American Airlines Group Inc.</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>#AAL</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F72" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G72" s="35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H72" s="35" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>American Electric Power Co.</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#AEP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F73" s="34" t="n">
+        <v>0.010004</v>
+      </c>
+      <c r="G73" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="35" t="n">
+        <v>120.61</v>
+      </c>
+      <c r="I73" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>American Express Co.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#AXP</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F74" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G74" s="35" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H74" s="35" t="n">
+        <v>343.59</v>
+      </c>
+      <c r="I74" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>American International Group</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#AIG</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F75" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G75" s="35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H75" s="35" t="n">
+        <v>77.61</v>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Amgen Inc.</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#AMGN</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F76" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G76" s="35" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H76" s="35" t="n">
+        <v>440.77</v>
+      </c>
+      <c r="I76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>#AAPL</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F77" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G77" s="35" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H77" s="35" t="n">
+        <v>312.8</v>
+      </c>
+      <c r="I77" t="n">
+        <v>5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Baidu Inc. ADR</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>#BIDU</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F78" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G78" s="35" t="n">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="H78" s="35" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="I78" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>#BAC</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F79" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G79" s="35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H79" s="35" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Baxter International Inc.</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>#BAX</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F80" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G80" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H80" s="35" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="I80" t="n">
+        <v>5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Best Buy Co. Inc.</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>#BBY</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F81" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G81" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="35" t="n">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="I81" t="n">
+        <v>5</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Beyond Meat Inc.</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>#BYND</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F82" s="34" t="n">
+        <v>0.010004</v>
+      </c>
+      <c r="G82" s="35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H82" s="35" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="I82" t="n">
+        <v>5</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Biogen Idec Inc.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>#BIIB</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F83" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G83" s="35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H83" s="35" t="n">
+        <v>215.06</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Boeing Co.</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>#BA</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F84" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G84" s="35" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H84" s="35" t="n">
+        <v>210.58</v>
+      </c>
+      <c r="I84" t="n">
+        <v>5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Broadcom Ltd.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>#AVGO</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F85" s="34" t="n">
+        <v>0.017508</v>
+      </c>
+      <c r="G85" s="35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H85" s="35" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="I85" t="n">
+        <v>5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Canopy Growth Corp.</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>#CGC</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F86" s="34" t="n">
+        <v>0.012503</v>
+      </c>
+      <c r="G86" s="35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H86" s="35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I86" t="n">
+        <v>5</v>
+      </c>
+      <c r="J86" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>#CAT</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F87" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G87" s="35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H87" s="35" t="n">
+        <v>810.67</v>
+      </c>
+      <c r="I87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J87" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Chevron Corp.</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>#CVX</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F88" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G88" s="35" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H88" s="35" t="n">
+        <v>204.32</v>
+      </c>
+      <c r="I88" t="n">
+        <v>5</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cisco Systems</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>#CSCO</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F89" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G89" s="35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H89" s="35" t="n">
+        <v>109.99</v>
+      </c>
+      <c r="I89" t="n">
+        <v>5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Citigroup Inc.</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>#C</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F90" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G90" s="35" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H90" s="35" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="I90" t="n">
+        <v>5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Coca Cola Company</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>#KO</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F91" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G91" s="35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H91" s="35" t="n">
+        <v>92.36</v>
+      </c>
+      <c r="I91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Coinbase Global Inc.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>#COIN</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F92" s="34" t="n">
+        <v>0.017508</v>
+      </c>
+      <c r="G92" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H92" s="35" t="n">
+        <v>188.42</v>
+      </c>
+      <c r="I92" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Corp.</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>#COST</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F93" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G93" s="35" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H93" s="35" t="n">
+        <v>961.46</v>
+      </c>
+      <c r="I93" t="n">
+        <v>5</v>
+      </c>
+      <c r="J93" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Credicorp Ltd (Peru)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>#ADR_BAP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F94" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G94" s="35" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H94" s="35" t="n">
+        <v>379.22</v>
+      </c>
+      <c r="I94" t="n">
+        <v>5</v>
+      </c>
+      <c r="J94" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>Deere &amp; Co.</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>#DE</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F95" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G95" s="35" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H95" s="35" t="n">
+        <v>658.03</v>
+      </c>
+      <c r="I95" t="n">
+        <v>5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Dell Technologies</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>#DELL</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F96" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G96" s="35" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H96" s="35" t="n">
+        <v>433.58</v>
+      </c>
+      <c r="I96" t="n">
+        <v>5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Delta Airlines Inc.</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>#DAL</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F97" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G97" s="35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H97" s="35" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="I97" t="n">
+        <v>5</v>
+      </c>
+      <c r="J97" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Ebay Inc.</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>#EBAY</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F98" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G98" s="35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H98" s="35" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="I98" t="n">
+        <v>5</v>
+      </c>
+      <c r="J98" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>#EA</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F99" s="34" t="n">
+        <v>0.007503</v>
+      </c>
+      <c r="G99" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H99" s="35" t="n">
+        <v>209.97</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5</v>
+      </c>
+      <c r="J99" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corp.</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>#XOM</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F100" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G100" s="35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H100" s="35" t="n">
+        <v>164.36</v>
+      </c>
+      <c r="I100" t="n">
+        <v>5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FedEx Corporation</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>#FDX</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F101" s="34" t="n">
+        <v>0.007503</v>
+      </c>
+      <c r="G101" s="35" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H101" s="35" t="n">
+        <v>328.2</v>
+      </c>
+      <c r="I101" t="n">
+        <v>5</v>
+      </c>
+      <c r="J101" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ferrari NV</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>#RACE</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F102" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G102" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H102" s="35" t="n">
+        <v>428.66</v>
+      </c>
+      <c r="I102" t="n">
+        <v>5</v>
+      </c>
+      <c r="J102" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>First Solar Inc.</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>#FSLR</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F103" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G103" s="35" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H103" s="35" t="n">
+        <v>210.79</v>
+      </c>
+      <c r="I103" t="n">
+        <v>5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ford Motor Co CFD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>#F</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F104" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G104" s="35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H104" s="35" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="I104" t="n">
+        <v>5</v>
+      </c>
+      <c r="J104" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>#GE</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F105" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G105" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H105" s="35" t="n">
+        <v>345.61</v>
+      </c>
+      <c r="I105" t="n">
+        <v>5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>General Motors Company</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>#GM</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F106" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G106" s="35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H106" s="35" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="I106" t="n">
+        <v>5</v>
+      </c>
+      <c r="J106" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>#GS</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F107" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G107" s="35" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="H107" s="35" t="n">
+        <v>1035.88</v>
+      </c>
+      <c r="I107" t="n">
+        <v>5</v>
+      </c>
+      <c r="J107" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Halliburton Co.</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>#HAL</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F108" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G108" s="35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H108" s="35" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="I108" t="n">
+        <v>5</v>
+      </c>
+      <c r="J108" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Hewlett-Packard Co.</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>#HPQ</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F109" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G109" s="35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H109" s="35" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="I109" t="n">
+        <v>5</v>
+      </c>
+      <c r="J109" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Illumina Inc.</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>#ILMN</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F110" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G110" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H110" s="35" t="n">
+        <v>219.96</v>
+      </c>
+      <c r="I110" t="n">
+        <v>5</v>
+      </c>
+      <c r="J110" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Intel Corp.</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>#INTC</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F111" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G111" s="35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H111" s="35" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="I111" t="n">
+        <v>5</v>
+      </c>
+      <c r="J111" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>International Business Machines Corp.</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>#IBM</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F112" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G112" s="35" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H112" s="35" t="n">
+        <v>231.95</v>
+      </c>
+      <c r="I112" t="n">
+        <v>5</v>
+      </c>
+      <c r="J112" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>#JPM</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F113" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G113" s="35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H113" s="35" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5</v>
+      </c>
+      <c r="J113" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>#JNJ</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F114" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G114" s="35" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H114" s="35" t="n">
+        <v>270.79</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Lockheed Martin Corp.</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>#LMT</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F115" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G115" s="35" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="H115" s="35" t="n">
+        <v>560.97</v>
+      </c>
+      <c r="I115" t="n">
+        <v>5</v>
+      </c>
+      <c r="J115" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Mastercard Inc.</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>#MA</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F116" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G116" s="35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H116" s="35" t="n">
+        <v>597.3099999999999</v>
+      </c>
+      <c r="I116" t="n">
+        <v>5</v>
+      </c>
+      <c r="J116" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>#MCD</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F117" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G117" s="35" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H117" s="35" t="n">
+        <v>271.83</v>
+      </c>
+      <c r="I117" t="n">
+        <v>5</v>
+      </c>
+      <c r="J117" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MercadoLibre Inc.</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>#MELI</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F118" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G118" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H118" s="35" t="n">
+        <v>1967.44</v>
+      </c>
+      <c r="I118" t="n">
+        <v>5</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Meta Platforms Inc.</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>#META</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F119" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G119" s="35" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H119" s="35" t="n">
+        <v>552.24</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MicroStrategy Inc.</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>#MSTR</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F120" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G120" s="35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H120" s="35" t="n">
+        <v>125.55</v>
+      </c>
+      <c r="I120" t="n">
+        <v>5</v>
+      </c>
+      <c r="J120" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Micron Technology Inc.</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>#MU</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F121" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G121" s="35" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H121" s="35" t="n">
+        <v>894.03</v>
+      </c>
+      <c r="I121" t="n">
+        <v>5</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>#MSFT</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F122" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G122" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H122" s="35" t="n">
+        <v>485.49</v>
+      </c>
+      <c r="I122" t="n">
+        <v>5</v>
+      </c>
+      <c r="J122" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Moderna Inc.</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>#MRNA</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F123" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G123" s="35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H123" s="35" t="n">
+        <v>133.64</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5</v>
+      </c>
+      <c r="J123" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>#MS</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>2</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F124" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G124" s="35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H124" s="35" t="n">
+        <v>215.35</v>
+      </c>
+      <c r="I124" t="n">
+        <v>5</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>NIO Limited</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>#NIO</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F125" s="34" t="n">
+        <v>0.017508</v>
+      </c>
+      <c r="G125" s="35" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H125" s="35" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>NVIDIA Corp.</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>#NVDA</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F126" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G126" s="35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H126" s="35" t="n">
+        <v>209.65</v>
+      </c>
+      <c r="I126" t="n">
+        <v>5</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Netflix Inc.</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>#NFLX</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F127" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G127" s="35" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="H127" s="35" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="I127" t="n">
+        <v>5</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Nike Inc.</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>#NKE</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F128" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G128" s="35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H128" s="35" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="I128" t="n">
+        <v>5</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Oracle Corp.</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>#ORCL</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F129" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G129" s="35" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H129" s="35" t="n">
+        <v>142.21</v>
+      </c>
+      <c r="I129" t="n">
+        <v>5</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>#PLTR</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F130" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G130" s="35" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H130" s="35" t="n">
+        <v>173.62</v>
+      </c>
+      <c r="I130" t="n">
+        <v>5</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Pfizer Inc.</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>#PFE</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F131" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G131" s="35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H131" s="35" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="I131" t="n">
+        <v>5</v>
+      </c>
+      <c r="J131" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>#PG</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F132" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G132" s="35" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H132" s="35" t="n">
+        <v>146.76</v>
+      </c>
+      <c r="I132" t="n">
+        <v>5</v>
+      </c>
+      <c r="J132" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Qualcomm Inc.</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>#QCOM</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F133" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G133" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H133" s="35" t="n">
+        <v>156.94</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Salesforce.com Inc.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>#CRM</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F134" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G134" s="35" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H134" s="35" t="n">
+        <v>211.67</v>
+      </c>
+      <c r="I134" t="n">
+        <v>5</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Simon Property Group Inc.</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>#SPG</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F135" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G135" s="35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H135" s="35" t="n">
+        <v>220.69</v>
+      </c>
+      <c r="I135" t="n">
+        <v>5</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Space Exploration Technologies Corp.</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>#SPCX</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="n">
         <v>50</v>
       </c>
-      <c r="E26" t="n">
-        <v>46037.5</v>
-      </c>
-      <c r="F26" s="34" t="n">
-        <v>0.005005</v>
-      </c>
-      <c r="G26" s="35" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>582.4299999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-5.1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>Actualizado desde MT5 (cuenta 51142, CLP) el 2026-08-19 22:06 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días).</t>
+      <c r="E136" t="n">
+        <v>45751.5</v>
+      </c>
+      <c r="F136" s="34" t="n">
+        <v>0.020009</v>
+      </c>
+      <c r="G136" s="35" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H136" s="35" t="n">
+        <v>133.86</v>
+      </c>
+      <c r="I136" t="n">
+        <v>5</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K136" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Starbucks Corp.</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>#SBUX</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F137" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G137" s="35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H137" s="35" t="n">
+        <v>106.63</v>
+      </c>
+      <c r="I137" t="n">
+        <v>5</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Synopsys Inc.</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>#SNPS</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F138" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G138" s="35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H138" s="35" t="n">
+        <v>390.42</v>
+      </c>
+      <c r="I138" t="n">
+        <v>5</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K138" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Target Corp.</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>#TGT</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F139" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G139" s="35" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H139" s="35" t="n">
+        <v>170.61</v>
+      </c>
+      <c r="I139" t="n">
+        <v>5</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Tesla Motors Inc.</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>#TSLA</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F140" s="34" t="n">
+        <v>0.010004</v>
+      </c>
+      <c r="G140" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H140" s="35" t="n">
+        <v>354.32</v>
+      </c>
+      <c r="I140" t="n">
+        <v>5</v>
+      </c>
+      <c r="J140" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K140" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon Corp.</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>#BK</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F141" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G141" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H141" s="35" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="I141" t="n">
+        <v>5</v>
+      </c>
+      <c r="J141" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>The Clorox Company</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>#CLX</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F142" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G142" s="35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H142" s="35" t="n">
+        <v>109</v>
+      </c>
+      <c r="I142" t="n">
+        <v>5</v>
+      </c>
+      <c r="J142" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K142" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>The Home Depot Inc.</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>#HD</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F143" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G143" s="35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H143" s="35" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="I143" t="n">
+        <v>5</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Tilray Inc.</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>#TLRY</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F144" s="34" t="n">
+        <v>0.005003</v>
+      </c>
+      <c r="G144" s="35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H144" s="35" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I144" t="n">
+        <v>5</v>
+      </c>
+      <c r="J144" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Uber Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>#UBER</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F145" s="34" t="n">
+        <v>0.010004</v>
+      </c>
+      <c r="G145" s="35" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H145" s="35" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="I145" t="n">
+        <v>5</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K145" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Vale SA (Brasil)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>#ADR_VALE</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F146" s="34" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="G146" s="35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H146" s="35" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>5</v>
+      </c>
+      <c r="J146" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>#V</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F147" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G147" s="35" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H147" s="35" t="n">
+        <v>380.64</v>
+      </c>
+      <c r="I147" t="n">
+        <v>5</v>
+      </c>
+      <c r="J147" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Walmart Stores</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>#WMT</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F148" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G148" s="35" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H148" s="35" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="I148" t="n">
+        <v>5</v>
+      </c>
+      <c r="J148" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K148" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Walt Disney Co.</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>#DIS</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>915.03</v>
+      </c>
+      <c r="F149" s="34" t="n">
+        <v>0.002501</v>
+      </c>
+      <c r="G149" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H149" s="35" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="I149" t="n">
+        <v>5</v>
+      </c>
+      <c r="J149" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K149" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>CFD Acciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="36" t="inlineStr">
+        <is>
+          <t>Actualizado desde MT5 (cuenta 51492, CLP) el 2026-08-24 10:28 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días). Los nombres en español son los del catálogo del grupo de análisis; el resto llega con la descripción del broker.</t>
         </is>
       </c>
     </row>

--- a/calculadoras excel/Simulador GI.xlsx
+++ b/calculadoras excel/Simulador GI.xlsx
@@ -988,10 +988,10 @@
         <v/>
       </c>
       <c r="G11" s="19" t="n">
-        <v>912.4299999999999</v>
+        <v>912.7</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>917.4299999999999</v>
+        <v>917.7</v>
       </c>
       <c r="I11" s="20" t="n">
         <v>2</v>
@@ -1043,10 +1043,10 @@
         <v/>
       </c>
       <c r="G12" s="19" t="n">
-        <v>919.4299999999999</v>
+        <v>919.7</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>916.4299999999999</v>
+        <v>916.7</v>
       </c>
       <c r="I12" s="20" t="n">
         <v>1</v>
@@ -1098,10 +1098,10 @@
         <v/>
       </c>
       <c r="G13" s="19" t="n">
-        <v>915.4299999999999</v>
+        <v>915.7</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>913.9299999999999</v>
+        <v>914.2</v>
       </c>
       <c r="I13" s="20" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
     <row r="27" ht="42" customHeight="1">
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>Especificaciones del broker al 2026-08-24 10:28 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos del paso que acepta MT5 en ese instrumento, indicado arriba a la derecha. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker avisa cuando el nivel de margen baja de 200% y cierra posiciones por su cuenta en 50%, que es el umbral contra el que se mide el recorrido. Este simulador no incorpora stop loss.</t>
+          <t>Especificaciones de la cuenta real del broker al 2026-08-24 10:45 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos del paso que acepta MT5 en ese instrumento, indicado arriba a la derecha. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker avisa cuando el nivel de margen baja de 200% y cierra posiciones por su cuenta en 50%, que es el umbral contra el que se mide el recorrido. Este simulador no incorpora stop loss.</t>
         </is>
       </c>
       <c r="D27" s="32" t="n"/>
@@ -1575,7 +1575,7 @@
         <v>100000</v>
       </c>
       <c r="E2" t="n">
-        <v>66220820.46</v>
+        <v>66210656.47</v>
       </c>
       <c r="F2" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -1584,7 +1584,7 @@
         <v>0.0004</v>
       </c>
       <c r="H2" s="35" t="n">
-        <v>0.99038</v>
+        <v>0.99028</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -1625,7 +1625,7 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>575344.1</v>
+        <v>575524.65</v>
       </c>
       <c r="F3" s="34" t="n">
         <v>0.009998</v>
@@ -1634,7 +1634,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="35" t="n">
-        <v>114.003</v>
+        <v>113.939</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1675,7 +1675,7 @@
         <v>100000</v>
       </c>
       <c r="E4" t="n">
-        <v>54639270.41</v>
+        <v>54626999.2</v>
       </c>
       <c r="F4" s="34" t="n">
         <v>0.009996</v>
@@ -1684,7 +1684,7 @@
         <v>0.0006000000000000001</v>
       </c>
       <c r="H4" s="35" t="n">
-        <v>1.20075</v>
+        <v>1.20072</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1725,7 +1725,7 @@
         <v>100000</v>
       </c>
       <c r="E5" t="n">
-        <v>114193226.47</v>
+        <v>114182752.26</v>
       </c>
       <c r="F5" s="34" t="n">
         <v>0.009991</v>
@@ -1734,7 +1734,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>0.57477</v>
+        <v>0.57468</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>100000</v>
       </c>
       <c r="E6" t="n">
-        <v>91543000</v>
+        <v>91570000</v>
       </c>
       <c r="F6" s="34" t="n">
         <v>0.01</v>
@@ -1784,7 +1784,7 @@
         <v>0.00032</v>
       </c>
       <c r="H6" s="35" t="n">
-        <v>0.71637</v>
+        <v>0.7159799999999999</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1825,7 +1825,7 @@
         <v>100000</v>
       </c>
       <c r="E7" t="n">
-        <v>54639270.41</v>
+        <v>54626999.2</v>
       </c>
       <c r="F7" s="34" t="n">
         <v>0.019982</v>
@@ -1834,7 +1834,7 @@
         <v>0.003</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>2.28802</v>
+        <v>2.28905</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1875,7 +1875,7 @@
         <v>100000</v>
       </c>
       <c r="E8" t="n">
-        <v>65578658.91</v>
+        <v>65562288.6</v>
       </c>
       <c r="F8" s="34" t="n">
         <v>0.009997000000000001</v>
@@ -1884,7 +1884,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H8" s="35" t="n">
-        <v>1.90519</v>
+        <v>1.90609</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1925,7 +1925,7 @@
         <v>100000</v>
       </c>
       <c r="E9" t="n">
-        <v>66220820.46</v>
+        <v>66210656.47</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>0.009998</v>
@@ -1934,7 +1934,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>1.88645</v>
+        <v>1.88718</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         <v>100000</v>
       </c>
       <c r="E10" t="n">
-        <v>575344.1</v>
+        <v>575524.65</v>
       </c>
       <c r="F10" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -1984,7 +1984,7 @@
         <v>0.08</v>
       </c>
       <c r="H10" s="35" t="n">
-        <v>217.117</v>
+        <v>217.1</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>100000</v>
       </c>
       <c r="E11" t="n">
-        <v>114193226.47</v>
+        <v>114182752.26</v>
       </c>
       <c r="F11" s="34" t="n">
         <v>0.009995</v>
@@ -2034,7 +2034,7 @@
         <v>0.0008</v>
       </c>
       <c r="H11" s="35" t="n">
-        <v>1.09432</v>
+        <v>1.09467</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2075,7 +2075,7 @@
         <v>100000</v>
       </c>
       <c r="E12" t="n">
-        <v>575344.1</v>
+        <v>575524.65</v>
       </c>
       <c r="F12" s="34" t="n">
         <v>0.009998</v>
@@ -2084,7 +2084,7 @@
         <v>0.05</v>
       </c>
       <c r="H12" s="35" t="n">
-        <v>115.125</v>
+        <v>115.071</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -2125,7 +2125,7 @@
         <v>100000</v>
       </c>
       <c r="E13" t="n">
-        <v>114193226.47</v>
+        <v>114182752.26</v>
       </c>
       <c r="F13" s="34" t="n">
         <v>0.009991</v>
@@ -2134,7 +2134,7 @@
         <v>0.00075</v>
       </c>
       <c r="H13" s="35" t="n">
-        <v>0.5804</v>
+        <v>0.5803700000000001</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2184,7 +2184,7 @@
         <v>0.4</v>
       </c>
       <c r="H14" s="35" t="n">
-        <v>915.4299999999999</v>
+        <v>915.7</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2225,7 +2225,7 @@
         <v>100000</v>
       </c>
       <c r="E15" t="n">
-        <v>571607.87</v>
+        <v>571787.17</v>
       </c>
       <c r="F15" s="34" t="n">
         <v>0.010063</v>
@@ -2234,7 +2234,7 @@
         <v>0.04</v>
       </c>
       <c r="H15" s="35" t="n">
-        <v>159.15</v>
+        <v>159.147</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2275,7 +2275,7 @@
         <v>100000</v>
       </c>
       <c r="E16" t="n">
-        <v>91543000</v>
+        <v>91570000</v>
       </c>
       <c r="F16" s="34" t="n">
         <v>0.01</v>
@@ -2284,7 +2284,7 @@
         <v>0.00026</v>
       </c>
       <c r="H16" s="35" t="n">
-        <v>1.16718</v>
+        <v>1.16708</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2325,7 +2325,7 @@
         <v>100000</v>
       </c>
       <c r="E17" t="n">
-        <v>65578658.91</v>
+        <v>65562288.6</v>
       </c>
       <c r="F17" s="34" t="n">
         <v>0.009997000000000001</v>
@@ -2334,7 +2334,7 @@
         <v>0.0006000000000000001</v>
       </c>
       <c r="H17" s="35" t="n">
-        <v>1.62979</v>
+        <v>1.63055</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2375,7 +2375,7 @@
         <v>100000</v>
       </c>
       <c r="E18" t="n">
-        <v>124903100.06</v>
+        <v>124932613.8</v>
       </c>
       <c r="F18" s="34" t="n">
         <v>0.009996</v>
@@ -2384,7 +2384,7 @@
         <v>0.0005</v>
       </c>
       <c r="H18" s="35" t="n">
-        <v>0.85575</v>
+        <v>0.85573</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -2425,7 +2425,7 @@
         <v>100000</v>
       </c>
       <c r="E19" t="n">
-        <v>66220820.46</v>
+        <v>66210656.47</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>0.009997000000000001</v>
@@ -2434,7 +2434,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H19" s="35" t="n">
-        <v>1.61392</v>
+        <v>1.61451</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -2475,7 +2475,7 @@
         <v>100000</v>
       </c>
       <c r="E20" t="n">
-        <v>575344.1</v>
+        <v>575524.65</v>
       </c>
       <c r="F20" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -2484,7 +2484,7 @@
         <v>0.05</v>
       </c>
       <c r="H20" s="35" t="n">
-        <v>185.734</v>
+        <v>185.716</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2525,7 +2525,7 @@
         <v>100000</v>
       </c>
       <c r="E21" t="n">
-        <v>54639270.41</v>
+        <v>54626999.2</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>0.009995</v>
@@ -2534,7 +2534,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H21" s="35" t="n">
-        <v>1.95655</v>
+        <v>1.95741</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2575,7 +2575,7 @@
         <v>100000</v>
       </c>
       <c r="E22" t="n">
-        <v>114193226.47</v>
+        <v>114182752.26</v>
       </c>
       <c r="F22" s="34" t="n">
         <v>0.009995</v>
@@ -2584,7 +2584,7 @@
         <v>0.0005</v>
       </c>
       <c r="H22" s="35" t="n">
-        <v>0.9361</v>
+        <v>0.9363899999999999</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -2625,7 +2625,7 @@
         <v>100000</v>
       </c>
       <c r="E23" t="n">
-        <v>1907120.41</v>
+        <v>1907662.63</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>0.009967999999999999</v>
@@ -2634,7 +2634,7 @@
         <v>0.1</v>
       </c>
       <c r="H23" s="35" t="n">
-        <v>56.20374</v>
+        <v>56.19975</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>100000</v>
       </c>
       <c r="E24" t="n">
-        <v>91543000</v>
+        <v>91570000</v>
       </c>
       <c r="F24" s="34" t="n">
         <v>0.01</v>
@@ -2684,7 +2684,7 @@
         <v>0.0005</v>
       </c>
       <c r="H24" s="35" t="n">
-        <v>1.36442</v>
+        <v>1.36434</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -2725,7 +2725,7 @@
         <v>100000</v>
       </c>
       <c r="E25" t="n">
-        <v>66220820.46</v>
+        <v>66210656.47</v>
       </c>
       <c r="F25" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -2734,7 +2734,7 @@
         <v>0.00075</v>
       </c>
       <c r="H25" s="35" t="n">
-        <v>0.82523</v>
+        <v>0.82517</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -2775,7 +2775,7 @@
         <v>100000</v>
       </c>
       <c r="E26" t="n">
-        <v>575344.1</v>
+        <v>575524.65</v>
       </c>
       <c r="F26" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -2784,7 +2784,7 @@
         <v>0.075</v>
       </c>
       <c r="H26" s="35" t="n">
-        <v>94.977</v>
+        <v>94.926</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -2825,7 +2825,7 @@
         <v>100000</v>
       </c>
       <c r="E27" t="n">
-        <v>114193226.47</v>
+        <v>114182752.26</v>
       </c>
       <c r="F27" s="34" t="n">
         <v>0.009993</v>
@@ -2834,7 +2834,7 @@
         <v>0.00075</v>
       </c>
       <c r="H27" s="35" t="n">
-        <v>0.47881</v>
+        <v>0.47875</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -2875,7 +2875,7 @@
         <v>100000</v>
       </c>
       <c r="E28" t="n">
-        <v>91543000</v>
+        <v>91570000</v>
       </c>
       <c r="F28" s="34" t="n">
         <v>0.01</v>
@@ -2884,7 +2884,7 @@
         <v>0.0005</v>
       </c>
       <c r="H28" s="35" t="n">
-        <v>0.59687</v>
+        <v>0.59656</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -2925,7 +2925,7 @@
         <v>100000</v>
       </c>
       <c r="E29" t="n">
-        <v>575344.1</v>
+        <v>575524.65</v>
       </c>
       <c r="F29" s="34" t="n">
         <v>0.01</v>
@@ -2934,7 +2934,7 @@
         <v>0.075</v>
       </c>
       <c r="H29" s="35" t="n">
-        <v>198.48</v>
+        <v>198.399</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -2975,16 +2975,16 @@
         <v>100000</v>
       </c>
       <c r="E30" t="n">
-        <v>38418086.21</v>
+        <v>38419420.75</v>
       </c>
       <c r="F30" s="34" t="n">
-        <v>0.017232</v>
+        <v>0.017228</v>
       </c>
       <c r="G30" s="35" t="n">
         <v>0.00042</v>
       </c>
       <c r="H30" s="35" t="n">
-        <v>1.38281</v>
+        <v>1.38343</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -3025,7 +3025,7 @@
         <v>100000</v>
       </c>
       <c r="E31" t="n">
-        <v>5098553.58</v>
+        <v>5099801.73</v>
       </c>
       <c r="F31" s="34" t="n">
         <v>0.01059</v>
@@ -3034,7 +3034,7 @@
         <v>0.008</v>
       </c>
       <c r="H31" s="35" t="n">
-        <v>16.9547</v>
+        <v>16.9556</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -3075,16 +3075,16 @@
         <v>100000</v>
       </c>
       <c r="E32" t="n">
-        <v>50796548.57</v>
+        <v>50802791.74</v>
       </c>
       <c r="F32" s="34" t="n">
-        <v>0.022466</v>
+        <v>0.022462</v>
       </c>
       <c r="G32" s="35" t="n">
         <v>0.0005</v>
       </c>
       <c r="H32" s="35" t="n">
-        <v>0.80215</v>
+        <v>0.80246</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -3125,7 +3125,7 @@
         <v>100000</v>
       </c>
       <c r="E33" t="n">
-        <v>1862119.78</v>
+        <v>1862649.67</v>
       </c>
       <c r="F33" s="34" t="n">
         <v>0.163322</v>
@@ -3134,7 +3134,7 @@
         <v>0.16</v>
       </c>
       <c r="H33" s="35" t="n">
-        <v>48.16064</v>
+        <v>48.16115</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -3175,7 +3175,7 @@
         <v>10000</v>
       </c>
       <c r="E34" t="n">
-        <v>9150300</v>
+        <v>9153000</v>
       </c>
       <c r="F34" s="34" t="n">
         <v>0.010004</v>
@@ -3225,7 +3225,7 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>91503</v>
+        <v>91530</v>
       </c>
       <c r="F35" s="34" t="n">
         <v>0.04502</v>
@@ -3234,7 +3234,7 @@
         <v>0.6</v>
       </c>
       <c r="H35" s="35" t="n">
-        <v>4673.36</v>
+        <v>4672.63</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -3275,7 +3275,7 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>91503</v>
+        <v>91530</v>
       </c>
       <c r="F36" s="34" t="n">
         <v>0.015007</v>
@@ -3284,7 +3284,7 @@
         <v>0.15</v>
       </c>
       <c r="H36" s="35" t="n">
-        <v>85.587</v>
+        <v>85.64700000000001</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -3325,7 +3325,7 @@
         <v>5000</v>
       </c>
       <c r="E37" t="n">
-        <v>4575150</v>
+        <v>4576500</v>
       </c>
       <c r="F37" s="34" t="n">
         <v>0.04502</v>
@@ -3334,7 +3334,7 @@
         <v>0.05</v>
       </c>
       <c r="H37" s="35" t="n">
-        <v>69.136</v>
+        <v>69.063</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -3375,7 +3375,7 @@
         <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>91503</v>
+        <v>91530</v>
       </c>
       <c r="F38" s="34" t="n">
         <v>0.015007</v>
@@ -3384,7 +3384,7 @@
         <v>0.1</v>
       </c>
       <c r="H38" s="35" t="n">
-        <v>92.676</v>
+        <v>92.76600000000001</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -3425,7 +3425,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1067.77</v>
+        <v>1067.99</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>0.050033</v>
@@ -3434,7 +3434,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="35" t="n">
-        <v>8459.6</v>
+        <v>8470.1</v>
       </c>
       <c r="I39" t="n">
         <v>5</v>
@@ -3475,7 +3475,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1248.03</v>
+        <v>1248.32</v>
       </c>
       <c r="F40" s="34" t="n">
         <v>0.05004</v>
@@ -3484,7 +3484,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="35" t="n">
-        <v>10857.3</v>
+        <v>10866.3</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1067.77</v>
+        <v>1067.99</v>
       </c>
       <c r="F41" s="34" t="n">
         <v>0.050033</v>
@@ -3534,7 +3534,7 @@
         <v>3</v>
       </c>
       <c r="H41" s="35" t="n">
-        <v>26074.25</v>
+        <v>26102.25</v>
       </c>
       <c r="I41" t="n">
         <v>5</v>
@@ -3575,7 +3575,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F42" s="34" t="n">
         <v>0.050022</v>
@@ -3584,7 +3584,7 @@
         <v>7</v>
       </c>
       <c r="H42" s="35" t="n">
-        <v>53439.51</v>
+        <v>53437.51</v>
       </c>
       <c r="I42" t="n">
         <v>5</v>
@@ -3625,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F43" s="34" t="n">
         <v>0.050022</v>
@@ -3634,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="35" t="n">
-        <v>28932.38</v>
+        <v>29031</v>
       </c>
       <c r="I43" t="n">
         <v>5</v>
@@ -3675,7 +3675,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>9150.299999999999</v>
+        <v>9153</v>
       </c>
       <c r="F44" s="34" t="n">
         <v>0.050022</v>
@@ -3684,7 +3684,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="35" t="n">
-        <v>7654.23</v>
+        <v>7664.23</v>
       </c>
       <c r="I44" t="n">
         <v>5</v>
@@ -3725,16 +3725,16 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F45" s="34" t="n">
         <v>0.015007</v>
       </c>
       <c r="G45" s="35" t="n">
-        <v>83.79000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="H45" s="35" t="n">
-        <v>79260.84</v>
+        <v>79732.67999999999</v>
       </c>
       <c r="I45" t="n">
         <v>5</v>
@@ -3775,7 +3775,7 @@
         <v>1000</v>
       </c>
       <c r="E46" t="n">
-        <v>915030</v>
+        <v>915300</v>
       </c>
       <c r="F46" s="34" t="n">
         <v>0.006003</v>
@@ -3784,7 +3784,7 @@
         <v>0.0103</v>
       </c>
       <c r="H46" s="35" t="n">
-        <v>0.2284</v>
+        <v>0.2305</v>
       </c>
       <c r="I46" t="n">
         <v>5</v>
@@ -3825,7 +3825,7 @@
         <v>10000</v>
       </c>
       <c r="E47" t="n">
-        <v>9150300</v>
+        <v>9153000</v>
       </c>
       <c r="F47" s="34" t="n">
         <v>0.006003</v>
@@ -3834,7 +3834,7 @@
         <v>0.0103</v>
       </c>
       <c r="H47" s="35" t="n">
-        <v>0.0965</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="I47" t="n">
         <v>5</v>
@@ -3875,16 +3875,16 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F48" s="34" t="n">
         <v>0.005002</v>
       </c>
       <c r="G48" s="35" t="n">
-        <v>9.59</v>
+        <v>9.700000000000001</v>
       </c>
       <c r="H48" s="35" t="n">
-        <v>2515.29</v>
+        <v>2526.77</v>
       </c>
       <c r="I48" t="n">
         <v>5</v>
@@ -3925,7 +3925,7 @@
         <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>9150.299999999999</v>
+        <v>9153</v>
       </c>
       <c r="F49" s="34" t="n">
         <v>0.005002</v>
@@ -3934,7 +3934,7 @@
         <v>1.61</v>
       </c>
       <c r="H49" s="35" t="n">
-        <v>53.16</v>
+        <v>53.47</v>
       </c>
       <c r="I49" t="n">
         <v>5</v>
@@ -3975,7 +3975,7 @@
         <v>100</v>
       </c>
       <c r="E50" t="n">
-        <v>91503</v>
+        <v>91530</v>
       </c>
       <c r="F50" s="34" t="n">
         <v>0.006003</v>
@@ -3984,7 +3984,7 @@
         <v>0.65</v>
       </c>
       <c r="H50" s="35" t="n">
-        <v>95.98999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="I50" t="n">
         <v>5</v>
@@ -4025,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F51" s="34" t="n">
         <v>0.250109</v>
@@ -4034,7 +4034,7 @@
         <v>0.26</v>
       </c>
       <c r="H51" s="35" t="n">
-        <v>185.64</v>
+        <v>184.86</v>
       </c>
       <c r="I51" t="n">
         <v>5</v>
@@ -4075,7 +4075,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F52" s="34" t="n">
         <v>0.250109</v>
@@ -4084,7 +4084,7 @@
         <v>0.06</v>
       </c>
       <c r="H52" s="35" t="n">
-        <v>58.38</v>
+        <v>58.29</v>
       </c>
       <c r="I52" t="n">
         <v>5</v>
@@ -4125,7 +4125,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F53" s="34" t="n">
         <v>0.100044</v>
@@ -4134,7 +4134,7 @@
         <v>0.05</v>
       </c>
       <c r="H53" s="35" t="n">
-        <v>62.17</v>
+        <v>62.4</v>
       </c>
       <c r="I53" t="n">
         <v>5</v>
@@ -4175,7 +4175,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F54" s="34" t="n">
         <v>0.100044</v>
@@ -4184,7 +4184,7 @@
         <v>0.53</v>
       </c>
       <c r="H54" s="35" t="n">
-        <v>704</v>
+        <v>706.35</v>
       </c>
       <c r="I54" t="n">
         <v>5</v>
@@ -4225,7 +4225,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F55" s="34" t="n">
         <v>0.100044</v>
@@ -4234,7 +4234,7 @@
         <v>0.25</v>
       </c>
       <c r="H55" s="35" t="n">
-        <v>428.74</v>
+        <v>428.66</v>
       </c>
       <c r="I55" t="n">
         <v>5</v>
@@ -4275,7 +4275,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F56" s="34" t="n">
         <v>0.100044</v>
@@ -4284,7 +4284,7 @@
         <v>0.48</v>
       </c>
       <c r="H56" s="35" t="n">
-        <v>763.04</v>
+        <v>763.98</v>
       </c>
       <c r="I56" t="n">
         <v>5</v>
@@ -4325,7 +4325,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F57" s="34" t="n">
         <v>0.250109</v>
@@ -4334,7 +4334,7 @@
         <v>0.26</v>
       </c>
       <c r="H57" s="35" t="n">
-        <v>72.47</v>
+        <v>72.48</v>
       </c>
       <c r="I57" t="n">
         <v>5</v>
@@ -4375,7 +4375,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F58" s="34" t="n">
         <v>0.250109</v>
@@ -4425,7 +4425,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F59" s="34" t="n">
         <v>0.100044</v>
@@ -4434,7 +4434,7 @@
         <v>0.15</v>
       </c>
       <c r="H59" s="35" t="n">
-        <v>35.61</v>
+        <v>35.68</v>
       </c>
       <c r="I59" t="n">
         <v>5</v>
@@ -4475,7 +4475,7 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F60" s="34" t="n">
         <v>0.100044</v>
@@ -4484,7 +4484,7 @@
         <v>0.22</v>
       </c>
       <c r="H60" s="35" t="n">
-        <v>35.35</v>
+        <v>35.43</v>
       </c>
       <c r="I60" t="n">
         <v>5</v>
@@ -4525,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F61" s="34" t="n">
         <v>0.100044</v>
@@ -4534,7 +4534,7 @@
         <v>0.15</v>
       </c>
       <c r="H61" s="35" t="n">
-        <v>66.03</v>
+        <v>66.12</v>
       </c>
       <c r="I61" t="n">
         <v>5</v>
@@ -4575,7 +4575,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F62" s="34" t="n">
         <v>0.100044</v>
@@ -4584,7 +4584,7 @@
         <v>0.4</v>
       </c>
       <c r="H62" s="35" t="n">
-        <v>500.46</v>
+        <v>502.2</v>
       </c>
       <c r="I62" t="n">
         <v>5</v>
@@ -4625,7 +4625,7 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F63" s="34" t="n">
         <v>0.250109</v>
@@ -4634,7 +4634,7 @@
         <v>0.26</v>
       </c>
       <c r="H63" s="35" t="n">
-        <v>298.89</v>
+        <v>298.72</v>
       </c>
       <c r="I63" t="n">
         <v>5</v>
@@ -4675,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F64" s="34" t="n">
         <v>0.005002</v>
@@ -4684,7 +4684,7 @@
         <v>0.14</v>
       </c>
       <c r="H64" s="35" t="n">
-        <v>25.57</v>
+        <v>25.61</v>
       </c>
       <c r="I64" t="n">
         <v>5</v>
@@ -4725,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F65" s="34" t="n">
         <v>0.005002</v>
@@ -4734,7 +4734,7 @@
         <v>0.25</v>
       </c>
       <c r="H65" s="35" t="n">
-        <v>117.17</v>
+        <v>117.07</v>
       </c>
       <c r="I65" t="n">
         <v>5</v>
@@ -4775,7 +4775,7 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F66" s="34" t="n">
         <v>0.002501</v>
@@ -4784,7 +4784,7 @@
         <v>1.48</v>
       </c>
       <c r="H66" s="35" t="n">
-        <v>277.19</v>
+        <v>278.34</v>
       </c>
       <c r="I66" t="n">
         <v>5</v>
@@ -4825,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F67" s="34" t="n">
         <v>0.005002</v>
@@ -4834,7 +4834,7 @@
         <v>0.26</v>
       </c>
       <c r="H67" s="35" t="n">
-        <v>455.71</v>
+        <v>456.51</v>
       </c>
       <c r="I67" t="n">
         <v>5</v>
@@ -4875,7 +4875,7 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F68" s="34" t="n">
         <v>0.020009</v>
@@ -4884,7 +4884,7 @@
         <v>0.6</v>
       </c>
       <c r="H68" s="35" t="n">
-        <v>192.8</v>
+        <v>192.95</v>
       </c>
       <c r="I68" t="n">
         <v>5</v>
@@ -4925,7 +4925,7 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F69" s="34" t="n">
         <v>0.005002</v>
@@ -4934,7 +4934,7 @@
         <v>0.4</v>
       </c>
       <c r="H69" s="35" t="n">
-        <v>117.85</v>
+        <v>120.23</v>
       </c>
       <c r="I69" t="n">
         <v>5</v>
@@ -4975,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F70" s="34" t="n">
         <v>0.002501</v>
@@ -4984,7 +4984,7 @@
         <v>0.35</v>
       </c>
       <c r="H70" s="35" t="n">
-        <v>345.2</v>
+        <v>346.65</v>
       </c>
       <c r="I70" t="n">
         <v>5</v>
@@ -5025,7 +5025,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F71" s="34" t="n">
         <v>0.007503</v>
@@ -5034,7 +5034,7 @@
         <v>0.31</v>
       </c>
       <c r="H71" s="35" t="n">
-        <v>261.31</v>
+        <v>262.57</v>
       </c>
       <c r="I71" t="n">
         <v>5</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F72" s="34" t="n">
         <v>0.005002</v>
@@ -5125,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F73" s="34" t="n">
         <v>0.010004</v>
@@ -5134,7 +5134,7 @@
         <v>0.2</v>
       </c>
       <c r="H73" s="35" t="n">
-        <v>120.61</v>
+        <v>120.71</v>
       </c>
       <c r="I73" t="n">
         <v>5</v>
@@ -5175,7 +5175,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F74" s="34" t="n">
         <v>0.002501</v>
@@ -5184,7 +5184,7 @@
         <v>0.31</v>
       </c>
       <c r="H74" s="35" t="n">
-        <v>343.59</v>
+        <v>343.24</v>
       </c>
       <c r="I74" t="n">
         <v>5</v>
@@ -5225,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F75" s="34" t="n">
         <v>0.002501</v>
@@ -5234,7 +5234,7 @@
         <v>0.11</v>
       </c>
       <c r="H75" s="35" t="n">
-        <v>77.61</v>
+        <v>77.7</v>
       </c>
       <c r="I75" t="n">
         <v>5</v>
@@ -5275,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F76" s="34" t="n">
         <v>0.002501</v>
@@ -5284,7 +5284,7 @@
         <v>0.47</v>
       </c>
       <c r="H76" s="35" t="n">
-        <v>440.77</v>
+        <v>440.38</v>
       </c>
       <c r="I76" t="n">
         <v>5</v>
@@ -5325,7 +5325,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F77" s="34" t="n">
         <v>0.005002</v>
@@ -5334,7 +5334,7 @@
         <v>0.32</v>
       </c>
       <c r="H77" s="35" t="n">
-        <v>312.8</v>
+        <v>313.35</v>
       </c>
       <c r="I77" t="n">
         <v>5</v>
@@ -5375,7 +5375,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F78" s="34" t="n">
         <v>0.002501</v>
@@ -5384,7 +5384,7 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="H78" s="35" t="n">
-        <v>93.28</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="I78" t="n">
         <v>5</v>
@@ -5425,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F79" s="34" t="n">
         <v>0.005002</v>
@@ -5434,7 +5434,7 @@
         <v>0.08</v>
       </c>
       <c r="H79" s="35" t="n">
-        <v>62.71</v>
+        <v>62.55</v>
       </c>
       <c r="I79" t="n">
         <v>5</v>
@@ -5475,7 +5475,7 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F80" s="34" t="n">
         <v>0.005002</v>
@@ -5484,7 +5484,7 @@
         <v>0.3</v>
       </c>
       <c r="H80" s="35" t="n">
-        <v>26.49</v>
+        <v>26.45</v>
       </c>
       <c r="I80" t="n">
         <v>5</v>
@@ -5525,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F81" s="34" t="n">
         <v>0.002501</v>
@@ -5534,7 +5534,7 @@
         <v>0.2</v>
       </c>
       <c r="H81" s="35" t="n">
-        <v>87.54000000000001</v>
+        <v>87.77</v>
       </c>
       <c r="I81" t="n">
         <v>5</v>
@@ -5575,16 +5575,16 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F82" s="34" t="n">
-        <v>0.010004</v>
+        <v>0.010005</v>
       </c>
       <c r="G82" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="H82" s="35" t="n">
-        <v>14.38</v>
+        <v>14.51</v>
       </c>
       <c r="I82" t="n">
         <v>5</v>
@@ -5625,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F83" s="34" t="n">
         <v>0.005002</v>
@@ -5634,7 +5634,7 @@
         <v>0.85</v>
       </c>
       <c r="H83" s="35" t="n">
-        <v>215.06</v>
+        <v>215.1</v>
       </c>
       <c r="I83" t="n">
         <v>5</v>
@@ -5675,7 +5675,7 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F84" s="34" t="n">
         <v>0.005002</v>
@@ -5684,7 +5684,7 @@
         <v>0.89</v>
       </c>
       <c r="H84" s="35" t="n">
-        <v>210.58</v>
+        <v>210.38</v>
       </c>
       <c r="I84" t="n">
         <v>5</v>
@@ -5725,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F85" s="34" t="n">
         <v>0.017508</v>
@@ -5734,7 +5734,7 @@
         <v>2.8</v>
       </c>
       <c r="H85" s="35" t="n">
-        <v>363.29</v>
+        <v>364.13</v>
       </c>
       <c r="I85" t="n">
         <v>5</v>
@@ -5775,7 +5775,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F86" s="34" t="n">
         <v>0.012503</v>
@@ -5784,7 +5784,7 @@
         <v>0.05</v>
       </c>
       <c r="H86" s="35" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I86" t="n">
         <v>5</v>
@@ -5825,7 +5825,7 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F87" s="34" t="n">
         <v>0.002501</v>
@@ -5834,7 +5834,7 @@
         <v>0.45</v>
       </c>
       <c r="H87" s="35" t="n">
-        <v>810.67</v>
+        <v>811.3200000000001</v>
       </c>
       <c r="I87" t="n">
         <v>5</v>
@@ -5875,7 +5875,7 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F88" s="34" t="n">
         <v>0.002501</v>
@@ -5884,7 +5884,7 @@
         <v>0.36</v>
       </c>
       <c r="H88" s="35" t="n">
-        <v>204.32</v>
+        <v>203.33</v>
       </c>
       <c r="I88" t="n">
         <v>5</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F89" s="34" t="n">
         <v>0.005002</v>
@@ -5934,7 +5934,7 @@
         <v>0.14</v>
       </c>
       <c r="H89" s="35" t="n">
-        <v>109.99</v>
+        <v>110.32</v>
       </c>
       <c r="I89" t="n">
         <v>5</v>
@@ -5975,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F90" s="34" t="n">
         <v>0.005002</v>
@@ -5984,7 +5984,7 @@
         <v>0.19</v>
       </c>
       <c r="H90" s="35" t="n">
-        <v>132.04</v>
+        <v>131.66</v>
       </c>
       <c r="I90" t="n">
         <v>5</v>
@@ -6025,7 +6025,7 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F91" s="34" t="n">
         <v>0.002501</v>
@@ -6034,7 +6034,7 @@
         <v>0.14</v>
       </c>
       <c r="H91" s="35" t="n">
-        <v>92.36</v>
+        <v>92.34</v>
       </c>
       <c r="I91" t="n">
         <v>5</v>
@@ -6075,7 +6075,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F92" s="34" t="n">
         <v>0.017508</v>
@@ -6084,7 +6084,7 @@
         <v>0.2</v>
       </c>
       <c r="H92" s="35" t="n">
-        <v>188.42</v>
+        <v>188.78</v>
       </c>
       <c r="I92" t="n">
         <v>5</v>
@@ -6125,7 +6125,7 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F93" s="34" t="n">
         <v>0.002501</v>
@@ -6134,7 +6134,7 @@
         <v>0.97</v>
       </c>
       <c r="H93" s="35" t="n">
-        <v>961.46</v>
+        <v>965.36</v>
       </c>
       <c r="I93" t="n">
         <v>5</v>
@@ -6175,7 +6175,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F94" s="34" t="n">
         <v>0.005002</v>
@@ -6184,7 +6184,7 @@
         <v>0.51</v>
       </c>
       <c r="H94" s="35" t="n">
-        <v>379.22</v>
+        <v>378.38</v>
       </c>
       <c r="I94" t="n">
         <v>5</v>
@@ -6225,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F95" s="34" t="n">
         <v>0.005002</v>
@@ -6234,7 +6234,7 @@
         <v>0.77</v>
       </c>
       <c r="H95" s="35" t="n">
-        <v>658.03</v>
+        <v>659.26</v>
       </c>
       <c r="I95" t="n">
         <v>5</v>
@@ -6275,7 +6275,7 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F96" s="34" t="n">
         <v>0.005002</v>
@@ -6284,7 +6284,7 @@
         <v>0.06</v>
       </c>
       <c r="H96" s="35" t="n">
-        <v>433.58</v>
+        <v>435.67</v>
       </c>
       <c r="I96" t="n">
         <v>5</v>
@@ -6325,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F97" s="34" t="n">
         <v>0.005002</v>
@@ -6334,7 +6334,7 @@
         <v>0.11</v>
       </c>
       <c r="H97" s="35" t="n">
-        <v>82.7</v>
+        <v>82.67</v>
       </c>
       <c r="I97" t="n">
         <v>5</v>
@@ -6375,7 +6375,7 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F98" s="34" t="n">
         <v>0.005002</v>
@@ -6384,7 +6384,7 @@
         <v>0.15</v>
       </c>
       <c r="H98" s="35" t="n">
-        <v>105.73</v>
+        <v>106.24</v>
       </c>
       <c r="I98" t="n">
         <v>5</v>
@@ -6425,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F99" s="34" t="n">
         <v>0.007503</v>
@@ -6475,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F100" s="34" t="n">
         <v>0.005002</v>
@@ -6484,7 +6484,7 @@
         <v>0.25</v>
       </c>
       <c r="H100" s="35" t="n">
-        <v>164.36</v>
+        <v>163.88</v>
       </c>
       <c r="I100" t="n">
         <v>5</v>
@@ -6525,7 +6525,7 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F101" s="34" t="n">
         <v>0.007503</v>
@@ -6534,7 +6534,7 @@
         <v>0.64</v>
       </c>
       <c r="H101" s="35" t="n">
-        <v>328.2</v>
+        <v>327.99</v>
       </c>
       <c r="I101" t="n">
         <v>5</v>
@@ -6575,7 +6575,7 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F102" s="34" t="n">
         <v>0.005002</v>
@@ -6584,7 +6584,7 @@
         <v>0.6</v>
       </c>
       <c r="H102" s="35" t="n">
-        <v>428.66</v>
+        <v>428.76</v>
       </c>
       <c r="I102" t="n">
         <v>5</v>
@@ -6625,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F103" s="34" t="n">
         <v>0.005002</v>
@@ -6634,7 +6634,7 @@
         <v>0.46</v>
       </c>
       <c r="H103" s="35" t="n">
-        <v>210.79</v>
+        <v>211.39</v>
       </c>
       <c r="I103" t="n">
         <v>5</v>
@@ -6675,7 +6675,7 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F104" s="34" t="n">
         <v>0.005002</v>
@@ -6684,7 +6684,7 @@
         <v>0.08</v>
       </c>
       <c r="H104" s="35" t="n">
-        <v>14.04</v>
+        <v>13.94</v>
       </c>
       <c r="I104" t="n">
         <v>5</v>
@@ -6725,7 +6725,7 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F105" s="34" t="n">
         <v>0.002501</v>
@@ -6734,7 +6734,7 @@
         <v>0.21</v>
       </c>
       <c r="H105" s="35" t="n">
-        <v>345.61</v>
+        <v>344.17</v>
       </c>
       <c r="I105" t="n">
         <v>5</v>
@@ -6775,7 +6775,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F106" s="34" t="n">
         <v>0.002501</v>
@@ -6784,7 +6784,7 @@
         <v>0.08</v>
       </c>
       <c r="H106" s="35" t="n">
-        <v>86.88</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="I106" t="n">
         <v>5</v>
@@ -6825,7 +6825,7 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F107" s="34" t="n">
         <v>0.002501</v>
@@ -6834,7 +6834,7 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="H107" s="35" t="n">
-        <v>1035.88</v>
+        <v>1032.08</v>
       </c>
       <c r="I107" t="n">
         <v>5</v>
@@ -6875,7 +6875,7 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F108" s="34" t="n">
         <v>0.002501</v>
@@ -6884,7 +6884,7 @@
         <v>0.09</v>
       </c>
       <c r="H108" s="35" t="n">
-        <v>34.74</v>
+        <v>34.52</v>
       </c>
       <c r="I108" t="n">
         <v>5</v>
@@ -6925,7 +6925,7 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F109" s="34" t="n">
         <v>0.005002</v>
@@ -6934,7 +6934,7 @@
         <v>0.08</v>
       </c>
       <c r="H109" s="35" t="n">
-        <v>29.26</v>
+        <v>29.08</v>
       </c>
       <c r="I109" t="n">
         <v>5</v>
@@ -6975,7 +6975,7 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F110" s="34" t="n">
         <v>0.005002</v>
@@ -6984,7 +6984,7 @@
         <v>1.6</v>
       </c>
       <c r="H110" s="35" t="n">
-        <v>219.96</v>
+        <v>220.82</v>
       </c>
       <c r="I110" t="n">
         <v>5</v>
@@ -7025,7 +7025,7 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F111" s="34" t="n">
         <v>0.005002</v>
@@ -7034,7 +7034,7 @@
         <v>0.08</v>
       </c>
       <c r="H111" s="35" t="n">
-        <v>85.84</v>
+        <v>86.27</v>
       </c>
       <c r="I111" t="n">
         <v>5</v>
@@ -7075,7 +7075,7 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F112" s="34" t="n">
         <v>0.005002</v>
@@ -7084,7 +7084,7 @@
         <v>0.66</v>
       </c>
       <c r="H112" s="35" t="n">
-        <v>231.95</v>
+        <v>232.46</v>
       </c>
       <c r="I112" t="n">
         <v>5</v>
@@ -7125,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F113" s="34" t="n">
         <v>0.002501</v>
@@ -7134,7 +7134,7 @@
         <v>0.25</v>
       </c>
       <c r="H113" s="35" t="n">
-        <v>357.52</v>
+        <v>356.84</v>
       </c>
       <c r="I113" t="n">
         <v>5</v>
@@ -7175,7 +7175,7 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F114" s="34" t="n">
         <v>0.002501</v>
@@ -7184,7 +7184,7 @@
         <v>0.37</v>
       </c>
       <c r="H114" s="35" t="n">
-        <v>270.79</v>
+        <v>271.04</v>
       </c>
       <c r="I114" t="n">
         <v>5</v>
@@ -7225,7 +7225,7 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F115" s="34" t="n">
         <v>0.002501</v>
@@ -7234,7 +7234,7 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="H115" s="35" t="n">
-        <v>560.97</v>
+        <v>562.84</v>
       </c>
       <c r="I115" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F116" s="34" t="n">
         <v>0.002501</v>
@@ -7284,7 +7284,7 @@
         <v>0.85</v>
       </c>
       <c r="H116" s="35" t="n">
-        <v>597.3099999999999</v>
+        <v>597.39</v>
       </c>
       <c r="I116" t="n">
         <v>5</v>
@@ -7325,7 +7325,7 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F117" s="34" t="n">
         <v>0.005002</v>
@@ -7334,7 +7334,7 @@
         <v>0.72</v>
       </c>
       <c r="H117" s="35" t="n">
-        <v>271.83</v>
+        <v>272.39</v>
       </c>
       <c r="I117" t="n">
         <v>5</v>
@@ -7375,7 +7375,7 @@
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F118" s="34" t="n">
         <v>0.005002</v>
@@ -7384,7 +7384,7 @@
         <v>7</v>
       </c>
       <c r="H118" s="35" t="n">
-        <v>1967.44</v>
+        <v>1976.61</v>
       </c>
       <c r="I118" t="n">
         <v>5</v>
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F119" s="34" t="n">
         <v>0.005002</v>
@@ -7434,7 +7434,7 @@
         <v>0.64</v>
       </c>
       <c r="H119" s="35" t="n">
-        <v>552.24</v>
+        <v>553.22</v>
       </c>
       <c r="I119" t="n">
         <v>5</v>
@@ -7475,7 +7475,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F120" s="34" t="n">
         <v>0.005002</v>
@@ -7484,7 +7484,7 @@
         <v>0.8</v>
       </c>
       <c r="H120" s="35" t="n">
-        <v>125.55</v>
+        <v>125.94</v>
       </c>
       <c r="I120" t="n">
         <v>5</v>
@@ -7525,7 +7525,7 @@
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F121" s="34" t="n">
         <v>0.005002</v>
@@ -7534,7 +7534,7 @@
         <v>0.19</v>
       </c>
       <c r="H121" s="35" t="n">
-        <v>894.03</v>
+        <v>900.79</v>
       </c>
       <c r="I121" t="n">
         <v>5</v>
@@ -7575,7 +7575,7 @@
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F122" s="34" t="n">
         <v>0.005002</v>
@@ -7584,7 +7584,7 @@
         <v>0.6</v>
       </c>
       <c r="H122" s="35" t="n">
-        <v>485.49</v>
+        <v>487.84</v>
       </c>
       <c r="I122" t="n">
         <v>5</v>
@@ -7625,7 +7625,7 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F123" s="34" t="n">
         <v>0.005002</v>
@@ -7634,7 +7634,7 @@
         <v>0.14</v>
       </c>
       <c r="H123" s="35" t="n">
-        <v>133.64</v>
+        <v>135.1</v>
       </c>
       <c r="I123" t="n">
         <v>5</v>
@@ -7675,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F124" s="34" t="n">
         <v>0.005002</v>
@@ -7684,7 +7684,7 @@
         <v>0.11</v>
       </c>
       <c r="H124" s="35" t="n">
-        <v>215.35</v>
+        <v>214.93</v>
       </c>
       <c r="I124" t="n">
         <v>5</v>
@@ -7725,16 +7725,16 @@
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F125" s="34" t="n">
-        <v>0.017508</v>
+        <v>0.017507</v>
       </c>
       <c r="G125" s="35" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H125" s="35" t="n">
-        <v>4.49</v>
+        <v>4.52</v>
       </c>
       <c r="I125" t="n">
         <v>5</v>
@@ -7775,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F126" s="34" t="n">
         <v>0.005002</v>
@@ -7784,7 +7784,7 @@
         <v>0.9</v>
       </c>
       <c r="H126" s="35" t="n">
-        <v>209.65</v>
+        <v>210.12</v>
       </c>
       <c r="I126" t="n">
         <v>5</v>
@@ -7825,7 +7825,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F127" s="34" t="n">
         <v>0.005002</v>
@@ -7834,7 +7834,7 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="H127" s="35" t="n">
-        <v>80.76000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="I127" t="n">
         <v>5</v>
@@ -7875,7 +7875,7 @@
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F128" s="34" t="n">
         <v>0.002501</v>
@@ -7884,7 +7884,7 @@
         <v>0.35</v>
       </c>
       <c r="H128" s="35" t="n">
-        <v>41.27</v>
+        <v>41.41</v>
       </c>
       <c r="I128" t="n">
         <v>5</v>
@@ -7925,7 +7925,7 @@
         <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F129" s="34" t="n">
         <v>0.002501</v>
@@ -7934,7 +7934,7 @@
         <v>0.17</v>
       </c>
       <c r="H129" s="35" t="n">
-        <v>142.21</v>
+        <v>142.74</v>
       </c>
       <c r="I129" t="n">
         <v>5</v>
@@ -7975,7 +7975,7 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F130" s="34" t="n">
         <v>0.005002</v>
@@ -7984,7 +7984,7 @@
         <v>0.19</v>
       </c>
       <c r="H130" s="35" t="n">
-        <v>173.62</v>
+        <v>176.55</v>
       </c>
       <c r="I130" t="n">
         <v>5</v>
@@ -8025,7 +8025,7 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F131" s="34" t="n">
         <v>0.005002</v>
@@ -8034,7 +8034,7 @@
         <v>0.08</v>
       </c>
       <c r="H131" s="35" t="n">
-        <v>27.96</v>
+        <v>27.92</v>
       </c>
       <c r="I131" t="n">
         <v>5</v>
@@ -8075,7 +8075,7 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F132" s="34" t="n">
         <v>0.002501</v>
@@ -8084,7 +8084,7 @@
         <v>0.31</v>
       </c>
       <c r="H132" s="35" t="n">
-        <v>146.76</v>
+        <v>146.78</v>
       </c>
       <c r="I132" t="n">
         <v>5</v>
@@ -8125,7 +8125,7 @@
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F133" s="34" t="n">
         <v>0.002501</v>
@@ -8134,7 +8134,7 @@
         <v>0.3</v>
       </c>
       <c r="H133" s="35" t="n">
-        <v>156.94</v>
+        <v>157.69</v>
       </c>
       <c r="I133" t="n">
         <v>5</v>
@@ -8175,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F134" s="34" t="n">
         <v>0.002501</v>
@@ -8184,7 +8184,7 @@
         <v>0.47</v>
       </c>
       <c r="H134" s="35" t="n">
-        <v>211.67</v>
+        <v>212.03</v>
       </c>
       <c r="I134" t="n">
         <v>5</v>
@@ -8225,7 +8225,7 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F135" s="34" t="n">
         <v>0.005002</v>
@@ -8234,7 +8234,7 @@
         <v>0.45</v>
       </c>
       <c r="H135" s="35" t="n">
-        <v>220.69</v>
+        <v>219.57</v>
       </c>
       <c r="I135" t="n">
         <v>5</v>
@@ -8275,7 +8275,7 @@
         <v>50</v>
       </c>
       <c r="E136" t="n">
-        <v>45751.5</v>
+        <v>45765</v>
       </c>
       <c r="F136" s="34" t="n">
         <v>0.020009</v>
@@ -8284,7 +8284,7 @@
         <v>0.23</v>
       </c>
       <c r="H136" s="35" t="n">
-        <v>133.86</v>
+        <v>135.16</v>
       </c>
       <c r="I136" t="n">
         <v>5</v>
@@ -8325,7 +8325,7 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F137" s="34" t="n">
         <v>0.002501</v>
@@ -8334,7 +8334,7 @@
         <v>0.15</v>
       </c>
       <c r="H137" s="35" t="n">
-        <v>106.63</v>
+        <v>106.69</v>
       </c>
       <c r="I137" t="n">
         <v>5</v>
@@ -8375,7 +8375,7 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F138" s="34" t="n">
         <v>0.005002</v>
@@ -8384,7 +8384,7 @@
         <v>0.65</v>
       </c>
       <c r="H138" s="35" t="n">
-        <v>390.42</v>
+        <v>389.91</v>
       </c>
       <c r="I138" t="n">
         <v>5</v>
@@ -8425,7 +8425,7 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F139" s="34" t="n">
         <v>0.002501</v>
@@ -8434,7 +8434,7 @@
         <v>0.59</v>
       </c>
       <c r="H139" s="35" t="n">
-        <v>170.61</v>
+        <v>170.34</v>
       </c>
       <c r="I139" t="n">
         <v>5</v>
@@ -8475,7 +8475,7 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F140" s="34" t="n">
         <v>0.010004</v>
@@ -8484,7 +8484,7 @@
         <v>0.3</v>
       </c>
       <c r="H140" s="35" t="n">
-        <v>354.32</v>
+        <v>358.04</v>
       </c>
       <c r="I140" t="n">
         <v>5</v>
@@ -8525,7 +8525,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F141" s="34" t="n">
         <v>0.005002</v>
@@ -8575,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F142" s="34" t="n">
         <v>0.005002</v>
@@ -8584,7 +8584,7 @@
         <v>0.35</v>
       </c>
       <c r="H142" s="35" t="n">
-        <v>109</v>
+        <v>109.06</v>
       </c>
       <c r="I142" t="n">
         <v>5</v>
@@ -8625,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F143" s="34" t="n">
         <v>0.002501</v>
@@ -8634,7 +8634,7 @@
         <v>0.8</v>
       </c>
       <c r="H143" s="35" t="n">
-        <v>340.12</v>
+        <v>338.9</v>
       </c>
       <c r="I143" t="n">
         <v>5</v>
@@ -8675,16 +8675,16 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F144" s="34" t="n">
-        <v>0.005003</v>
+        <v>0.005001</v>
       </c>
       <c r="G144" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="H144" s="35" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="I144" t="n">
         <v>5</v>
@@ -8725,7 +8725,7 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F145" s="34" t="n">
         <v>0.010004</v>
@@ -8734,7 +8734,7 @@
         <v>0.17</v>
       </c>
       <c r="H145" s="35" t="n">
-        <v>79.43000000000001</v>
+        <v>79.58</v>
       </c>
       <c r="I145" t="n">
         <v>5</v>
@@ -8775,7 +8775,7 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F146" s="34" t="n">
         <v>0.005002</v>
@@ -8784,7 +8784,7 @@
         <v>0.09</v>
       </c>
       <c r="H146" s="35" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="I146" t="n">
         <v>5</v>
@@ -8825,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F147" s="34" t="n">
         <v>0.002501</v>
@@ -8834,7 +8834,7 @@
         <v>0.37</v>
       </c>
       <c r="H147" s="35" t="n">
-        <v>380.64</v>
+        <v>381.12</v>
       </c>
       <c r="I147" t="n">
         <v>5</v>
@@ -8875,7 +8875,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F148" s="34" t="n">
         <v>0.002501</v>
@@ -8884,7 +8884,7 @@
         <v>0.28</v>
       </c>
       <c r="H148" s="35" t="n">
-        <v>104.7</v>
+        <v>104.55</v>
       </c>
       <c r="I148" t="n">
         <v>5</v>
@@ -8925,7 +8925,7 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>915.03</v>
+        <v>915.3</v>
       </c>
       <c r="F149" s="34" t="n">
         <v>0.002501</v>
@@ -8934,7 +8934,7 @@
         <v>0.5</v>
       </c>
       <c r="H149" s="35" t="n">
-        <v>111.05</v>
+        <v>110.83</v>
       </c>
       <c r="I149" t="n">
         <v>5</v>
@@ -8960,7 +8960,7 @@
     <row r="151">
       <c r="A151" s="36" t="inlineStr">
         <is>
-          <t>Actualizado desde MT5 (cuenta 51492, CLP) el 2026-08-24 10:28 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días). Los nombres en español son los del catálogo del grupo de análisis; el resto llega con la descripción del broker.</t>
+          <t>Especificaciones tomadas de la cuenta 51492 de MT5, GrupoInteligenciaSpA-Server, tipo REAL, en CLP, el 2026-08-24 10:45 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días). Los nombres en español son los del catálogo del grupo de análisis; el resto llega con la descripción del broker.</t>
         </is>
       </c>
     </row>
